--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -5,18 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/base de datos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/rigi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F639624F-9726-1949-8FBA-E1B8B4BC3652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6768F59F-1435-D647-9AC9-C083F6591518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36640" yWindow="600" windowWidth="32160" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36640" yWindow="600" windowWidth="32160" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="7" r:id="rId1"/>
     <sheet name="Diccionario" sheetId="6" r:id="rId2"/>
     <sheet name="Variable_Anterior" sheetId="8" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -98,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="483">
   <si>
     <t>id_proyecto</t>
   </si>
@@ -451,9 +454,6 @@
     <t>Rechazado</t>
   </si>
   <si>
-    <t>Mega</t>
-  </si>
-  <si>
     <t>Minera Agua Rica (MARA)</t>
   </si>
   <si>
@@ -1135,22 +1135,7 @@
     <t>https://www.geo-park.com/es/news/geopark-solicita-adhesion-al-rigi-por-proyecto-de-inversion/; https://econojournal.com.ar/oilgas/geopark-presenta-al-rigi-una-inversion-por-us1-000-millones-para-un-hub-petrolero-en-vaca-muerta/</t>
   </si>
   <si>
-    <t>Ampliación de la capacidad de procesamiento, fraccionamiento y transporte de líquidos del gas natural provenientes de la Cuenca Neuquina. Las obras abarcan instalaciones en Neuquén y el corredor de transporte hasta el complejo de fraccionamiento y exportación de Bahía Blanca, con un aumento proyectado de 1.500 toneladas diarias.</t>
-  </si>
-  <si>
     <t>YPF S.A. (Argentina); Petrobras (Brasil); Dow (Argentina)</t>
-  </si>
-  <si>
-    <t>Compañía Mega S.A. – Sucursal Dedicada</t>
-  </si>
-  <si>
-    <t>Neuquén; Río Negro; La Pampa; Buenos Aires</t>
-  </si>
-  <si>
-    <t>Globaris; EconoJournal; Compañía MEGA; Luis Caputo; auditoría 2026-08-08</t>
-  </si>
-  <si>
-    <t>https://econojournal.com.ar/oilgas/vaca-muerta-mega-se-presenta-al-rigi-con-una-inversion-de-us360-millones-en-su-planta-de-separacion-de-liquidos-del-gas/; https://www.ingenierowhite.com/2026/07/31/mega-obtuvo-la-aprobacion-de-su-proyecto-de-inversion-bajo-el-rigi/; https://x.com/LuisCaputoAR/status/2083255389399744911</t>
   </si>
   <si>
     <t>Desarrollo de una mina de cobre, oro, plata y molibdeno en Catamarca, integrando el yacimiento Agua Rica con la infraestructura existente de Alumbrera, ubicada a unos 35 km. El esquema MARA contempla explotación, procesamiento y uso de instalaciones compartidas para producción destinada principalmente a exportación.</t>
@@ -1557,14 +1542,45 @@
   <si>
     <t>Zijin Mining (China)</t>
   </si>
+  <si>
+    <t>Ampliación Mega</t>
+  </si>
+  <si>
+    <t>Ampliación de un complejo industrial para incrementar la capacidad de producción de Líquidos del Gas Natural (LGN) en 1500 toneladas diarias.  El proyecto contempla nuevas instalaciones en la Planta de Separación de Loma La Lata, la ampliación de la capacidad de transporte del poliducto que atraviesa Neuquén, Río Negro, La Pampa y Buenos Aires, y la expansión de la Planta de Fraccionamiento ubicada en Bahía Blanca.</t>
+  </si>
+  <si>
+    <t>Compañía Mega SA Sucursal Dedicada</t>
+  </si>
+  <si>
+    <t>30-71932893-4</t>
+  </si>
+  <si>
+    <t>Construcción de plantas de tratamiento, plantas de separación de líquidos de gas natural, oleoductos, gasoductos y poliductos e instalaciones de almacenamiento</t>
+  </si>
+  <si>
+    <t>Neuquén; La Pampa; Río Negro; Buenos Aires</t>
+  </si>
+  <si>
+    <t>Res. 1381/2026</t>
+  </si>
+  <si>
+    <t>La resolución define expresamente al proyecto como una ampliación de un proyecto preexistente no adherido al RIGI: el Complejo Industrial MEGA, cuya capacidad actual de producción de LGN será incrementada mediante nuevas instalaciones e infraestructura.</t>
+  </si>
+  <si>
+    <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346397/20260826</t>
+  </si>
+  <si>
+    <t>Res. 1381/2026; Globaris; MECON</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -1720,7 +1736,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1804,6 +1820,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2545,6 +2567,27 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Proyectos"/>
+      <sheetName val="Diccionario"/>
+      <sheetName val="Variable_Anterior"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Lucas Ordoñez" id="{3AB22868-5EC9-474A-BBCF-88B6CF007C82}" userId="aece5baeefa9fdd6" providerId="Windows Live"/>
@@ -2813,13 +2856,13 @@
   <sheetData>
     <row r="1" spans="1:30" ht="32">
       <c r="A1" s="23" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D1" s="23" t="s">
         <v>0</v>
@@ -2828,10 +2871,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="H1" s="23" t="s">
         <v>2</v>
@@ -2840,7 +2883,7 @@
         <v>3</v>
       </c>
       <c r="J1" s="23" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="K1" s="23" t="s">
         <v>4</v>
@@ -2849,69 +2892,69 @@
         <v>5</v>
       </c>
       <c r="M1" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="N1" s="23" t="s">
+        <v>383</v>
+      </c>
+      <c r="O1" s="23" t="s">
+        <v>384</v>
+      </c>
+      <c r="P1" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q1" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="R1" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="S1" s="23" t="s">
         <v>388</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="T1" s="23" t="s">
         <v>389</v>
       </c>
-      <c r="O1" s="23" t="s">
-        <v>390</v>
-      </c>
-      <c r="P1" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="Q1" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="R1" s="23" t="s">
-        <v>393</v>
-      </c>
-      <c r="S1" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="T1" s="23" t="s">
-        <v>395</v>
-      </c>
       <c r="U1" s="23" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="V1" s="23" t="s">
         <v>6</v>
       </c>
       <c r="W1" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="X1" s="23" t="s">
         <v>156</v>
-      </c>
-      <c r="X1" s="23" t="s">
-        <v>157</v>
       </c>
       <c r="Y1" s="23" t="s">
         <v>7</v>
       </c>
       <c r="Z1" s="23" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AA1" s="23" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AB1" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AC1" s="23" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="AD1" s="23" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="102">
       <c r="A2" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D2" s="6">
         <v>1</v>
@@ -2923,22 +2966,22 @@
         <v>9</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K2" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>177</v>
       </c>
       <c r="M2" s="7">
         <v>550</v>
@@ -2981,16 +3024,16 @@
         <v>12</v>
       </c>
       <c r="Z2" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA2" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AB2" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AC2" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AD2" s="13"/>
     </row>
@@ -2999,10 +3042,10 @@
         <v>15</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D3" s="14">
         <v>2</v>
@@ -3014,19 +3057,19 @@
         <v>17</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H3" s="15" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L3" s="13" t="s">
         <v>20</v>
@@ -3072,28 +3115,28 @@
         <v>21</v>
       </c>
       <c r="Z3" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA3" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AB3" s="18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AC3" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AD3" s="13"/>
     </row>
     <row r="4" spans="1:30" ht="102">
       <c r="A4" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D4" s="6">
         <v>3</v>
@@ -3105,16 +3148,16 @@
         <v>23</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H4" s="15" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>24</v>
@@ -3163,16 +3206,16 @@
         <v>26</v>
       </c>
       <c r="Z4" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA4" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB4" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC4" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AD4" s="13"/>
     </row>
@@ -3181,10 +3224,10 @@
         <v>27</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D5" s="14">
         <v>4</v>
@@ -3196,7 +3239,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H5" s="15" t="s">
         <v>10</v>
@@ -3254,16 +3297,16 @@
         <v>33</v>
       </c>
       <c r="Z5" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA5" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AB5" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AC5" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AD5" s="13"/>
     </row>
@@ -3272,28 +3315,28 @@
         <v>34</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D6" s="6">
         <v>5</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5" t="s">
@@ -3344,16 +3387,16 @@
         <v>37</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA6" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AB6" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AC6" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AD6" s="13"/>
     </row>
@@ -3362,10 +3405,10 @@
         <v>38</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D7" s="14">
         <v>6</v>
@@ -3374,19 +3417,19 @@
         <v>39</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>40</v>
@@ -3435,16 +3478,16 @@
         <v>41</v>
       </c>
       <c r="Z7" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB7" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AC7" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AD7" s="13"/>
     </row>
@@ -3453,10 +3496,10 @@
         <v>42</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D8" s="6">
         <v>7</v>
@@ -3468,7 +3511,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>45</v>
@@ -3477,7 +3520,7 @@
         <v>45</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K8" s="13" t="s">
         <v>31</v>
@@ -3526,16 +3569,16 @@
         <v>46</v>
       </c>
       <c r="Z8" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA8" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AB8" s="20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AC8" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AD8" s="13"/>
     </row>
@@ -3544,10 +3587,10 @@
         <v>47</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D9" s="14">
         <v>8</v>
@@ -3559,7 +3602,7 @@
         <v>49</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>18</v>
@@ -3568,7 +3611,7 @@
         <v>50</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>36</v>
@@ -3617,28 +3660,28 @@
         <v>51</v>
       </c>
       <c r="Z9" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB9" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC9" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AD9" s="13"/>
     </row>
     <row r="10" spans="1:30" ht="119">
       <c r="A10" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D10" s="6">
         <v>9</v>
@@ -3650,7 +3693,7 @@
         <v>53</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>18</v>
@@ -3659,7 +3702,7 @@
         <v>54</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K10" s="13" t="s">
         <v>19</v>
@@ -3708,28 +3751,28 @@
         <v>55</v>
       </c>
       <c r="Z10" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA10" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB10" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC10" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AD10" s="13"/>
     </row>
     <row r="11" spans="1:30" ht="255">
       <c r="A11" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D11" s="14">
         <v>10</v>
@@ -3738,10 +3781,10 @@
         <v>52</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>18</v>
@@ -3750,7 +3793,7 @@
         <v>54</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>56</v>
@@ -3799,28 +3842,28 @@
         <v>57</v>
       </c>
       <c r="Z11" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AB11" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AC11" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AD11" s="13"/>
     </row>
     <row r="12" spans="1:30" ht="119">
       <c r="A12" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D12" s="6">
         <v>11</v>
@@ -3832,7 +3875,7 @@
         <v>59</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>60</v>
@@ -3841,7 +3884,7 @@
         <v>61</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>62</v>
@@ -3890,28 +3933,28 @@
         <v>63</v>
       </c>
       <c r="Z12" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA12" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AB12" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AC12" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AD12" s="13"/>
     </row>
     <row r="13" spans="1:30" ht="372">
       <c r="A13" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D13" s="14">
         <v>12</v>
@@ -3923,16 +3966,16 @@
         <v>65</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>40</v>
@@ -3981,28 +4024,28 @@
         <v>66</v>
       </c>
       <c r="Z13" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA13" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB13" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AC13" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AD13" s="13"/>
     </row>
     <row r="14" spans="1:30" ht="136">
       <c r="A14" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D14" s="6">
         <v>13</v>
@@ -4011,19 +4054,19 @@
         <v>67</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>24</v>
@@ -4072,16 +4115,16 @@
         <v>68</v>
       </c>
       <c r="Z14" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA14" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AB14" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC14" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AD14" s="13"/>
     </row>
@@ -4090,17 +4133,17 @@
         <v>76</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="14">
         <v>14</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="15" t="s">
@@ -4130,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T15" s="13"/>
       <c r="U15" s="10"/>
@@ -4144,10 +4187,10 @@
       <c r="AA15" s="13"/>
       <c r="AB15" s="13"/>
       <c r="AC15" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="AD15" s="13" t="s">
         <v>300</v>
-      </c>
-      <c r="AD15" s="13" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="409.6">
@@ -4155,7 +4198,7 @@
         <v>77</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="6">
@@ -4195,7 +4238,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="10"/>
@@ -4209,10 +4252,10 @@
       <c r="AA16" s="5"/>
       <c r="AB16" s="5"/>
       <c r="AC16" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="AD16" s="13" t="s">
         <v>303</v>
-      </c>
-      <c r="AD16" s="13" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="409.6">
@@ -4220,24 +4263,24 @@
         <v>81</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="14">
         <v>16</v>
       </c>
       <c r="E17" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="F17" s="13" t="s">
         <v>306</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>307</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J17" s="13"/>
       <c r="K17" s="13" t="s">
@@ -4260,7 +4303,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T17" s="13"/>
       <c r="U17" s="10"/>
@@ -4274,21 +4317,21 @@
       <c r="AA17" s="13"/>
       <c r="AB17" s="13"/>
       <c r="AC17" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="AD17" s="13" t="s">
         <v>309</v>
-      </c>
-      <c r="AD17" s="13" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="119">
       <c r="A18" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D18" s="6">
         <v>17</v>
@@ -4297,10 +4340,10 @@
         <v>83</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>18</v>
@@ -4309,7 +4352,7 @@
         <v>54</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>84</v>
@@ -4355,19 +4398,19 @@
         <v>46177</v>
       </c>
       <c r="Y18" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z18" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA18" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="AB18" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="Z18" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA18" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="AB18" s="12" t="s">
-        <v>203</v>
-      </c>
       <c r="AC18" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AD18" s="13"/>
     </row>
@@ -4376,7 +4419,7 @@
         <v>85</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="14">
@@ -4390,14 +4433,14 @@
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>11</v>
@@ -4416,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T19" s="13"/>
       <c r="U19" s="10"/>
@@ -4430,10 +4473,10 @@
       <c r="AA19" s="13"/>
       <c r="AB19" s="13"/>
       <c r="AC19" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD19" s="13" t="s">
         <v>313</v>
-      </c>
-      <c r="AD19" s="13" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="409.6">
@@ -4441,7 +4484,7 @@
         <v>88</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="6">
@@ -4481,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T20" s="5"/>
       <c r="U20" s="10"/>
@@ -4495,10 +4538,10 @@
       <c r="AA20" s="5"/>
       <c r="AB20" s="5"/>
       <c r="AC20" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="AD20" s="13" t="s">
         <v>316</v>
-      </c>
-      <c r="AD20" s="13" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="409.6">
@@ -4506,7 +4549,7 @@
         <v>91</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="14">
@@ -4516,14 +4559,14 @@
         <v>92</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J21" s="13"/>
       <c r="K21" s="13" t="s">
@@ -4546,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T21" s="13"/>
       <c r="U21" s="10"/>
@@ -4560,10 +4603,10 @@
       <c r="AA21" s="13"/>
       <c r="AB21" s="13"/>
       <c r="AC21" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="AD21" s="13" t="s">
         <v>319</v>
-      </c>
-      <c r="AD21" s="13" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="409.6">
@@ -4571,17 +4614,17 @@
         <v>93</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="6">
         <v>21</v>
       </c>
       <c r="E22" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>322</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>323</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="7" t="s">
@@ -4592,10 +4635,10 @@
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="L22" s="5" t="s">
         <v>324</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>325</v>
       </c>
       <c r="M22" s="7">
         <v>200</v>
@@ -4611,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="10"/>
@@ -4625,10 +4668,10 @@
       <c r="AA22" s="5"/>
       <c r="AB22" s="5"/>
       <c r="AC22" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="AD22" s="13" t="s">
         <v>326</v>
-      </c>
-      <c r="AD22" s="13" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="409.6">
@@ -4636,7 +4679,7 @@
         <v>95</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="14">
@@ -4676,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T23" s="13"/>
       <c r="U23" s="10"/>
@@ -4690,10 +4733,10 @@
       <c r="AA23" s="13"/>
       <c r="AB23" s="13"/>
       <c r="AC23" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="AD23" s="13" t="s">
         <v>329</v>
-      </c>
-      <c r="AD23" s="13" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="409.6">
@@ -4701,7 +4744,7 @@
         <v>98</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="6">
@@ -4715,10 +4758,10 @@
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
@@ -4741,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T24" s="5"/>
       <c r="U24" s="10"/>
@@ -4755,10 +4798,10 @@
       <c r="AA24" s="5"/>
       <c r="AB24" s="5"/>
       <c r="AC24" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="AD24" s="13" t="s">
         <v>332</v>
-      </c>
-      <c r="AD24" s="13" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="409.6">
@@ -4766,14 +4809,14 @@
         <v>101</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="14">
         <v>24</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>102</v>
@@ -4806,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T25" s="13"/>
       <c r="U25" s="10"/>
@@ -4820,21 +4863,21 @@
       <c r="AA25" s="13"/>
       <c r="AB25" s="13"/>
       <c r="AC25" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="AD25" s="13" t="s">
         <v>336</v>
-      </c>
-      <c r="AD25" s="13" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="289">
       <c r="A26" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D26" s="6">
         <v>25</v>
@@ -4846,16 +4889,16 @@
         <v>104</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>82</v>
@@ -4901,31 +4944,31 @@
         <v>46224</v>
       </c>
       <c r="Y26" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Z26" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA26" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AB26" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AC26" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AD26" s="13"/>
     </row>
     <row r="27" spans="1:30" ht="255">
       <c r="A27" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D27" s="14">
         <v>26</v>
@@ -4934,10 +4977,10 @@
         <v>105</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>18</v>
@@ -4946,10 +4989,10 @@
         <v>54</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K27" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L27" s="13" t="s">
         <v>20</v>
@@ -4992,19 +5035,19 @@
         <v>46234</v>
       </c>
       <c r="Y27" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Z27" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AB27" s="21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AC27" s="13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AD27" s="13"/>
     </row>
@@ -5013,7 +5056,7 @@
         <v>106</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="6">
@@ -5053,7 +5096,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="10"/>
@@ -5067,31 +5110,31 @@
       <c r="AA28" s="5"/>
       <c r="AB28" s="5"/>
       <c r="AC28" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD28" s="13" t="s">
         <v>339</v>
-      </c>
-      <c r="AD28" s="13" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="289">
       <c r="A29" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="14">
         <v>28</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>108</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>18</v>
@@ -5100,7 +5143,7 @@
         <v>54</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K29" s="13" t="s">
         <v>56</v>
@@ -5146,19 +5189,19 @@
         <v>46232</v>
       </c>
       <c r="Y29" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Z29" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA29" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AB29" s="18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AC29" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AD29" s="13"/>
     </row>
@@ -5167,10 +5210,10 @@
         <v>109</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D30" s="6">
         <v>29</v>
@@ -5182,16 +5225,16 @@
         <v>111</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>24</v>
@@ -5238,19 +5281,19 @@
         <v>46233</v>
       </c>
       <c r="Y30" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z30" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA30" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB30" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="Z30" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA30" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="AB30" s="12" t="s">
+      <c r="AC30" s="5" t="s">
         <v>279</v>
-      </c>
-      <c r="AC30" s="5" t="s">
-        <v>280</v>
       </c>
       <c r="AD30" s="13"/>
     </row>
@@ -5259,24 +5302,24 @@
         <v>112</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="14">
         <v>30</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5" t="s">
@@ -5299,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T31" s="5"/>
       <c r="U31" s="10"/>
@@ -5313,21 +5356,21 @@
       <c r="AA31" s="5"/>
       <c r="AB31" s="5"/>
       <c r="AC31" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="AD31" s="13" t="s">
         <v>343</v>
-      </c>
-      <c r="AD31" s="13" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="119">
       <c r="A32" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="D32" s="6">
         <v>31</v>
@@ -5339,7 +5382,7 @@
         <v>74</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>18</v>
@@ -5348,7 +5391,7 @@
         <v>50</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>24</v>
@@ -5397,16 +5440,16 @@
         <v>75</v>
       </c>
       <c r="Z32" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AA32" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AB32" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AC32" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD32" s="13"/>
     </row>
@@ -5467,81 +5510,107 @@
       <c r="AA33" s="13"/>
       <c r="AB33" s="13"/>
       <c r="AC33" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AD33" s="13"/>
     </row>
-    <row r="34" spans="1:30" ht="409.6">
-      <c r="A34" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="6">
+    <row r="34" spans="1:30" ht="136">
+      <c r="A34" s="13" t="s">
+        <v>473</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="14">
         <v>33</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5" t="s">
-        <v>348</v>
+      <c r="E34" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>478</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="M34" s="7">
-        <v>360</v>
-      </c>
-      <c r="N34" s="7">
-        <v>360</v>
-      </c>
-      <c r="O34" s="7"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="9">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
-      <c r="S34" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="T34" s="5"/>
-      <c r="U34" s="10"/>
-      <c r="V34" s="11">
+        <v>324</v>
+      </c>
+      <c r="M34" s="29">
+        <v>365.39866899999998</v>
+      </c>
+      <c r="N34" s="29">
+        <v>365.39866899999998</v>
+      </c>
+      <c r="O34" s="15">
+        <v>359.16436099999999</v>
+      </c>
+      <c r="P34" s="16">
+        <v>121.613889</v>
+      </c>
+      <c r="Q34" s="16">
+        <v>152.70910599999999</v>
+      </c>
+      <c r="R34" s="16">
+        <f>SUM([1]!Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
+        <v>274.32299499999999</v>
+      </c>
+      <c r="S34" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="T34" s="15">
+        <v>792</v>
+      </c>
+      <c r="U34" s="30">
+        <v>46661</v>
+      </c>
+      <c r="V34" s="17">
         <v>46099</v>
       </c>
-      <c r="W34" s="11"/>
-      <c r="X34" s="11"/>
-      <c r="Y34" s="5"/>
-      <c r="Z34" s="5"/>
-      <c r="AA34" s="5"/>
-      <c r="AB34" s="5"/>
-      <c r="AC34" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="AD34" s="13" t="s">
-        <v>350</v>
-      </c>
+      <c r="W34" s="17">
+        <v>46231</v>
+      </c>
+      <c r="X34" s="17">
+        <v>46260</v>
+      </c>
+      <c r="Y34" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="Z34" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA34" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="AB34" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="AC34" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="AD34" s="13"/>
     </row>
     <row r="35" spans="1:30" ht="409.6">
       <c r="A35" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="14">
@@ -5551,7 +5620,7 @@
         <v>89</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G35" s="13"/>
       <c r="H35" s="15" t="s">
@@ -5581,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T35" s="13"/>
       <c r="U35" s="10"/>
@@ -5595,18 +5664,18 @@
       <c r="AA35" s="13"/>
       <c r="AB35" s="13"/>
       <c r="AC35" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="AD35" s="13" t="s">
         <v>316</v>
-      </c>
-      <c r="AD35" s="13" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="409.6">
       <c r="A36" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="6">
@@ -5616,14 +5685,14 @@
         <v>103</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5" t="s">
@@ -5646,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T36" s="5"/>
       <c r="U36" s="10"/>
@@ -5660,45 +5729,45 @@
       <c r="AA36" s="5"/>
       <c r="AB36" s="5"/>
       <c r="AC36" s="5" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AD36" s="13" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="204">
       <c r="A37" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D37" s="14">
         <v>36</v>
       </c>
       <c r="E37" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="F37" s="13" t="s">
-        <v>123</v>
-      </c>
       <c r="G37" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="K37" s="13" t="s">
         <v>242</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="J37" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="K37" s="13" t="s">
-        <v>243</v>
       </c>
       <c r="L37" s="13" t="s">
         <v>11</v>
@@ -5741,19 +5810,19 @@
         <v>46198</v>
       </c>
       <c r="Y37" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z37" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA37" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="AB37" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="Z37" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA37" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="AB37" s="21" t="s">
+      <c r="AC37" s="13" t="s">
         <v>245</v>
-      </c>
-      <c r="AC37" s="13" t="s">
-        <v>246</v>
       </c>
       <c r="AD37" s="13"/>
     </row>
@@ -5762,10 +5831,10 @@
         <v>69</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D38" s="6">
         <v>37</v>
@@ -5777,7 +5846,7 @@
         <v>71</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>18</v>
@@ -5786,7 +5855,7 @@
         <v>54</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K38" s="13" t="s">
         <v>56</v>
@@ -5835,35 +5904,35 @@
         <v>72</v>
       </c>
       <c r="Z38" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA38" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AB38" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AC38" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AD38" s="13"/>
     </row>
     <row r="39" spans="1:30" ht="409.6">
       <c r="A39" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="14">
         <v>38</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="7" t="s">
@@ -5893,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T39" s="5"/>
       <c r="U39" s="10"/>
@@ -5907,35 +5976,35 @@
       <c r="AA39" s="5"/>
       <c r="AB39" s="5"/>
       <c r="AC39" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AD39" s="13" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="409.6">
       <c r="A40" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="6">
         <v>39</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="G40" s="13"/>
       <c r="H40" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J40" s="13"/>
       <c r="K40" s="13" t="s">
@@ -5958,7 +6027,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T40" s="13"/>
       <c r="U40" s="10"/>
@@ -5972,35 +6041,35 @@
       <c r="AA40" s="13"/>
       <c r="AB40" s="13"/>
       <c r="AC40" s="13" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="AD40" s="13" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="409.6">
       <c r="A41" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="14">
         <v>40</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="G41" s="13"/>
       <c r="H41" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J41" s="13"/>
       <c r="K41" s="13" t="s">
@@ -6023,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T41" s="17"/>
       <c r="U41" s="10"/>
@@ -6037,39 +6106,39 @@
       <c r="AA41" s="13"/>
       <c r="AB41" s="13"/>
       <c r="AC41" s="13" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AD41" s="18" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="409.6">
       <c r="A42" s="13" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="14">
         <v>41</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="G42" s="13"/>
       <c r="H42" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J42" s="13"/>
       <c r="K42" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L42" s="13" t="s">
         <v>11</v>
@@ -6086,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="T42" s="15"/>
       <c r="U42" s="10"/>
@@ -6100,10 +6169,10 @@
       <c r="AA42" s="13"/>
       <c r="AB42" s="13"/>
       <c r="AC42" s="13" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AD42" s="13" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="43" spans="1:30">
@@ -6188,22 +6257,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="24" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16">
@@ -6211,19 +6280,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16">
@@ -6231,19 +6300,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16">
@@ -6251,19 +6320,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16">
@@ -6274,16 +6343,16 @@
         <v>0</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16">
@@ -6294,16 +6363,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16">
@@ -6311,19 +6380,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16">
@@ -6331,19 +6400,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16">
@@ -6354,16 +6423,16 @@
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16">
@@ -6374,16 +6443,16 @@
         <v>3</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16">
@@ -6391,19 +6460,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16">
@@ -6414,16 +6483,16 @@
         <v>4</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16">
@@ -6434,16 +6503,16 @@
         <v>5</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16">
@@ -6451,19 +6520,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16">
@@ -6471,19 +6540,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16">
@@ -6491,19 +6560,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="D16" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="F16" s="23" t="s">
         <v>435</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>436</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16">
@@ -6511,19 +6580,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16">
@@ -6531,19 +6600,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32">
@@ -6551,19 +6620,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16">
@@ -6571,19 +6640,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16">
@@ -6591,19 +6660,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16">
@@ -6611,19 +6680,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16">
@@ -6634,16 +6703,16 @@
         <v>6</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16">
@@ -6651,19 +6720,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16">
@@ -6671,19 +6740,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="16">
@@ -6694,16 +6763,16 @@
         <v>7</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="32">
@@ -6711,19 +6780,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16">
@@ -6731,19 +6800,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16">
@@ -6751,19 +6820,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16">
@@ -6771,19 +6840,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16">
@@ -6791,19 +6860,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -6818,13 +6887,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60">
       <c r="A1" s="26" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6832,10 +6901,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45">
@@ -6843,10 +6912,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="105">
@@ -6854,10 +6923,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6887,10 +6956,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6898,10 +6967,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6931,10 +7000,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6964,10 +7033,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60">
@@ -6975,10 +7044,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="60">
@@ -6986,10 +7055,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="90">
@@ -6997,10 +7066,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90">
@@ -7008,10 +7077,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="90">
@@ -7019,10 +7088,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="45">
@@ -7030,10 +7099,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="60">
@@ -7041,10 +7110,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="75">
@@ -7052,10 +7121,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30">
@@ -7074,10 +7143,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30">
@@ -7085,10 +7154,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30">
@@ -7107,10 +7176,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="60">
@@ -7118,10 +7187,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7129,10 +7198,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7140,10 +7209,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="30">
@@ -7151,10 +7220,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/rigi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6768F59F-1435-D647-9AC9-C083F6591518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E72C1D-546E-0546-819C-35C80583B28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36640" yWindow="600" windowWidth="32160" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="487">
   <si>
     <t>id_proyecto</t>
   </si>
@@ -460,9 +460,6 @@
     <t>Minera Agua Rica LLC Sucursal Argentina</t>
   </si>
   <si>
-    <t>Fértil Pampa</t>
-  </si>
-  <si>
     <t>Fértil Pampa S.A.U.</t>
   </si>
   <si>
@@ -1139,18 +1136,6 @@
   </si>
   <si>
     <t>Desarrollo de una mina de cobre, oro, plata y molibdeno en Catamarca, integrando el yacimiento Agua Rica con la infraestructura existente de Alumbrera, ubicada a unos 35 km. El esquema MARA contempla explotación, procesamiento y uso de instalaciones compartidas para producción destinada principalmente a exportación.</t>
-  </si>
-  <si>
-    <t>Construcción de un complejo industrial de amoníaco y urea granulada en Bahía Blanca, provincia de Buenos Aires, a cargo de Fértil Pampa. La planta tendrá dos trenes de urea, instalaciones auxiliares, almacenamiento y logística portuaria, con capacidad prevista de 2,1 millones de toneladas anuales.</t>
-  </si>
-  <si>
-    <t>Petroquímica / Fertilizantes</t>
-  </si>
-  <si>
-    <t>Globaris; Pampa Energía; International Finance Corporation; El Cronista; La Nación; Luis Caputo; auditoría 2026-08-08</t>
-  </si>
-  <si>
-    <t>https://ri.pampa.com/en/press-release/pampa-energia-announces-its-entry-into-the-fertilizer-business-with-the-construction-of-latin-americas-largest-urea-plant/; https://disclosures.ifc.org/project-detail/ED/52106/fer-il-p; https://www.cronista.com/negocios/fertil-pampa-se-presenta-al-rigi-con-una-inversion-de-us-2400-millones-para-producir-fertilizantes/; https://www.lanacion.com.ar/economia/campo/invertiria-us2400-millones-una-empresa-de-marcelo-mindlin-pidio-ingresar-al-rigi-para-producir-nid23042026/</t>
   </si>
   <si>
     <t>Desarrollo integrado de litio en los proyectos Jama y Solaroz, en la Puna de Jujuy, con una planta prevista en el Salar de Jama. La iniciativa contempla extracción de salmuera y producción de compuestos de litio, con una capacidad informada de aproximadamente 22.000 toneladas anuales.</t>
@@ -1572,6 +1557,33 @@
   <si>
     <t>Res. 1381/2026; Globaris; MECON</t>
   </si>
+  <si>
+    <t>Fertilizantes</t>
+  </si>
+  <si>
+    <t>Construcción, operación y gerenciamiento de dos (2) plantas de producción de urea, cada una con capacidad de tres mil toneladas (3.000 t) por día, con sus correspondientes unidades de granulación, y una planta de amoníaco con capacidad de tres mil cuatrocientas cincuenta toneladas (3.450 t) por día, utilizando como insumo principal el gas natural de Vaca Muerta, a desarrollarse en el Puerto de Ingeniero White, partido de Bahía Blanca, provincia de Buenos Aires.</t>
+  </si>
+  <si>
+    <t>30-71875855-2</t>
+  </si>
+  <si>
+    <t>Petroquímica y Fertilizantes</t>
+  </si>
+  <si>
+    <t>Puerto de Ingeniero White, Bahía Blanca</t>
+  </si>
+  <si>
+    <t>Res. 1468/2026</t>
+  </si>
+  <si>
+    <t>Se identifican signos fuertes de preexistencia. El proyecto “Fertilizantes” de Fértil Pampa SAU fue aprobado bajo RIGI por la Resolución 1468/2026, publicada el 07/09/2026, pero existía públicamente antes de esa fecha. La sociedad Fértil Pampa SAU fue constituida en octubre de 2024 con objeto específico de construir y operar una planta de amoníaco, urea y otros fertilizantes. Antes de la aprobación RIGI ya existían divulgaciones financieras y ambientales ante BID Invest e IFC, solicitud RIGI presentada el 21/04/2026, memorándum de entendimiento con el Municipio de Bahía Blanca, decisión final de inversión de Pampa Energía del 17/07/2026, contrato EPC con Tecnimont–SACDE y trámites de participación pública ambiental. Por lo tanto, se clasifica como proyecto preexistente al anuncio/aprobación oficial, aunque corresponde a una inversión greenfield y no a una ampliación de una planta ya operativa.</t>
+  </si>
+  <si>
+    <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/346966/20260907</t>
+  </si>
+  <si>
+    <t>Res.1468/2026; MECON</t>
+  </si>
 </sst>
 </file>
 
@@ -1582,7 +1594,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1668,6 +1680,13 @@
       <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1736,7 +1755,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1824,6 +1843,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2856,13 +2881,13 @@
   <sheetData>
     <row r="1" spans="1:30" ht="32">
       <c r="A1" s="23" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D1" s="23" t="s">
         <v>0</v>
@@ -2871,10 +2896,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="H1" s="23" t="s">
         <v>2</v>
@@ -2883,7 +2908,7 @@
         <v>3</v>
       </c>
       <c r="J1" s="23" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="K1" s="23" t="s">
         <v>4</v>
@@ -2892,69 +2917,69 @@
         <v>5</v>
       </c>
       <c r="M1" s="23" t="s">
+        <v>377</v>
+      </c>
+      <c r="N1" s="23" t="s">
+        <v>378</v>
+      </c>
+      <c r="O1" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="P1" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q1" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="R1" s="23" t="s">
         <v>382</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="S1" s="23" t="s">
         <v>383</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="T1" s="23" t="s">
         <v>384</v>
       </c>
-      <c r="P1" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q1" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="R1" s="23" t="s">
-        <v>387</v>
-      </c>
-      <c r="S1" s="23" t="s">
-        <v>388</v>
-      </c>
-      <c r="T1" s="23" t="s">
-        <v>389</v>
-      </c>
       <c r="U1" s="23" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="V1" s="23" t="s">
         <v>6</v>
       </c>
       <c r="W1" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="X1" s="23" t="s">
         <v>155</v>
-      </c>
-      <c r="X1" s="23" t="s">
-        <v>156</v>
       </c>
       <c r="Y1" s="23" t="s">
         <v>7</v>
       </c>
       <c r="Z1" s="23" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AA1" s="23" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AB1" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AC1" s="23" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AD1" s="23" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="102">
       <c r="A2" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D2" s="6">
         <v>1</v>
@@ -2966,22 +2991,22 @@
         <v>9</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K2" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>176</v>
       </c>
       <c r="M2" s="7">
         <v>550</v>
@@ -3024,16 +3049,16 @@
         <v>12</v>
       </c>
       <c r="Z2" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA2" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB2" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AC2" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AD2" s="13"/>
     </row>
@@ -3042,10 +3067,10 @@
         <v>15</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D3" s="14">
         <v>2</v>
@@ -3057,19 +3082,19 @@
         <v>17</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H3" s="15" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L3" s="13" t="s">
         <v>20</v>
@@ -3115,28 +3140,28 @@
         <v>21</v>
       </c>
       <c r="Z3" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA3" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AB3" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AC3" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AD3" s="13"/>
     </row>
     <row r="4" spans="1:30" ht="102">
       <c r="A4" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D4" s="6">
         <v>3</v>
@@ -3148,16 +3173,16 @@
         <v>23</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H4" s="15" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K4" s="13" t="s">
         <v>24</v>
@@ -3206,16 +3231,16 @@
         <v>26</v>
       </c>
       <c r="Z4" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA4" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB4" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AC4" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AD4" s="13"/>
     </row>
@@ -3224,10 +3249,10 @@
         <v>27</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D5" s="14">
         <v>4</v>
@@ -3239,7 +3264,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H5" s="15" t="s">
         <v>10</v>
@@ -3297,16 +3322,16 @@
         <v>33</v>
       </c>
       <c r="Z5" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA5" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AB5" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AC5" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AD5" s="13"/>
     </row>
@@ -3315,28 +3340,28 @@
         <v>34</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D6" s="6">
         <v>5</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5" t="s">
@@ -3387,16 +3412,16 @@
         <v>37</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA6" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AB6" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AC6" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AD6" s="13"/>
     </row>
@@ -3405,10 +3430,10 @@
         <v>38</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D7" s="14">
         <v>6</v>
@@ -3417,19 +3442,19 @@
         <v>39</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>147</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>40</v>
@@ -3478,16 +3503,16 @@
         <v>41</v>
       </c>
       <c r="Z7" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA7" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB7" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AC7" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AD7" s="13"/>
     </row>
@@ -3496,10 +3521,10 @@
         <v>42</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D8" s="6">
         <v>7</v>
@@ -3511,7 +3536,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>45</v>
@@ -3520,7 +3545,7 @@
         <v>45</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K8" s="13" t="s">
         <v>31</v>
@@ -3569,16 +3594,16 @@
         <v>46</v>
       </c>
       <c r="Z8" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA8" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AB8" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AC8" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AD8" s="13"/>
     </row>
@@ -3587,10 +3612,10 @@
         <v>47</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D9" s="14">
         <v>8</v>
@@ -3602,7 +3627,7 @@
         <v>49</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>18</v>
@@ -3611,7 +3636,7 @@
         <v>50</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>36</v>
@@ -3660,28 +3685,28 @@
         <v>51</v>
       </c>
       <c r="Z9" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AB9" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC9" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AD9" s="13"/>
     </row>
     <row r="10" spans="1:30" ht="119">
       <c r="A10" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D10" s="6">
         <v>9</v>
@@ -3693,7 +3718,7 @@
         <v>53</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>18</v>
@@ -3702,7 +3727,7 @@
         <v>54</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K10" s="13" t="s">
         <v>19</v>
@@ -3751,28 +3776,28 @@
         <v>55</v>
       </c>
       <c r="Z10" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA10" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AB10" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AC10" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD10" s="13"/>
     </row>
     <row r="11" spans="1:30" ht="255">
       <c r="A11" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D11" s="14">
         <v>10</v>
@@ -3781,10 +3806,10 @@
         <v>52</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>193</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>18</v>
@@ -3793,7 +3818,7 @@
         <v>54</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>56</v>
@@ -3842,28 +3867,28 @@
         <v>57</v>
       </c>
       <c r="Z11" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AB11" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AC11" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AD11" s="13"/>
     </row>
     <row r="12" spans="1:30" ht="119">
       <c r="A12" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" s="6">
         <v>11</v>
@@ -3875,7 +3900,7 @@
         <v>59</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>60</v>
@@ -3884,7 +3909,7 @@
         <v>61</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>62</v>
@@ -3933,28 +3958,28 @@
         <v>63</v>
       </c>
       <c r="Z12" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA12" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AB12" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AC12" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AD12" s="13"/>
     </row>
     <row r="13" spans="1:30" ht="372">
       <c r="A13" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D13" s="14">
         <v>12</v>
@@ -3966,16 +3991,16 @@
         <v>65</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>40</v>
@@ -4024,28 +4049,28 @@
         <v>66</v>
       </c>
       <c r="Z13" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA13" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB13" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AC13" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AD13" s="13"/>
     </row>
     <row r="14" spans="1:30" ht="136">
       <c r="A14" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D14" s="6">
         <v>13</v>
@@ -4054,19 +4079,19 @@
         <v>67</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>24</v>
@@ -4115,16 +4140,16 @@
         <v>68</v>
       </c>
       <c r="Z14" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA14" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AB14" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AC14" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AD14" s="13"/>
     </row>
@@ -4133,17 +4158,17 @@
         <v>76</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C15" s="13"/>
       <c r="D15" s="14">
         <v>14</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="15" t="s">
@@ -4173,7 +4198,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T15" s="13"/>
       <c r="U15" s="10"/>
@@ -4187,10 +4212,10 @@
       <c r="AA15" s="13"/>
       <c r="AB15" s="13"/>
       <c r="AC15" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD15" s="13" t="s">
         <v>299</v>
-      </c>
-      <c r="AD15" s="13" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="409.6">
@@ -4198,7 +4223,7 @@
         <v>77</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="6">
@@ -4238,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T16" s="5"/>
       <c r="U16" s="10"/>
@@ -4252,10 +4277,10 @@
       <c r="AA16" s="5"/>
       <c r="AB16" s="5"/>
       <c r="AC16" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AD16" s="13" t="s">
         <v>302</v>
-      </c>
-      <c r="AD16" s="13" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="409.6">
@@ -4263,24 +4288,24 @@
         <v>81</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="14">
         <v>16</v>
       </c>
       <c r="E17" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="F17" s="13" t="s">
         <v>305</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>306</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J17" s="13"/>
       <c r="K17" s="13" t="s">
@@ -4303,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T17" s="13"/>
       <c r="U17" s="10"/>
@@ -4317,21 +4342,21 @@
       <c r="AA17" s="13"/>
       <c r="AB17" s="13"/>
       <c r="AC17" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="AD17" s="13" t="s">
         <v>308</v>
-      </c>
-      <c r="AD17" s="13" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="119">
       <c r="A18" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D18" s="6">
         <v>17</v>
@@ -4340,10 +4365,10 @@
         <v>83</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>18</v>
@@ -4352,7 +4377,7 @@
         <v>54</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>84</v>
@@ -4398,19 +4423,19 @@
         <v>46177</v>
       </c>
       <c r="Y18" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="Z18" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA18" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB18" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="Z18" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AA18" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="AB18" s="12" t="s">
-        <v>202</v>
-      </c>
       <c r="AC18" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AD18" s="13"/>
     </row>
@@ -4419,7 +4444,7 @@
         <v>85</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="14">
@@ -4433,14 +4458,14 @@
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>11</v>
@@ -4459,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T19" s="13"/>
       <c r="U19" s="10"/>
@@ -4473,10 +4498,10 @@
       <c r="AA19" s="13"/>
       <c r="AB19" s="13"/>
       <c r="AC19" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="AD19" s="13" t="s">
         <v>312</v>
-      </c>
-      <c r="AD19" s="13" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="409.6">
@@ -4484,7 +4509,7 @@
         <v>88</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="6">
@@ -4524,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T20" s="5"/>
       <c r="U20" s="10"/>
@@ -4538,10 +4563,10 @@
       <c r="AA20" s="5"/>
       <c r="AB20" s="5"/>
       <c r="AC20" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="AD20" s="13" t="s">
         <v>315</v>
-      </c>
-      <c r="AD20" s="13" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="409.6">
@@ -4549,7 +4574,7 @@
         <v>91</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="14">
@@ -4559,14 +4584,14 @@
         <v>92</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J21" s="13"/>
       <c r="K21" s="13" t="s">
@@ -4589,7 +4614,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T21" s="13"/>
       <c r="U21" s="10"/>
@@ -4603,10 +4628,10 @@
       <c r="AA21" s="13"/>
       <c r="AB21" s="13"/>
       <c r="AC21" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="AD21" s="13" t="s">
         <v>318</v>
-      </c>
-      <c r="AD21" s="13" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="409.6">
@@ -4614,17 +4639,17 @@
         <v>93</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="6">
         <v>21</v>
       </c>
       <c r="E22" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>321</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>322</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="7" t="s">
@@ -4635,10 +4660,10 @@
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="L22" s="5" t="s">
         <v>323</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>324</v>
       </c>
       <c r="M22" s="7">
         <v>200</v>
@@ -4654,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="10"/>
@@ -4668,10 +4693,10 @@
       <c r="AA22" s="5"/>
       <c r="AB22" s="5"/>
       <c r="AC22" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD22" s="13" t="s">
         <v>325</v>
-      </c>
-      <c r="AD22" s="13" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="409.6">
@@ -4679,7 +4704,7 @@
         <v>95</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="14">
@@ -4719,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T23" s="13"/>
       <c r="U23" s="10"/>
@@ -4733,10 +4758,10 @@
       <c r="AA23" s="13"/>
       <c r="AB23" s="13"/>
       <c r="AC23" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="AD23" s="13" t="s">
         <v>328</v>
-      </c>
-      <c r="AD23" s="13" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="409.6">
@@ -4744,7 +4769,7 @@
         <v>98</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="6">
@@ -4758,10 +4783,10 @@
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
@@ -4784,7 +4809,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T24" s="5"/>
       <c r="U24" s="10"/>
@@ -4798,10 +4823,10 @@
       <c r="AA24" s="5"/>
       <c r="AB24" s="5"/>
       <c r="AC24" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="AD24" s="13" t="s">
         <v>331</v>
-      </c>
-      <c r="AD24" s="13" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="409.6">
@@ -4809,14 +4834,14 @@
         <v>101</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="14">
         <v>24</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F25" s="13" t="s">
         <v>102</v>
@@ -4849,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T25" s="13"/>
       <c r="U25" s="10"/>
@@ -4863,21 +4888,21 @@
       <c r="AA25" s="13"/>
       <c r="AB25" s="13"/>
       <c r="AC25" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="AD25" s="13" t="s">
         <v>335</v>
-      </c>
-      <c r="AD25" s="13" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="289">
       <c r="A26" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D26" s="6">
         <v>25</v>
@@ -4889,16 +4914,16 @@
         <v>104</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>82</v>
@@ -4944,31 +4969,31 @@
         <v>46224</v>
       </c>
       <c r="Y26" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Z26" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA26" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AB26" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AC26" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AD26" s="13"/>
     </row>
     <row r="27" spans="1:30" ht="255">
       <c r="A27" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D27" s="14">
         <v>26</v>
@@ -4977,10 +5002,10 @@
         <v>105</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>18</v>
@@ -4989,10 +5014,10 @@
         <v>54</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K27" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L27" s="13" t="s">
         <v>20</v>
@@ -5035,19 +5060,19 @@
         <v>46234</v>
       </c>
       <c r="Y27" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Z27" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA27" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB27" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AC27" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AD27" s="13"/>
     </row>
@@ -5056,7 +5081,7 @@
         <v>106</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="6">
@@ -5096,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="10"/>
@@ -5110,31 +5135,31 @@
       <c r="AA28" s="5"/>
       <c r="AB28" s="5"/>
       <c r="AC28" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="AD28" s="13" t="s">
         <v>338</v>
-      </c>
-      <c r="AD28" s="13" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="289">
       <c r="A29" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="14">
         <v>28</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>108</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>18</v>
@@ -5143,7 +5168,7 @@
         <v>54</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K29" s="13" t="s">
         <v>56</v>
@@ -5189,19 +5214,19 @@
         <v>46232</v>
       </c>
       <c r="Y29" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Z29" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA29" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AB29" s="18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AC29" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AD29" s="13"/>
     </row>
@@ -5210,10 +5235,10 @@
         <v>109</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D30" s="6">
         <v>29</v>
@@ -5225,16 +5250,16 @@
         <v>111</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>24</v>
@@ -5281,19 +5306,19 @@
         <v>46233</v>
       </c>
       <c r="Y30" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z30" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA30" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="AB30" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="Z30" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AA30" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="AB30" s="12" t="s">
+      <c r="AC30" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="AC30" s="5" t="s">
-        <v>279</v>
       </c>
       <c r="AD30" s="13"/>
     </row>
@@ -5302,24 +5327,24 @@
         <v>112</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="14">
         <v>30</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5" t="s">
@@ -5342,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T31" s="5"/>
       <c r="U31" s="10"/>
@@ -5356,21 +5381,21 @@
       <c r="AA31" s="5"/>
       <c r="AB31" s="5"/>
       <c r="AC31" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="AD31" s="13" t="s">
         <v>342</v>
-      </c>
-      <c r="AD31" s="13" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="119">
       <c r="A32" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="D32" s="6">
         <v>31</v>
@@ -5382,7 +5407,7 @@
         <v>74</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>18</v>
@@ -5391,7 +5416,7 @@
         <v>50</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K32" s="5" t="s">
         <v>24</v>
@@ -5440,16 +5465,16 @@
         <v>75</v>
       </c>
       <c r="Z32" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AA32" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AB32" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AC32" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AD32" s="13"/>
     </row>
@@ -5510,46 +5535,46 @@
       <c r="AA33" s="13"/>
       <c r="AB33" s="13"/>
       <c r="AC33" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AD33" s="13"/>
     </row>
     <row r="34" spans="1:30" ht="136">
       <c r="A34" s="13" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D34" s="14">
         <v>33</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M34" s="29">
         <v>365.39866899999998</v>
@@ -5589,19 +5614,19 @@
         <v>46260</v>
       </c>
       <c r="Y34" s="13" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="Z34" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA34" s="13" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="AB34" s="13" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="AC34" s="13" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AD34" s="13"/>
     </row>
@@ -5610,7 +5635,7 @@
         <v>117</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C35" s="13"/>
       <c r="D35" s="14">
@@ -5650,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T35" s="13"/>
       <c r="U35" s="10"/>
@@ -5664,20 +5689,22 @@
       <c r="AA35" s="13"/>
       <c r="AB35" s="13"/>
       <c r="AC35" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="AD35" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="AD35" s="13" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="36" spans="1:30" ht="409.6">
+    </row>
+    <row r="36" spans="1:30" ht="102">
       <c r="A36" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="C36" s="5"/>
+        <v>478</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>479</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>147</v>
+      </c>
       <c r="D36" s="6">
         <v>35</v>
       </c>
@@ -5685,89 +5712,113 @@
         <v>103</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G36" s="5"/>
+        <v>119</v>
+      </c>
+      <c r="G36" s="31" t="s">
+        <v>480</v>
+      </c>
       <c r="H36" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="J36" s="5"/>
+        <v>143</v>
+      </c>
+      <c r="I36" s="31" t="s">
+        <v>481</v>
+      </c>
+      <c r="J36" s="31" t="s">
+        <v>481</v>
+      </c>
       <c r="K36" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L36" s="5" t="s">
-        <v>32</v>
+      <c r="L36" s="31" t="s">
+        <v>482</v>
       </c>
       <c r="M36" s="7">
-        <v>2400</v>
+        <v>2693</v>
       </c>
       <c r="N36" s="7">
-        <v>2400</v>
-      </c>
-      <c r="O36" s="7"/>
-      <c r="P36" s="8"/>
-      <c r="Q36" s="8"/>
+        <v>2693</v>
+      </c>
+      <c r="O36" s="7">
+        <v>2693</v>
+      </c>
+      <c r="P36" s="16">
+        <v>785</v>
+      </c>
+      <c r="Q36" s="16">
+        <v>881</v>
+      </c>
       <c r="R36" s="9">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
+        <f>SUM([1]!Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
+        <v>1666</v>
       </c>
       <c r="S36" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="T36" s="5"/>
-      <c r="U36" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="T36" s="5">
+        <v>12500</v>
+      </c>
+      <c r="U36" s="30">
+        <v>47453</v>
+      </c>
       <c r="V36" s="11">
-        <v>46136</v>
-      </c>
-      <c r="W36" s="11"/>
-      <c r="X36" s="11"/>
-      <c r="Y36" s="5"/>
-      <c r="Z36" s="5"/>
-      <c r="AA36" s="5"/>
-      <c r="AB36" s="5"/>
+        <v>46237</v>
+      </c>
+      <c r="W36" s="11">
+        <v>46237</v>
+      </c>
+      <c r="X36" s="11">
+        <v>46272</v>
+      </c>
+      <c r="Y36" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="Z36" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA36" s="31" t="s">
+        <v>484</v>
+      </c>
+      <c r="AB36" s="32" t="s">
+        <v>485</v>
+      </c>
       <c r="AC36" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="AD36" s="13" t="s">
-        <v>349</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="AD36" s="13"/>
     </row>
     <row r="37" spans="1:30" ht="204">
       <c r="A37" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D37" s="14">
         <v>36</v>
       </c>
       <c r="E37" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="F37" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="F37" s="13" t="s">
-        <v>122</v>
-      </c>
       <c r="G37" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="K37" s="13" t="s">
         <v>241</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="J37" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="K37" s="13" t="s">
-        <v>242</v>
       </c>
       <c r="L37" s="13" t="s">
         <v>11</v>
@@ -5810,19 +5861,19 @@
         <v>46198</v>
       </c>
       <c r="Y37" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z37" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA37" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="AB37" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="Z37" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="AA37" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="AB37" s="21" t="s">
+      <c r="AC37" s="13" t="s">
         <v>244</v>
-      </c>
-      <c r="AC37" s="13" t="s">
-        <v>245</v>
       </c>
       <c r="AD37" s="13"/>
     </row>
@@ -5831,10 +5882,10 @@
         <v>69</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D38" s="6">
         <v>37</v>
@@ -5846,7 +5897,7 @@
         <v>71</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>18</v>
@@ -5855,7 +5906,7 @@
         <v>54</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K38" s="13" t="s">
         <v>56</v>
@@ -5904,35 +5955,35 @@
         <v>72</v>
       </c>
       <c r="Z38" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA38" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AB38" s="21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AC38" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AD38" s="13"/>
     </row>
     <row r="39" spans="1:30" ht="409.6">
       <c r="A39" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="14">
         <v>38</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="7" t="s">
@@ -5962,7 +6013,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T39" s="5"/>
       <c r="U39" s="10"/>
@@ -5976,35 +6027,35 @@
       <c r="AA39" s="5"/>
       <c r="AB39" s="5"/>
       <c r="AC39" s="5" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="AD39" s="13" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="409.6">
       <c r="A40" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="6">
         <v>39</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="G40" s="13"/>
       <c r="H40" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J40" s="13"/>
       <c r="K40" s="13" t="s">
@@ -6027,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T40" s="13"/>
       <c r="U40" s="10"/>
@@ -6041,35 +6092,35 @@
       <c r="AA40" s="13"/>
       <c r="AB40" s="13"/>
       <c r="AC40" s="13" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="AD40" s="13" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="409.6">
       <c r="A41" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="14">
         <v>40</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G41" s="13"/>
       <c r="H41" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J41" s="13"/>
       <c r="K41" s="13" t="s">
@@ -6092,7 +6143,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T41" s="17"/>
       <c r="U41" s="10"/>
@@ -6106,39 +6157,39 @@
       <c r="AA41" s="13"/>
       <c r="AB41" s="13"/>
       <c r="AC41" s="13" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="AD41" s="18" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="409.6">
       <c r="A42" s="13" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="14">
         <v>41</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="G42" s="13"/>
       <c r="H42" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J42" s="13"/>
       <c r="K42" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L42" s="13" t="s">
         <v>11</v>
@@ -6155,7 +6206,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T42" s="15"/>
       <c r="U42" s="10"/>
@@ -6169,10 +6220,10 @@
       <c r="AA42" s="13"/>
       <c r="AB42" s="13"/>
       <c r="AC42" s="13" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AD42" s="13" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="43" spans="1:30">
@@ -6232,12 +6283,13 @@
     <hyperlink ref="AD41" r:id="rId20" xr:uid="{8B349C04-C00D-AF45-A235-16E6BEF78B40}"/>
     <hyperlink ref="AB27" r:id="rId21" xr:uid="{C5A97FE8-FC03-4B41-86D8-2D3DFD0E915C}"/>
     <hyperlink ref="AB37" r:id="rId22" xr:uid="{95B4063F-E390-2F4C-97F4-22710E08828D}"/>
+    <hyperlink ref="AB36" r:id="rId23" xr:uid="{9B51BCFC-E252-834C-AFEB-4F698D772E88}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId23"/>
-  <legacyDrawing r:id="rId24"/>
+  <drawing r:id="rId24"/>
+  <legacyDrawing r:id="rId25"/>
   <tableParts count="1">
-    <tablePart r:id="rId25"/>
+    <tablePart r:id="rId26"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6257,22 +6309,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>463</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>464</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>392</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="F1" s="24" t="s">
         <v>394</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>468</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>469</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>397</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>398</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16">
@@ -6280,19 +6332,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16">
@@ -6300,19 +6352,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16">
@@ -6320,19 +6372,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16">
@@ -6343,16 +6395,16 @@
         <v>0</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16">
@@ -6363,16 +6415,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16">
@@ -6380,19 +6432,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16">
@@ -6400,19 +6452,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16">
@@ -6423,16 +6475,16 @@
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16">
@@ -6443,16 +6495,16 @@
         <v>3</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16">
@@ -6460,19 +6512,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16">
@@ -6483,16 +6535,16 @@
         <v>4</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16">
@@ -6503,16 +6555,16 @@
         <v>5</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16">
@@ -6520,19 +6572,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16">
@@ -6540,19 +6592,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16">
@@ -6560,19 +6612,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E16" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="F16" s="23" t="s">
         <v>430</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16">
@@ -6580,19 +6632,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16">
@@ -6600,19 +6652,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32">
@@ -6620,19 +6672,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16">
@@ -6640,19 +6692,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16">
@@ -6660,19 +6712,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16">
@@ -6680,19 +6732,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16">
@@ -6703,16 +6755,16 @@
         <v>6</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16">
@@ -6720,19 +6772,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D24" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="F24" s="23" t="s">
         <v>447</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>447</v>
-      </c>
-      <c r="F24" s="23" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16">
@@ -6740,19 +6792,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="16">
@@ -6763,16 +6815,16 @@
         <v>7</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="32">
@@ -6780,19 +6832,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16">
@@ -6800,19 +6852,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16">
@@ -6820,19 +6872,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16">
@@ -6840,19 +6892,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16">
@@ -6860,19 +6912,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -6887,13 +6939,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="60">
       <c r="A1" s="26" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6901,10 +6953,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45">
@@ -6912,10 +6964,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="105">
@@ -6923,10 +6975,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6956,10 +7008,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6967,10 +7019,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7000,10 +7052,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7033,10 +7085,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60">
@@ -7044,10 +7096,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="60">
@@ -7055,10 +7107,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="90">
@@ -7066,10 +7118,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90">
@@ -7077,10 +7129,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="90">
@@ -7088,10 +7140,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="45">
@@ -7099,10 +7151,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="60">
@@ -7110,10 +7162,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="75">
@@ -7121,10 +7173,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30">
@@ -7143,10 +7195,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30">
@@ -7154,10 +7206,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30">
@@ -7176,10 +7228,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="60">
@@ -7187,10 +7239,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7198,10 +7250,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7209,10 +7261,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C30" s="27" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="30">
@@ -7220,10 +7272,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/rigi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E72C1D-546E-0546-819C-35C80583B28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA70704-9E5E-7741-AB65-575170B0A617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36640" yWindow="600" windowWidth="32160" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2606,8 +2606,8 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5761,7 +5761,7 @@
         <v>47453</v>
       </c>
       <c r="V36" s="11">
-        <v>46237</v>
+        <v>46133</v>
       </c>
       <c r="W36" s="11">
         <v>46237</v>
@@ -6283,7 +6283,7 @@
     <hyperlink ref="AD41" r:id="rId20" xr:uid="{8B349C04-C00D-AF45-A235-16E6BEF78B40}"/>
     <hyperlink ref="AB27" r:id="rId21" xr:uid="{C5A97FE8-FC03-4B41-86D8-2D3DFD0E915C}"/>
     <hyperlink ref="AB37" r:id="rId22" xr:uid="{95B4063F-E390-2F4C-97F4-22710E08828D}"/>
-    <hyperlink ref="AB36" r:id="rId23" xr:uid="{9B51BCFC-E252-834C-AFEB-4F698D772E88}"/>
+    <hyperlink ref="AB36" r:id="rId23" xr:uid="{CD0FDE43-399C-FA46-A379-C33D9FA306FF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId24"/>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/rigi-dashboard/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3646DA-E5C7-144A-ADC9-97E8137BAEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF1336A-3420-8149-8972-E618DC203F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="507">
   <si>
     <t>id_proyecto</t>
   </si>
@@ -1622,6 +1622,24 @@
       </rPr>
       <t xml:space="preserve"> en Argentina.</t>
     </r>
+  </si>
+  <si>
+    <t>Pampa Exploración S.A.</t>
+  </si>
+  <si>
+    <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
+  </si>
+  <si>
+    <t>NGEx Minerals Ltd. (Canadá)</t>
+  </si>
+  <si>
+    <t>Departamento Iglesia; Distrito Vicuña</t>
+  </si>
+  <si>
+    <t>https://ngexminerals.com/news/ngex-releases-2025-sustainability-summary-122811/; https://www.panorama-minero.com/es/mining-compendium/argentina/project/lunahuasi</t>
+  </si>
+  <si>
+    <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
   </si>
 </sst>
 </file>
@@ -1708,7 +1726,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1734,6 +1752,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF2F75B5"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1767,7 +1790,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1887,6 +1910,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2638,8 +2679,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7BB49DC-9D24-614F-848B-0F39C691B2B5}" name="Tabla22" displayName="Tabla22" ref="A1:AD44" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31">
-  <autoFilter ref="A1:AD44" xr:uid="{C7BB49DC-9D24-614F-848B-0F39C691B2B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7BB49DC-9D24-614F-848B-0F39C691B2B5}" name="Tabla22" displayName="Tabla22" ref="A1:AD45" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31">
+  <autoFilter ref="A1:AD45" xr:uid="{C7BB49DC-9D24-614F-848B-0F39C691B2B5}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC41">
     <sortCondition ref="D1:D41"/>
   </sortState>
@@ -2869,7 +2910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19742F29-8880-E54E-B5B1-A7D7707C4679}">
-  <dimension ref="A1:AD44"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -6362,6 +6403,69 @@
       </c>
       <c r="AD44" s="12" t="s">
         <v>496</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" ht="240">
+      <c r="A45" s="41" t="s">
+        <v>501</v>
+      </c>
+      <c r="B45" s="41" t="s">
+        <v>502</v>
+      </c>
+      <c r="C45" s="41"/>
+      <c r="D45" s="42">
+        <v>44</v>
+      </c>
+      <c r="E45" s="43" t="s">
+        <v>503</v>
+      </c>
+      <c r="F45" s="41" t="s">
+        <v>501</v>
+      </c>
+      <c r="G45" s="41"/>
+      <c r="H45" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="J45" s="41"/>
+      <c r="K45" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="41" t="s">
+        <v>504</v>
+      </c>
+      <c r="M45" s="43">
+        <v>2437</v>
+      </c>
+      <c r="N45" s="43"/>
+      <c r="O45" s="43"/>
+      <c r="P45" s="44"/>
+      <c r="Q45" s="44"/>
+      <c r="R45" s="44">
+        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
+        <v>0</v>
+      </c>
+      <c r="S45" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="T45" s="41"/>
+      <c r="U45" s="45"/>
+      <c r="V45" s="46">
+        <v>46113</v>
+      </c>
+      <c r="W45" s="46"/>
+      <c r="X45" s="46"/>
+      <c r="Y45" s="41"/>
+      <c r="Z45" s="41"/>
+      <c r="AA45" s="41"/>
+      <c r="AB45" s="41"/>
+      <c r="AC45" s="41" t="s">
+        <v>506</v>
+      </c>
+      <c r="AD45" s="41" t="s">
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -6413,7 +6517,7 @@
     <col min="6" max="6" width="84" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="32">
       <c r="A1" s="2" t="s">
         <v>387</v>
       </c>
@@ -7043,7 +7147,7 @@
   <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="60">
+    <row r="1" spans="1:3" ht="64">
       <c r="A1" s="4" t="s">
         <v>387</v>
       </c>
@@ -7054,7 +7158,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" ht="16">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -7065,7 +7169,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="45">
+    <row r="3" spans="1:3" ht="48">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -7076,7 +7180,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="105">
+    <row r="4" spans="1:3" ht="112">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -7087,7 +7191,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" ht="16">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -7098,7 +7202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" ht="16">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -7109,7 +7213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30">
+    <row r="7" spans="1:3" ht="32">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -7120,7 +7224,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" ht="16">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -7131,7 +7235,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" ht="16">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -7142,7 +7246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" ht="16">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -7153,7 +7257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="60">
+    <row r="11" spans="1:3" ht="64">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -7164,7 +7268,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" ht="16">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -7175,7 +7279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="30">
+    <row r="13" spans="1:3" ht="32">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -7186,7 +7290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="30">
+    <row r="14" spans="1:3" ht="48">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -7197,7 +7301,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="60">
+    <row r="15" spans="1:3" ht="64">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -7208,7 +7312,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="60">
+    <row r="16" spans="1:3" ht="64">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -7219,7 +7323,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="90">
+    <row r="17" spans="1:3" ht="96">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -7230,7 +7334,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="90">
+    <row r="18" spans="1:3" ht="96">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -7241,7 +7345,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="90">
+    <row r="19" spans="1:3" ht="96">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -7252,7 +7356,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="45">
+    <row r="20" spans="1:3" ht="48">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -7263,7 +7367,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="60">
+    <row r="21" spans="1:3" ht="64">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -7274,7 +7378,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="75">
+    <row r="22" spans="1:3" ht="80">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -7285,7 +7389,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="30">
+    <row r="23" spans="1:3" ht="32">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -7296,7 +7400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30">
+    <row r="24" spans="1:3" ht="32">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -7307,7 +7411,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30">
+    <row r="25" spans="1:3" ht="32">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -7318,7 +7422,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="30">
+    <row r="26" spans="1:3" ht="32">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -7329,7 +7433,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="60">
+    <row r="27" spans="1:3" ht="64">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -7340,7 +7444,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="60">
+    <row r="28" spans="1:3" ht="64">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -7351,7 +7455,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" ht="16">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -7362,7 +7466,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" ht="16">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -7373,7 +7477,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="30">
+    <row r="31" spans="1:3" ht="32">
       <c r="A31" s="5">
         <v>30</v>
       </c>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/rigi-dashboard/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/base de datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF1336A-3420-8149-8972-E618DC203F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2B53E7-0301-A847-9022-879617AD4322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31600" yWindow="600" windowWidth="37180" windowHeight="25800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="7" r:id="rId1"/>
@@ -1018,12 +1018,6 @@
     <t>Upstream</t>
   </si>
   <si>
-    <t>Globaris; Gobierno de Neuquén; EconoJournal; Luis Caputo; Clarín; auditoría 2026-08-08</t>
-  </si>
-  <si>
-    <t>https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp; https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/; https://x.com/LuisCaputoAR/status/2047621135127269495; https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html</t>
-  </si>
-  <si>
     <t>Construcción de un oleoducto de aproximadamente 207 km entre el área de Auca Mahuida/Puesto Hernández, en Neuquén, y Allen, en Río Negro, junto con obras de repotenciación y medición. La ampliación busca sumar capacidad de transporte de crudo desde Vaca Muerta.</t>
   </si>
   <si>
@@ -1640,6 +1634,12 @@
   </si>
   <si>
     <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
+  </si>
+  <si>
+    <t>Globaris; Gobierno de Neuquén; EconoJournal; Luis Caputo; Clarín; La Nación; Bloomberg</t>
+  </si>
+  <si>
+    <t>https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp; https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/; https://x.com/LuisCaputoAR/status/2047621135127269495; https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html; https://www.lanacion.com.ar/economia/pluspetrol-y-gyp-obtuvieron-el-rigi-para-un-proyecto-de-us12400-millones-en-vaca-muerta-nid02102026/; https://www.bloomberglinea.com/latinoamerica/argentina/pluspetrol-recibe-luz-verde-del-rigi-para-invertir-us12400-millones-en-vaca-muerta/</t>
   </si>
 </sst>
 </file>
@@ -2942,13 +2942,13 @@
   <sheetData>
     <row r="1" spans="1:30" ht="32">
       <c r="A1" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -2969,7 +2969,7 @@
         <v>3</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>4</v>
@@ -2978,31 +2978,31 @@
         <v>5</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="U1" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>6</v>
@@ -3017,19 +3017,19 @@
         <v>7</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>128</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="91">
@@ -3410,7 +3410,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>35</v>
@@ -4052,7 +4052,7 @@
         <v>65</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H13" s="23" t="s">
         <v>142</v>
@@ -4226,7 +4226,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F15" s="21" t="s">
         <v>296</v>
@@ -4376,10 +4376,10 @@
         <v>11</v>
       </c>
       <c r="M17" s="23">
-        <v>12000</v>
+        <v>12400</v>
       </c>
       <c r="N17" s="23">
-        <v>12000</v>
+        <v>12400</v>
       </c>
       <c r="O17" s="23"/>
       <c r="P17" s="16"/>
@@ -4391,7 +4391,9 @@
       <c r="S17" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="T17" s="21"/>
+      <c r="T17" s="21">
+        <v>6990</v>
+      </c>
       <c r="U17" s="18"/>
       <c r="V17" s="24">
         <v>45771</v>
@@ -4403,10 +4405,10 @@
       <c r="AA17" s="21"/>
       <c r="AB17" s="21"/>
       <c r="AC17" s="21" t="s">
-        <v>306</v>
+        <v>505</v>
       </c>
       <c r="AD17" s="21" t="s">
-        <v>307</v>
+        <v>506</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="106">
@@ -4414,7 +4416,7 @@
         <v>195</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>158</v>
@@ -4505,7 +4507,7 @@
         <v>85</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C19" s="21"/>
       <c r="D19" s="22">
@@ -4526,7 +4528,7 @@
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L19" s="21" t="s">
         <v>11</v>
@@ -4559,10 +4561,10 @@
       <c r="AA19" s="21"/>
       <c r="AB19" s="21"/>
       <c r="AC19" s="21" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AD19" s="21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="409.6">
@@ -4570,7 +4572,7 @@
         <v>88</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="14">
@@ -4624,10 +4626,10 @@
       <c r="AA20" s="13"/>
       <c r="AB20" s="13"/>
       <c r="AC20" s="13" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AD20" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="409.6">
@@ -4635,7 +4637,7 @@
         <v>91</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C21" s="21"/>
       <c r="D21" s="22">
@@ -4645,7 +4647,7 @@
         <v>92</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="23" t="s">
@@ -4689,10 +4691,10 @@
       <c r="AA21" s="21"/>
       <c r="AB21" s="21"/>
       <c r="AC21" s="21" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AD21" s="21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="409.6">
@@ -4700,17 +4702,17 @@
         <v>93</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="14">
         <v>21</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="15" t="s">
@@ -4721,10 +4723,10 @@
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="13" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="M22" s="15">
         <v>200</v>
@@ -4754,10 +4756,10 @@
       <c r="AA22" s="13"/>
       <c r="AB22" s="13"/>
       <c r="AC22" s="13" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AD22" s="21" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="399">
@@ -4765,7 +4767,7 @@
         <v>95</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C23" s="21"/>
       <c r="D23" s="22">
@@ -4819,10 +4821,10 @@
       <c r="AA23" s="21"/>
       <c r="AB23" s="21"/>
       <c r="AC23" s="21" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AD23" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="409.6">
@@ -4830,7 +4832,7 @@
         <v>98</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="14">
@@ -4884,10 +4886,10 @@
       <c r="AA24" s="13"/>
       <c r="AB24" s="13"/>
       <c r="AC24" s="13" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AD24" s="21" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="409.6">
@@ -4895,14 +4897,14 @@
         <v>101</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C25" s="21"/>
       <c r="D25" s="22">
         <v>24</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>102</v>
@@ -4949,10 +4951,10 @@
       <c r="AA25" s="21"/>
       <c r="AB25" s="21"/>
       <c r="AC25" s="21" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AD25" s="21" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="256">
@@ -5142,7 +5144,7 @@
         <v>106</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="14">
@@ -5196,10 +5198,10 @@
       <c r="AA28" s="13"/>
       <c r="AB28" s="13"/>
       <c r="AC28" s="13" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AD28" s="21" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="241">
@@ -5214,7 +5216,7 @@
         <v>28</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F29" s="21" t="s">
         <v>108</v>
@@ -5388,17 +5390,17 @@
         <v>112</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="22">
         <v>30</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G31" s="13"/>
       <c r="H31" s="15" t="s">
@@ -5442,10 +5444,10 @@
       <c r="AA31" s="13"/>
       <c r="AB31" s="13"/>
       <c r="AC31" s="13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AD31" s="21" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="106">
@@ -5602,10 +5604,10 @@
     </row>
     <row r="34" spans="1:30" ht="121">
       <c r="A34" s="21" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>158</v>
@@ -5614,13 +5616,13 @@
         <v>33</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H34" s="23" t="s">
         <v>142</v>
@@ -5629,13 +5631,13 @@
         <v>151</v>
       </c>
       <c r="J34" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="K34" s="21" t="s">
         <v>470</v>
       </c>
-      <c r="K34" s="21" t="s">
-        <v>472</v>
-      </c>
       <c r="L34" s="13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="M34" s="30">
         <v>365.39866899999998</v>
@@ -5675,19 +5677,19 @@
         <v>46260</v>
       </c>
       <c r="Y34" s="21" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="Z34" s="21" t="s">
         <v>146</v>
       </c>
       <c r="AA34" s="21" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AB34" s="21" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AC34" s="21" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AD34" s="21"/>
     </row>
@@ -5696,7 +5698,7 @@
         <v>117</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C35" s="21"/>
       <c r="D35" s="22">
@@ -5750,18 +5752,18 @@
       <c r="AA35" s="21"/>
       <c r="AB35" s="21"/>
       <c r="AC35" s="21" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AD35" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="75">
       <c r="A36" s="31" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C36" s="31" t="s">
         <v>146</v>
@@ -5776,22 +5778,22 @@
         <v>119</v>
       </c>
       <c r="G36" s="32" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H36" s="34" t="s">
         <v>142</v>
       </c>
       <c r="I36" s="32" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J36" s="32" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="K36" s="31" t="s">
         <v>31</v>
       </c>
       <c r="L36" s="32" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="M36" s="34">
         <v>2693</v>
@@ -5831,19 +5833,19 @@
         <v>46272</v>
       </c>
       <c r="Y36" s="31" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="Z36" s="31" t="s">
         <v>146</v>
       </c>
       <c r="AA36" s="32" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AB36" s="39" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AC36" s="31" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AD36" s="40"/>
     </row>
@@ -5864,7 +5866,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G37" s="21" t="s">
         <v>239</v>
@@ -5928,7 +5930,7 @@
         <v>146</v>
       </c>
       <c r="AA37" s="21" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AB37" s="28" t="s">
         <v>242</v>
@@ -6034,17 +6036,17 @@
         <v>121</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="22">
         <v>38</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G39" s="13"/>
       <c r="H39" s="15" t="s">
@@ -6088,10 +6090,10 @@
       <c r="AA39" s="13"/>
       <c r="AB39" s="13"/>
       <c r="AC39" s="13" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AD39" s="21" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="385">
@@ -6099,7 +6101,7 @@
         <v>291</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C40" s="21"/>
       <c r="D40" s="14">
@@ -6109,7 +6111,7 @@
         <v>122</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G40" s="21"/>
       <c r="H40" s="23" t="s">
@@ -6153,10 +6155,10 @@
       <c r="AA40" s="21"/>
       <c r="AB40" s="21"/>
       <c r="AC40" s="21" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AD40" s="21" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="409.6">
@@ -6164,7 +6166,7 @@
         <v>292</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="22">
@@ -6174,7 +6176,7 @@
         <v>293</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G41" s="21"/>
       <c r="H41" s="23" t="s">
@@ -6218,28 +6220,28 @@
       <c r="AA41" s="21"/>
       <c r="AB41" s="21"/>
       <c r="AC41" s="21" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AD41" s="25" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="409.6">
       <c r="A42" s="21" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C42" s="21"/>
       <c r="D42" s="22">
         <v>41</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G42" s="21"/>
       <c r="H42" s="23" t="s">
@@ -6250,7 +6252,7 @@
       </c>
       <c r="J42" s="21"/>
       <c r="K42" s="21" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L42" s="21" t="s">
         <v>11</v>
@@ -6281,40 +6283,40 @@
       <c r="AA42" s="21"/>
       <c r="AB42" s="21"/>
       <c r="AC42" s="21" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AD42" s="21" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" spans="1:30" ht="409.6">
       <c r="A43" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="7">
         <v>42</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="8" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J43" s="6"/>
       <c r="K43" s="6" t="s">
         <v>31</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="M43" s="8">
         <v>1341</v>
@@ -6341,18 +6343,18 @@
       <c r="AA43" s="6"/>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="AD43" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="409.6">
       <c r="A44" s="12" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C44" s="12"/>
       <c r="D44" s="12">
@@ -6371,10 +6373,10 @@
       </c>
       <c r="J44" s="12"/>
       <c r="K44" s="12" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="M44" s="12">
         <v>1200</v>
@@ -6399,28 +6401,28 @@
       <c r="AA44" s="12"/>
       <c r="AB44" s="12"/>
       <c r="AC44" s="12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="AD44" s="12" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="45" spans="1:30" ht="240">
       <c r="A45" s="41" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B45" s="41" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C45" s="41"/>
       <c r="D45" s="42">
         <v>44</v>
       </c>
       <c r="E45" s="43" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F45" s="41" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G45" s="41"/>
       <c r="H45" s="43" t="s">
@@ -6434,7 +6436,7 @@
         <v>24</v>
       </c>
       <c r="L45" s="41" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="M45" s="43">
         <v>2437</v>
@@ -6452,9 +6454,7 @@
       </c>
       <c r="T45" s="41"/>
       <c r="U45" s="45"/>
-      <c r="V45" s="46">
-        <v>46113</v>
-      </c>
+      <c r="V45" s="46"/>
       <c r="W45" s="46"/>
       <c r="X45" s="46"/>
       <c r="Y45" s="41"/>
@@ -6462,10 +6462,10 @@
       <c r="AA45" s="41"/>
       <c r="AB45" s="41"/>
       <c r="AC45" s="41" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="AD45" s="41" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -6519,22 +6519,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32">
       <c r="A1" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16">
@@ -6542,19 +6542,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>172</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16">
@@ -6562,19 +6562,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16">
@@ -6582,19 +6582,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16">
@@ -6605,16 +6605,16 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16">
@@ -6625,16 +6625,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16">
@@ -6645,16 +6645,16 @@
         <v>171</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16">
@@ -6662,19 +6662,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16">
@@ -6685,16 +6685,16 @@
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16">
@@ -6705,16 +6705,16 @@
         <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16">
@@ -6722,19 +6722,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16">
@@ -6745,16 +6745,16 @@
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16">
@@ -6765,16 +6765,16 @@
         <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16">
@@ -6782,19 +6782,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16">
@@ -6802,19 +6802,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16">
@@ -6822,19 +6822,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16">
@@ -6842,19 +6842,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16">
@@ -6862,19 +6862,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32">
@@ -6882,19 +6882,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16">
@@ -6902,19 +6902,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>126</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16">
@@ -6922,19 +6922,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16">
@@ -6942,19 +6942,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16">
@@ -6965,16 +6965,16 @@
         <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16">
@@ -6985,16 +6985,16 @@
         <v>153</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16">
@@ -7005,16 +7005,16 @@
         <v>154</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="16">
@@ -7025,16 +7025,16 @@
         <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="32">
@@ -7042,19 +7042,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16">
@@ -7062,19 +7062,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16">
@@ -7085,16 +7085,16 @@
         <v>128</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16">
@@ -7102,19 +7102,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>147</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16">
@@ -7122,19 +7122,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -7149,13 +7149,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="64">
       <c r="A1" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>387</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16">
@@ -7166,7 +7166,7 @@
         <v>172</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="48">
@@ -7177,7 +7177,7 @@
         <v>159</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="112">
@@ -7188,7 +7188,7 @@
         <v>251</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16">
@@ -7232,7 +7232,7 @@
         <v>143</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16">
@@ -7265,7 +7265,7 @@
         <v>188</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16">
@@ -7298,7 +7298,7 @@
         <v>124</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="64">
@@ -7309,7 +7309,7 @@
         <v>279</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="64">
@@ -7320,7 +7320,7 @@
         <v>125</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="96">
@@ -7328,10 +7328,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="96">
@@ -7339,10 +7339,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="96">
@@ -7350,10 +7350,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="48">
@@ -7364,7 +7364,7 @@
         <v>126</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="64">
@@ -7375,7 +7375,7 @@
         <v>221</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="80">
@@ -7383,10 +7383,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="32">
@@ -7441,7 +7441,7 @@
         <v>219</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="64">
@@ -7452,7 +7452,7 @@
         <v>220</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16">
@@ -7474,7 +7474,7 @@
         <v>147</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="32">
@@ -7485,7 +7485,7 @@
         <v>294</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/base de datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2B53E7-0301-A847-9022-879617AD4322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217E0B12-3668-5849-9BD1-32C9FCFD18AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31600" yWindow="600" windowWidth="37180" windowHeight="25800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35760" yWindow="600" windowWidth="33020" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="7" r:id="rId1"/>
@@ -39,6 +39,7 @@
   <authors>
     <author>Lucas Sebastian Ordoñez</author>
     <author>tc={AB094BBD-1C2D-6F4B-8934-933C032D5033}</author>
+    <author>tc={1C1F2559-7EE3-DF4D-8661-353CB183F945}</author>
     <author>tc={81907ACA-C719-C348-AD5F-B563992B5DE3}</author>
   </authors>
   <commentList>
@@ -84,7 +85,16 @@
     En la resolución del proyecto aclara que se va a poner en el primer año solamente</t>
       </text>
     </comment>
-    <comment ref="R30" authorId="2" shapeId="0" xr:uid="{81907ACA-C719-C348-AD5F-B563992B5DE3}">
+    <comment ref="O24" authorId="2" shapeId="0" xr:uid="{1C1F2559-7EE3-DF4D-8661-353CB183F945}">
+      <text>
+        <t xml:space="preserve">[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    No se incluye en la resolución
+</t>
+      </text>
+    </comment>
+    <comment ref="R30" authorId="3" shapeId="0" xr:uid="{81907ACA-C719-C348-AD5F-B563992B5DE3}">
       <text>
         <t xml:space="preserve">[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -98,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="513">
   <si>
     <t>id_proyecto</t>
   </si>
@@ -394,15 +404,9 @@
     <t>Vientos La Rinconada S.A.U.</t>
   </si>
   <si>
-    <t>Planta de Tratamiento Los Toldos</t>
-  </si>
-  <si>
     <t>Tecpetrol S.A. (Argentina); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
   </si>
   <si>
-    <t>Tecpetrol S.A – Gas y Petróleo del Neuquén S.A. (UT)</t>
-  </si>
-  <si>
     <t>Pozuelos Pastos Grandes (PPG)</t>
   </si>
   <si>
@@ -1076,15 +1080,6 @@
   </si>
   <si>
     <t>https://www.tenaris.com/en/news/2025/tenaris-begins-construction-of-second-wind-farm-in-argentina; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
-  </si>
-  <si>
-    <t>Desarrollo del área no convencional Los Toldos II Este, en Neuquén, con una planta central de procesamiento de crudo, perforación de pozos y sistemas de recolección y evacuación. El proyecto apunta a alcanzar una producción cercana a 70.000 barriles diarios.</t>
-  </si>
-  <si>
-    <t>Globaris; Techint Ingeniería y Construcción; Vaca Muerta News; Infobae; auditoría 2026-08-08</t>
-  </si>
-  <si>
-    <t>https://www.techint.com/es/nuestros-proyectos/los-toldos-ii-este; https://vacamuertanews.com/amp/a-30-km-de-rincon-de-los-sauces-tecpetrol-y-gyp-lanzan-un-megaproyecto-de-shale-oil-con-380-pozos.htm; https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/</t>
   </si>
   <si>
     <t>Desarrollo integrado de litio en los salares Pozuelos y Pastos Grandes, en la Puna salteña, mediante una operación conjunta de Ganfeng Lithium y Lithium Argentina. El plan contempla infraestructura de extracción y procesamiento y una expansión por etapas hasta una capacidad objetivo de 150.000 toneladas anuales de carbonato de litio equivalente.</t>
@@ -1640,6 +1635,39 @@
   </si>
   <si>
     <t>https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp; https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/; https://x.com/LuisCaputoAR/status/2047621135127269495; https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html; https://www.lanacion.com.ar/economia/pluspetrol-y-gyp-obtuvieron-el-rigi-para-un-proyecto-de-us12400-millones-en-vaca-muerta-nid02102026/; https://www.bloomberglinea.com/latinoamerica/argentina/pluspetrol-recibe-luz-verde-del-rigi-para-invertir-us12400-millones-en-vaca-muerta/</t>
+  </si>
+  <si>
+    <t>UT RIGI LOS TOLDOS</t>
+  </si>
+  <si>
+    <t>Tecpetrol S.A. Gas y Petróleo del Neuquén S.A. UT RIGI Los Toldos U.T.E.</t>
+  </si>
+  <si>
+    <t>33-71889684-9</t>
+  </si>
+  <si>
+    <t>Explotación y producción de nuevos desarrollos de hidrocarburos líquidos y gaseosos costa adentro</t>
+  </si>
+  <si>
+    <t>Departamento Pehuenches; área Los Toldos II Este; Engolfamiento/Bajo de Añelo</t>
+  </si>
+  <si>
+    <t>La resolución establece que la primera etapa comenzó el 01/11/2024, antes de la presentación y aprobación RIGI.</t>
+  </si>
+  <si>
+    <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/348768/20261009</t>
+  </si>
+  <si>
+    <t>https://www.argentina.gob.ar/normativa/nacional/norma-431089 ; https://www.tecpetrol.com/es/noticias/2026/rigi-los-toldos-ii-este</t>
+  </si>
+  <si>
+    <t>Desarrollo de hidrocarburos en el área Los Toldos II Este, Vaca Muerta, el cual consiste en la perforación de 380 pozos junto con su infraestructura asociada para el tratamiento de la producción por una capacidad máxima de 70 mil barriles de petróleo diarios. El proyecto prevé un total de 360 millones de barriles de petróleo de exportación durante su operación.</t>
+  </si>
+  <si>
+    <t>Res. 1771/2026</t>
+  </si>
+  <si>
+    <t>Res. 1771/2026; Tecpetrol</t>
   </si>
 </sst>
 </file>
@@ -1790,7 +1818,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1928,6 +1956,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2901,6 +2947,10 @@
   <threadedComment ref="R11" dT="2026-08-23T00:21:57.27" personId="{3AB22868-5EC9-474A-BBCF-88B6CF007C82}" id="{AB094BBD-1C2D-6F4B-8934-933C032D5033}">
     <text>En la resolución del proyecto aclara que se va a poner en el primer año solamente</text>
   </threadedComment>
+  <threadedComment ref="O24" dT="2026-10-09T18:59:55.16" personId="{3AB22868-5EC9-474A-BBCF-88B6CF007C82}" id="{1C1F2559-7EE3-DF4D-8661-353CB183F945}">
+    <text xml:space="preserve">No se incluye en la resolución
+</text>
+  </threadedComment>
   <threadedComment ref="R30" dT="2026-08-23T00:27:42.92" personId="{3AB22868-5EC9-474A-BBCF-88B6CF007C82}" id="{81907ACA-C719-C348-AD5F-B563992B5DE3}">
     <text xml:space="preserve">En la resolución del proyecto se da el valor total de los dos primeros años. Divido en partes iguales los dos primeros años
 </text>
@@ -2942,13 +2992,13 @@
   <sheetData>
     <row r="1" spans="1:30" ht="32">
       <c r="A1" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -2957,10 +3007,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>2</v>
@@ -2969,7 +3019,7 @@
         <v>3</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>4</v>
@@ -2978,69 +3028,69 @@
         <v>5</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="U1" s="1" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="91">
       <c r="A2" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D2" s="14">
         <v>1</v>
@@ -3052,22 +3102,22 @@
         <v>9</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="L2" s="13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M2" s="15">
         <v>550</v>
@@ -3110,16 +3160,16 @@
         <v>12</v>
       </c>
       <c r="Z2" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AA2" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AB2" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AC2" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AD2" s="21"/>
     </row>
@@ -3128,10 +3178,10 @@
         <v>15</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D3" s="22">
         <v>2</v>
@@ -3143,19 +3193,19 @@
         <v>17</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H3" s="23" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L3" s="21" t="s">
         <v>20</v>
@@ -3201,28 +3251,28 @@
         <v>21</v>
       </c>
       <c r="Z3" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AB3" s="25" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AD3" s="21"/>
     </row>
     <row r="4" spans="1:30" ht="91">
       <c r="A4" s="21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D4" s="14">
         <v>3</v>
@@ -3234,16 +3284,16 @@
         <v>23</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K4" s="21" t="s">
         <v>24</v>
@@ -3292,16 +3342,16 @@
         <v>26</v>
       </c>
       <c r="Z4" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA4" s="21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AB4" s="25" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AC4" s="21" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AD4" s="21"/>
     </row>
@@ -3310,10 +3360,10 @@
         <v>27</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D5" s="22">
         <v>4</v>
@@ -3325,7 +3375,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H5" s="23" t="s">
         <v>10</v>
@@ -3383,16 +3433,16 @@
         <v>33</v>
       </c>
       <c r="Z5" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA5" s="21" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AB5" s="25" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AC5" s="21" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AD5" s="21"/>
     </row>
@@ -3401,28 +3451,28 @@
         <v>34</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D6" s="14">
         <v>5</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="13" t="s">
@@ -3473,16 +3523,16 @@
         <v>37</v>
       </c>
       <c r="Z6" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA6" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AB6" s="20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AC6" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AD6" s="21"/>
     </row>
@@ -3491,10 +3541,10 @@
         <v>38</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D7" s="22">
         <v>6</v>
@@ -3503,19 +3553,19 @@
         <v>39</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="K7" s="13" t="s">
         <v>40</v>
@@ -3564,16 +3614,16 @@
         <v>41</v>
       </c>
       <c r="Z7" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA7" s="13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AB7" s="26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AC7" s="13" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AD7" s="21"/>
     </row>
@@ -3582,10 +3632,10 @@
         <v>42</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D8" s="14">
         <v>7</v>
@@ -3597,7 +3647,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H8" s="23" t="s">
         <v>45</v>
@@ -3606,7 +3656,7 @@
         <v>45</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K8" s="21" t="s">
         <v>31</v>
@@ -3655,16 +3705,16 @@
         <v>46</v>
       </c>
       <c r="Z8" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA8" s="21" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AB8" s="27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AC8" s="21" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AD8" s="21"/>
     </row>
@@ -3673,10 +3723,10 @@
         <v>47</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D9" s="22">
         <v>8</v>
@@ -3688,7 +3738,7 @@
         <v>49</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>18</v>
@@ -3697,7 +3747,7 @@
         <v>50</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K9" s="13" t="s">
         <v>36</v>
@@ -3746,28 +3796,28 @@
         <v>51</v>
       </c>
       <c r="Z9" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA9" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AB9" s="20" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AC9" s="13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AD9" s="21"/>
     </row>
     <row r="10" spans="1:30" ht="106">
       <c r="A10" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D10" s="14">
         <v>9</v>
@@ -3779,7 +3829,7 @@
         <v>53</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H10" s="23" t="s">
         <v>18</v>
@@ -3788,7 +3838,7 @@
         <v>54</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K10" s="21" t="s">
         <v>19</v>
@@ -3837,28 +3887,28 @@
         <v>55</v>
       </c>
       <c r="Z10" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AA10" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="AB10" s="25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AC10" s="21" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AD10" s="21"/>
     </row>
     <row r="11" spans="1:30" ht="226">
       <c r="A11" s="13" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D11" s="22">
         <v>10</v>
@@ -3867,10 +3917,10 @@
         <v>52</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>18</v>
@@ -3879,7 +3929,7 @@
         <v>54</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K11" s="13" t="s">
         <v>56</v>
@@ -3928,28 +3978,28 @@
         <v>57</v>
       </c>
       <c r="Z11" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AA11" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AB11" s="20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AC11" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AD11" s="21"/>
     </row>
     <row r="12" spans="1:30" ht="106">
       <c r="A12" s="13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" s="14">
         <v>11</v>
@@ -3961,7 +4011,7 @@
         <v>59</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>60</v>
@@ -3970,7 +4020,7 @@
         <v>61</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K12" s="13" t="s">
         <v>62</v>
@@ -4019,28 +4069,28 @@
         <v>63</v>
       </c>
       <c r="Z12" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA12" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AB12" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AC12" s="13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AD12" s="21"/>
     </row>
     <row r="13" spans="1:30" ht="315">
       <c r="A13" s="21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D13" s="22">
         <v>12</v>
@@ -4052,16 +4102,16 @@
         <v>65</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J13" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K13" s="21" t="s">
         <v>40</v>
@@ -4110,28 +4160,28 @@
         <v>66</v>
       </c>
       <c r="Z13" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA13" s="21" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AB13" s="25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AC13" s="21" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AD13" s="21"/>
     </row>
     <row r="14" spans="1:30" ht="121">
       <c r="A14" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D14" s="14">
         <v>13</v>
@@ -4140,19 +4190,19 @@
         <v>67</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H14" s="15" t="s">
         <v>18</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K14" s="13" t="s">
         <v>24</v>
@@ -4201,16 +4251,16 @@
         <v>68</v>
       </c>
       <c r="Z14" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AA14" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AB14" s="20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AC14" s="13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AD14" s="21"/>
     </row>
@@ -4219,17 +4269,17 @@
         <v>76</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="22">
         <v>14</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="23" t="s">
@@ -4259,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T15" s="21"/>
       <c r="U15" s="18"/>
@@ -4273,10 +4323,10 @@
       <c r="AA15" s="21"/>
       <c r="AB15" s="21"/>
       <c r="AC15" s="21" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AD15" s="21" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="399">
@@ -4284,7 +4334,7 @@
         <v>77</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="14">
@@ -4324,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T16" s="13"/>
       <c r="U16" s="18"/>
@@ -4338,10 +4388,10 @@
       <c r="AA16" s="13"/>
       <c r="AB16" s="13"/>
       <c r="AC16" s="13" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AD16" s="21" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="409.6">
@@ -4349,24 +4399,24 @@
         <v>81</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="22">
         <v>16</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I17" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J17" s="21"/>
       <c r="K17" s="21" t="s">
@@ -4389,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T17" s="21">
         <v>6990</v>
@@ -4405,21 +4455,21 @@
       <c r="AA17" s="21"/>
       <c r="AB17" s="21"/>
       <c r="AC17" s="21" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="AD17" s="21" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="106">
       <c r="A18" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D18" s="14">
         <v>17</v>
@@ -4428,10 +4478,10 @@
         <v>83</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>18</v>
@@ -4440,7 +4490,7 @@
         <v>54</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K18" s="13" t="s">
         <v>84</v>
@@ -4486,19 +4536,19 @@
         <v>46177</v>
       </c>
       <c r="Y18" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Z18" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AA18" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AB18" s="20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AC18" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AD18" s="21"/>
     </row>
@@ -4507,7 +4557,7 @@
         <v>85</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C19" s="21"/>
       <c r="D19" s="22">
@@ -4521,14 +4571,14 @@
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J19" s="21"/>
       <c r="K19" s="21" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L19" s="21" t="s">
         <v>11</v>
@@ -4547,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T19" s="21"/>
       <c r="U19" s="18"/>
@@ -4561,10 +4611,10 @@
       <c r="AA19" s="21"/>
       <c r="AB19" s="21"/>
       <c r="AC19" s="21" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AD19" s="21" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="409.6">
@@ -4572,7 +4622,7 @@
         <v>88</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="14">
@@ -4612,7 +4662,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T20" s="13"/>
       <c r="U20" s="18"/>
@@ -4626,10 +4676,10 @@
       <c r="AA20" s="13"/>
       <c r="AB20" s="13"/>
       <c r="AC20" s="13" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AD20" s="21" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="409.6">
@@ -4637,7 +4687,7 @@
         <v>91</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C21" s="21"/>
       <c r="D21" s="22">
@@ -4647,14 +4697,14 @@
         <v>92</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I21" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21" t="s">
@@ -4677,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T21" s="21"/>
       <c r="U21" s="18"/>
@@ -4691,10 +4741,10 @@
       <c r="AA21" s="21"/>
       <c r="AB21" s="21"/>
       <c r="AC21" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AD21" s="21" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="409.6">
@@ -4702,17 +4752,17 @@
         <v>93</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="14">
         <v>21</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="15" t="s">
@@ -4723,10 +4773,10 @@
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="M22" s="15">
         <v>200</v>
@@ -4742,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T22" s="13"/>
       <c r="U22" s="18"/>
@@ -4756,10 +4806,10 @@
       <c r="AA22" s="13"/>
       <c r="AB22" s="13"/>
       <c r="AC22" s="13" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AD22" s="21" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="399">
@@ -4767,7 +4817,7 @@
         <v>95</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C23" s="21"/>
       <c r="D23" s="22">
@@ -4807,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T23" s="21"/>
       <c r="U23" s="18"/>
@@ -4821,93 +4871,119 @@
       <c r="AA23" s="21"/>
       <c r="AB23" s="21"/>
       <c r="AC23" s="21" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AD23" s="21" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" ht="409.6">
-      <c r="A24" s="13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="180">
+      <c r="A24" s="40" t="s">
+        <v>502</v>
+      </c>
+      <c r="B24" s="40" t="s">
+        <v>510</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="47">
+        <v>23</v>
+      </c>
+      <c r="E24" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14">
-        <v>23</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G24" s="13"/>
-      <c r="H24" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13" t="s">
+      <c r="F24" s="40" t="s">
+        <v>503</v>
+      </c>
+      <c r="G24" s="49" t="s">
+        <v>504</v>
+      </c>
+      <c r="H24" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="I24" s="40" t="s">
+        <v>303</v>
+      </c>
+      <c r="J24" s="40" t="s">
+        <v>505</v>
+      </c>
+      <c r="K24" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="L24" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="M24" s="15">
-        <v>6391</v>
-      </c>
-      <c r="N24" s="15">
-        <v>6391</v>
-      </c>
-      <c r="O24" s="15"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="17">
+      <c r="L24" s="40" t="s">
+        <v>506</v>
+      </c>
+      <c r="M24" s="48">
+        <v>6432</v>
+      </c>
+      <c r="N24" s="48">
+        <v>6432</v>
+      </c>
+      <c r="O24" s="48"/>
+      <c r="P24" s="35">
+        <v>1182.281332</v>
+      </c>
+      <c r="Q24" s="35">
+        <v>577.93346799999995</v>
+      </c>
+      <c r="R24" s="35">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
-      <c r="S24" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="T24" s="13"/>
-      <c r="U24" s="18"/>
-      <c r="V24" s="19">
-        <v>46118</v>
-      </c>
-      <c r="W24" s="19"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="13"/>
-      <c r="Z24" s="13"/>
-      <c r="AA24" s="13"/>
-      <c r="AB24" s="13"/>
-      <c r="AC24" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="AD24" s="21" t="s">
-        <v>328</v>
+        <v>1760.2148</v>
+      </c>
+      <c r="S24" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="T24" s="40">
+        <v>7900</v>
+      </c>
+      <c r="U24" s="50">
+        <v>46630</v>
+      </c>
+      <c r="V24" s="51">
+        <v>46101</v>
+      </c>
+      <c r="W24" s="51">
+        <v>46274</v>
+      </c>
+      <c r="X24" s="51">
+        <v>46304</v>
+      </c>
+      <c r="Y24" s="40" t="s">
+        <v>511</v>
+      </c>
+      <c r="Z24" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA24" s="40" t="s">
+        <v>507</v>
+      </c>
+      <c r="AB24" s="52" t="s">
+        <v>508</v>
+      </c>
+      <c r="AC24" s="40" t="s">
+        <v>512</v>
+      </c>
+      <c r="AD24" s="40" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="409.6">
       <c r="A25" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C25" s="21"/>
       <c r="D25" s="22">
         <v>24</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="23" t="s">
@@ -4937,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T25" s="21"/>
       <c r="U25" s="18"/>
@@ -4951,42 +5027,42 @@
       <c r="AA25" s="21"/>
       <c r="AB25" s="21"/>
       <c r="AC25" s="21" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AD25" s="21" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="256">
       <c r="A26" s="13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D26" s="14">
         <v>25</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K26" s="13" t="s">
         <v>82</v>
@@ -5032,43 +5108,43 @@
         <v>46224</v>
       </c>
       <c r="Y26" s="13" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Z26" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AA26" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="AB26" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AC26" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AD26" s="21"/>
     </row>
     <row r="27" spans="1:30" ht="211">
       <c r="A27" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="B27" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="B27" s="21" t="s">
-        <v>289</v>
-      </c>
       <c r="C27" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D27" s="22">
         <v>26</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H27" s="23" t="s">
         <v>18</v>
@@ -5077,10 +5153,10 @@
         <v>54</v>
       </c>
       <c r="J27" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K27" s="21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L27" s="21" t="s">
         <v>20</v>
@@ -5123,28 +5199,28 @@
         <v>46234</v>
       </c>
       <c r="Y27" s="21" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="Z27" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AA27" s="21" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AB27" s="28" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AC27" s="21" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AD27" s="21"/>
     </row>
     <row r="28" spans="1:30" ht="409.6">
       <c r="A28" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="14">
@@ -5154,7 +5230,7 @@
         <v>52</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G28" s="13"/>
       <c r="H28" s="15" t="s">
@@ -5184,7 +5260,7 @@
         <v>0</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T28" s="13"/>
       <c r="U28" s="18"/>
@@ -5198,31 +5274,31 @@
       <c r="AA28" s="13"/>
       <c r="AB28" s="13"/>
       <c r="AC28" s="13" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AD28" s="21" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="241">
       <c r="A29" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B29" s="21" t="s">
         <v>256</v>
-      </c>
-      <c r="B29" s="21" t="s">
-        <v>258</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="22">
         <v>28</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H29" s="23" t="s">
         <v>18</v>
@@ -5231,7 +5307,7 @@
         <v>54</v>
       </c>
       <c r="J29" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K29" s="21" t="s">
         <v>56</v>
@@ -5277,52 +5353,52 @@
         <v>46232</v>
       </c>
       <c r="Y29" s="21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Z29" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AA29" s="21" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AB29" s="25" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AC29" s="21" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AD29" s="21"/>
     </row>
     <row r="30" spans="1:30" ht="241">
       <c r="A30" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D30" s="14">
         <v>29</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>18</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K30" s="13" t="s">
         <v>24</v>
@@ -5369,45 +5445,45 @@
         <v>46233</v>
       </c>
       <c r="Y30" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="Z30" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA30" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB30" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="AC30" s="13" t="s">
         <v>275</v>
-      </c>
-      <c r="Z30" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA30" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="AB30" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="AC30" s="13" t="s">
-        <v>277</v>
       </c>
       <c r="AD30" s="21"/>
     </row>
     <row r="31" spans="1:30" ht="329">
       <c r="A31" s="13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C31" s="13"/>
       <c r="D31" s="22">
         <v>30</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="F31" s="29" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G31" s="13"/>
       <c r="H31" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J31" s="13"/>
       <c r="K31" s="13" t="s">
@@ -5430,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="S31" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T31" s="13"/>
       <c r="U31" s="18"/>
@@ -5444,21 +5520,21 @@
       <c r="AA31" s="13"/>
       <c r="AB31" s="13"/>
       <c r="AC31" s="13" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AD31" s="21" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="106">
       <c r="A32" s="13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D32" s="14">
         <v>31</v>
@@ -5470,7 +5546,7 @@
         <v>74</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>18</v>
@@ -5479,7 +5555,7 @@
         <v>50</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K32" s="13" t="s">
         <v>24</v>
@@ -5528,22 +5604,22 @@
         <v>75</v>
       </c>
       <c r="Z32" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AA32" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AB32" s="20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AC32" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AD32" s="21"/>
     </row>
     <row r="33" spans="1:30" ht="31">
       <c r="A33" s="21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -5551,10 +5627,10 @@
         <v>32</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G33" s="21"/>
       <c r="H33" s="23" t="s">
@@ -5584,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="T33" s="21"/>
       <c r="U33" s="18"/>
@@ -5598,46 +5674,46 @@
       <c r="AA33" s="21"/>
       <c r="AB33" s="21"/>
       <c r="AC33" s="21" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AD33" s="21"/>
     </row>
     <row r="34" spans="1:30" ht="121">
       <c r="A34" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="B34" s="21" t="s">
         <v>464</v>
       </c>
-      <c r="B34" s="21" t="s">
-        <v>469</v>
-      </c>
       <c r="C34" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D34" s="22">
         <v>33</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F34" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="H34" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="I34" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="J34" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="K34" s="21" t="s">
         <v>465</v>
       </c>
-      <c r="G34" s="21" t="s">
-        <v>466</v>
-      </c>
-      <c r="H34" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="I34" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="J34" s="21" t="s">
-        <v>468</v>
-      </c>
-      <c r="K34" s="21" t="s">
-        <v>470</v>
-      </c>
       <c r="L34" s="13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="M34" s="30">
         <v>365.39866899999998</v>
@@ -5677,28 +5753,28 @@
         <v>46260</v>
       </c>
       <c r="Y34" s="21" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="Z34" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AA34" s="21" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="AB34" s="21" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AC34" s="21" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="AD34" s="21"/>
     </row>
     <row r="35" spans="1:30" ht="409.6">
       <c r="A35" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C35" s="21"/>
       <c r="D35" s="22">
@@ -5708,7 +5784,7 @@
         <v>89</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G35" s="21"/>
       <c r="H35" s="23" t="s">
@@ -5738,7 +5814,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T35" s="21"/>
       <c r="U35" s="18"/>
@@ -5752,48 +5828,48 @@
       <c r="AA35" s="21"/>
       <c r="AB35" s="21"/>
       <c r="AC35" s="21" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AD35" s="21" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="75">
       <c r="A36" s="31" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D36" s="33">
         <v>35</v>
       </c>
       <c r="E36" s="34" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G36" s="32" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="H36" s="34" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I36" s="32" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="J36" s="32" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="K36" s="31" t="s">
         <v>31</v>
       </c>
       <c r="L36" s="32" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="M36" s="34">
         <v>2693</v>
@@ -5833,55 +5909,55 @@
         <v>46272</v>
       </c>
       <c r="Y36" s="31" t="s">
+        <v>473</v>
+      </c>
+      <c r="Z36" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA36" s="32" t="s">
         <v>478</v>
       </c>
-      <c r="Z36" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA36" s="32" t="s">
-        <v>483</v>
-      </c>
       <c r="AB36" s="39" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="AC36" s="31" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AD36" s="40"/>
     </row>
     <row r="37" spans="1:30" ht="166">
       <c r="A37" s="21" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D37" s="22">
         <v>36</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="G37" s="21" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J37" s="21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="K37" s="21" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L37" s="21" t="s">
         <v>11</v>
@@ -5924,19 +6000,19 @@
         <v>46198</v>
       </c>
       <c r="Y37" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="Z37" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA37" s="21" t="s">
+        <v>493</v>
+      </c>
+      <c r="AB37" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="AC37" s="21" t="s">
         <v>241</v>
-      </c>
-      <c r="Z37" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA37" s="21" t="s">
-        <v>498</v>
-      </c>
-      <c r="AB37" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="AC37" s="21" t="s">
-        <v>243</v>
       </c>
       <c r="AD37" s="21"/>
     </row>
@@ -5945,10 +6021,10 @@
         <v>69</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D38" s="14">
         <v>37</v>
@@ -5960,7 +6036,7 @@
         <v>71</v>
       </c>
       <c r="G38" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H38" s="23" t="s">
         <v>18</v>
@@ -5969,7 +6045,7 @@
         <v>54</v>
       </c>
       <c r="J38" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K38" s="21" t="s">
         <v>56</v>
@@ -6018,35 +6094,35 @@
         <v>72</v>
       </c>
       <c r="Z38" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA38" s="21" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AB38" s="28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC38" s="21" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AD38" s="21"/>
     </row>
     <row r="39" spans="1:30" ht="409.6">
       <c r="A39" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="22">
         <v>38</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="G39" s="13"/>
       <c r="H39" s="15" t="s">
@@ -6076,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T39" s="13"/>
       <c r="U39" s="18"/>
@@ -6090,35 +6166,35 @@
       <c r="AA39" s="13"/>
       <c r="AB39" s="13"/>
       <c r="AC39" s="13" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="AD39" s="21" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="385">
       <c r="A40" s="21" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C40" s="21"/>
       <c r="D40" s="14">
         <v>39</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G40" s="21"/>
       <c r="H40" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J40" s="21"/>
       <c r="K40" s="21" t="s">
@@ -6141,7 +6217,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T40" s="21"/>
       <c r="U40" s="18"/>
@@ -6155,35 +6231,35 @@
       <c r="AA40" s="21"/>
       <c r="AB40" s="21"/>
       <c r="AC40" s="21" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="AD40" s="21" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="409.6">
       <c r="A41" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="22">
         <v>40</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="G41" s="21"/>
       <c r="H41" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I41" s="21" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J41" s="21"/>
       <c r="K41" s="21" t="s">
@@ -6206,7 +6282,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T41" s="24"/>
       <c r="U41" s="18"/>
@@ -6220,39 +6296,39 @@
       <c r="AA41" s="21"/>
       <c r="AB41" s="21"/>
       <c r="AC41" s="21" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="AD41" s="25" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="409.6">
       <c r="A42" s="21" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C42" s="21"/>
       <c r="D42" s="22">
         <v>41</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G42" s="21"/>
       <c r="H42" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I42" s="21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J42" s="21"/>
       <c r="K42" s="21" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L42" s="21" t="s">
         <v>11</v>
@@ -6269,7 +6345,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T42" s="23"/>
       <c r="U42" s="18"/>
@@ -6283,40 +6359,40 @@
       <c r="AA42" s="21"/>
       <c r="AB42" s="21"/>
       <c r="AC42" s="21" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AD42" s="21" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="43" spans="1:30" ht="409.6">
       <c r="A43" s="6" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C43" s="6"/>
       <c r="D43" s="7">
         <v>42</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="8" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="J43" s="6"/>
       <c r="K43" s="6" t="s">
         <v>31</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="M43" s="8">
         <v>1341</v>
@@ -6327,7 +6403,7 @@
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
       <c r="S43" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T43" s="8">
         <v>6200</v>
@@ -6343,40 +6419,40 @@
       <c r="AA43" s="6"/>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="AD43" s="6" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="409.6">
       <c r="A44" s="12" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C44" s="12"/>
       <c r="D44" s="12">
         <v>43</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F44" s="12"/>
       <c r="G44" s="12"/>
       <c r="H44" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J44" s="12"/>
       <c r="K44" s="12" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="M44" s="12">
         <v>1200</v>
@@ -6387,7 +6463,7 @@
       <c r="Q44" s="12"/>
       <c r="R44" s="12"/>
       <c r="S44" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T44" s="12"/>
       <c r="U44" s="12"/>
@@ -6401,28 +6477,28 @@
       <c r="AA44" s="12"/>
       <c r="AB44" s="12"/>
       <c r="AC44" s="12" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="AD44" s="12" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="45" spans="1:30" ht="240">
       <c r="A45" s="41" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B45" s="41" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C45" s="41"/>
       <c r="D45" s="42">
         <v>44</v>
       </c>
       <c r="E45" s="43" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="F45" s="41" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="G45" s="41"/>
       <c r="H45" s="43" t="s">
@@ -6436,7 +6512,7 @@
         <v>24</v>
       </c>
       <c r="L45" s="41" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="M45" s="43">
         <v>2437</v>
@@ -6450,7 +6526,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="41" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T45" s="41"/>
       <c r="U45" s="45"/>
@@ -6462,10 +6538,10 @@
       <c r="AA45" s="41"/>
       <c r="AB45" s="41"/>
       <c r="AC45" s="41" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="AD45" s="41" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -6494,12 +6570,13 @@
     <hyperlink ref="AB27" r:id="rId21" xr:uid="{C5A97FE8-FC03-4B41-86D8-2D3DFD0E915C}"/>
     <hyperlink ref="AB37" r:id="rId22" xr:uid="{95B4063F-E390-2F4C-97F4-22710E08828D}"/>
     <hyperlink ref="AB36" r:id="rId23" xr:uid="{58EFA9E3-F5DD-7244-B47A-5A35FCC395E1}"/>
+    <hyperlink ref="AB24" r:id="rId24" xr:uid="{8FAD3DFA-392A-1846-AD7B-B2015845524B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId24"/>
-  <legacyDrawing r:id="rId25"/>
+  <drawing r:id="rId25"/>
+  <legacyDrawing r:id="rId26"/>
   <tableParts count="1">
-    <tablePart r:id="rId26"/>
+    <tablePart r:id="rId27"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6519,22 +6596,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32">
       <c r="A1" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16">
@@ -6542,19 +6619,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16">
@@ -6562,19 +6639,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16">
@@ -6582,19 +6659,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16">
@@ -6605,16 +6682,16 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16">
@@ -6625,16 +6702,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16">
@@ -6642,19 +6719,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16">
@@ -6662,19 +6739,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16">
@@ -6685,16 +6762,16 @@
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16">
@@ -6705,16 +6782,16 @@
         <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16">
@@ -6722,19 +6799,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16">
@@ -6745,16 +6822,16 @@
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16">
@@ -6765,16 +6842,16 @@
         <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16">
@@ -6782,19 +6859,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16">
@@ -6802,19 +6879,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16">
@@ -6822,19 +6899,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16">
@@ -6842,19 +6919,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16">
@@ -6862,19 +6939,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32">
@@ -6882,19 +6959,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16">
@@ -6902,19 +6979,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16">
@@ -6922,19 +6999,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16">
@@ -6942,19 +7019,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16">
@@ -6965,16 +7042,16 @@
         <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16">
@@ -6982,19 +7059,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16">
@@ -7002,19 +7079,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="16">
@@ -7025,16 +7102,16 @@
         <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="32">
@@ -7042,19 +7119,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16">
@@ -7062,19 +7139,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16">
@@ -7082,19 +7159,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16">
@@ -7102,19 +7179,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16">
@@ -7122,19 +7199,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -7149,13 +7226,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="64">
       <c r="A1" s="4" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16">
@@ -7163,10 +7240,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="48">
@@ -7174,10 +7251,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="112">
@@ -7185,10 +7262,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16">
@@ -7218,10 +7295,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="16">
@@ -7229,10 +7306,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16">
@@ -7262,10 +7339,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16">
@@ -7295,10 +7372,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="64">
@@ -7306,10 +7383,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="64">
@@ -7317,10 +7394,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="96">
@@ -7328,10 +7405,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="96">
@@ -7339,10 +7416,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="96">
@@ -7350,10 +7427,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="48">
@@ -7361,10 +7438,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="64">
@@ -7372,10 +7449,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="80">
@@ -7383,10 +7460,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="32">
@@ -7405,10 +7482,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="32">
@@ -7416,10 +7493,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="32">
@@ -7438,10 +7515,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="64">
@@ -7449,10 +7526,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16">
@@ -7460,10 +7537,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16">
@@ -7471,10 +7548,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="32">
@@ -7482,10 +7559,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/base de datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217E0B12-3668-5849-9BD1-32C9FCFD18AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8D117A-E4BA-A64B-83DE-1C65C25B9F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35760" yWindow="600" windowWidth="33020" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5190,7 +5190,7 @@
         <v>47330</v>
       </c>
       <c r="V27" s="24">
-        <v>45595</v>
+        <v>45978</v>
       </c>
       <c r="W27" s="24">
         <v>46185</v>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/base de datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8D117A-E4BA-A64B-83DE-1C65C25B9F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F104212-E614-8743-9668-39DE40512F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35760" yWindow="600" windowWidth="33020" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2920" yWindow="600" windowWidth="65860" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="7" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="519">
   <si>
     <t>id_proyecto</t>
   </si>
@@ -1010,15 +1010,9 @@
     <t>https://www.infobae.com/economia/2026/05/13/el-gobierno-aprobo-el-ingreso-al-rigi-de-la-ampliacion-del-gasoducto-perito-moreno-con-una-inversion-de-usd-550-millones/; https://rionegro.gov.ar/articulo/53275/rio-negro-fortalece-su-rol-en-el-abastecimiento-de-arena-para-vaca-muerta</t>
   </si>
   <si>
-    <t>Desarrollo no convencional de petróleo y gas en los bloques Bajo del Choique–La Invernada, en Vaca Muerta. Contempla la perforación de más de 600 pozos, plantas de procesamiento, ductos e infraestructura asociada, con objetivos de hasta 100.000 barriles diarios de petróleo y 12 millones de m³ diarios de gas.</t>
-  </si>
-  <si>
     <t>Pluspetrol (Argentina); Gas y Petróleo del Neuquén S.A. (Argentina)</t>
   </si>
   <si>
-    <t>Pluspetrol Cuenca Neuquina S.R.L.</t>
-  </si>
-  <si>
     <t>Upstream</t>
   </si>
   <si>
@@ -1587,6 +1581,87 @@
   </si>
   <si>
     <t xml:space="preserve">Automotriz </t>
+  </si>
+  <si>
+    <t>Pampa Exploración S.A.</t>
+  </si>
+  <si>
+    <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
+  </si>
+  <si>
+    <t>NGEx Minerals Ltd. (Canadá)</t>
+  </si>
+  <si>
+    <t>Departamento Iglesia; Distrito Vicuña</t>
+  </si>
+  <si>
+    <t>https://ngexminerals.com/news/ngex-releases-2025-sustainability-summary-122811/; https://www.panorama-minero.com/es/mining-compendium/argentina/project/lunahuasi</t>
+  </si>
+  <si>
+    <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
+  </si>
+  <si>
+    <t>UT RIGI LOS TOLDOS</t>
+  </si>
+  <si>
+    <t>Tecpetrol S.A. Gas y Petróleo del Neuquén S.A. UT RIGI Los Toldos U.T.E.</t>
+  </si>
+  <si>
+    <t>33-71889684-9</t>
+  </si>
+  <si>
+    <t>Explotación y producción de nuevos desarrollos de hidrocarburos líquidos y gaseosos costa adentro</t>
+  </si>
+  <si>
+    <t>Departamento Pehuenches; área Los Toldos II Este; Engolfamiento/Bajo de Añelo</t>
+  </si>
+  <si>
+    <t>La resolución establece que la primera etapa comenzó el 01/11/2024, antes de la presentación y aprobación RIGI.</t>
+  </si>
+  <si>
+    <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/348768/20261009</t>
+  </si>
+  <si>
+    <t>https://www.argentina.gob.ar/normativa/nacional/norma-431089 ; https://www.tecpetrol.com/es/noticias/2026/rigi-los-toldos-ii-este</t>
+  </si>
+  <si>
+    <t>Desarrollo de hidrocarburos en el área Los Toldos II Este, Vaca Muerta, el cual consiste en la perforación de 380 pozos junto con su infraestructura asociada para el tratamiento de la producción por una capacidad máxima de 70 mil barriles de petróleo diarios. El proyecto prevé un total de 360 millones de barriles de petróleo de exportación durante su operación.</t>
+  </si>
+  <si>
+    <t>Res. 1771/2026</t>
+  </si>
+  <si>
+    <t>Res. 1771/2026; Tecpetrol</t>
+  </si>
+  <si>
+    <t>Exploración, producción, tratamiento y transporte de hidrocarburos en un área aproximada de 400 km² del centro-norte de Neuquén. El alcance comprende 620 pozos horizontales, cuatro plantas de tratamiento temprano (EPF), un oleoducto de 45 km y un gasoducto de 20 km, con capacidad total de 100.000 barriles diarios de petróleo y 12 millones de Sm³ diarios de gas. La primera etapa prevé 206 pozos y las EPF 1 y 2; la segunda, 414 pozos y las EPF 3 y 4.</t>
+  </si>
+  <si>
+    <t>Gas y Petróleo del Neuquén S.A. - Pluspetrol Cuenca Neuquina S.R.L. – Unión Transitoria Exploración y Producción Bajo del Choique – La Invernada</t>
+  </si>
+  <si>
+    <t>30-71920381-3</t>
+  </si>
+  <si>
+    <t>Explotación y producción de nuevos desarrollos de hidrocarburos líquidos y gaseosos costa adentro, con instalaciones complementarias de tratamiento y transporte</t>
+  </si>
+  <si>
+    <t>Centro-norte de Neuquén, aproximadamente 40 km al sur de Rincón de los Sauces; Hub Norte de la Cuenca Neuquina</t>
+  </si>
+  <si>
+    <t>La primera etapa comenzó el 22/05/2025, once meses antes de la presentación al RIGI del 23/04/2026; por ello existe preexistencia según la cronología consignada en la resolución.</t>
+  </si>
+  <si>
+    <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349233/20261019</t>
+  </si>
+  <si>
+    <t>https://www.argentina.gob.ar/normativa/nacional/norma-431356; https://www.neuqueninforma.gob.ar/noticias/2026/10/19/265814-vaca-muerta-acelera-su-expansion-aprobaron-el-ingreso-al-rigi-de-un-proyecto-de-12-mil-millones-de-dolares; https://www.casarosada.gob.ar/informacion/conferencias/51404-conferencia-de-prensa-del-vocero-presidencial-adrian-ravier-desde-casa-rosada-19-10-2026</t>
+  </si>
+  <si>
+    <t>Res. 1808/2026</t>
+  </si>
+  <si>
+    <t>Res. 1808/2026; Gobierno de la Provincia del Neuquén; Casa Rosada</t>
   </si>
   <si>
     <r>
@@ -1595,79 +1670,24 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </rPr>
       <t>Hilli Episeyo</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </rPr>
       <t xml:space="preserve"> en Argentina.</t>
     </r>
-  </si>
-  <si>
-    <t>Pampa Exploración S.A.</t>
-  </si>
-  <si>
-    <t>Desarrollo del depósito Lunahuasi de cobre, oro y plata, actualmente en exploración, con perforaciones y una galería de exploración planificada para avanzar hacia su desarrollo minero</t>
-  </si>
-  <si>
-    <t>NGEx Minerals Ltd. (Canadá)</t>
-  </si>
-  <si>
-    <t>Departamento Iglesia; Distrito Vicuña</t>
-  </si>
-  <si>
-    <t>https://ngexminerals.com/news/ngex-releases-2025-sustainability-summary-122811/; https://www.panorama-minero.com/es/mining-compendium/argentina/project/lunahuasi</t>
-  </si>
-  <si>
-    <t>NGEx Minerals, 14/05/2026; Panorama Minero, consulta 02/10/2026</t>
-  </si>
-  <si>
-    <t>Globaris; Gobierno de Neuquén; EconoJournal; Luis Caputo; Clarín; La Nación; Bloomberg</t>
-  </si>
-  <si>
-    <t>https://www.neuqueninforma.gob.ar/noticias/2026/04/23/256641-neuquen-suma-un-nuevo-megaproyecto-al-rigi-con-apoyo-de-gyp; https://econojournal.com.ar/oilgas/pluspetrol-solicito-la-adhesion-al-rigi-para-el-bloque-bajo-del-choique-la-invernada-con-una-inversion-de-us12-000-millones/; https://x.com/LuisCaputoAR/status/2047621135127269495; https://www.clarin.com/economia/rigi-vaca-muerta-pluspetrol-presento-inversiones-us-12000-millones-campo-compro-exxon_0_gYALiNgXD0.html; https://www.lanacion.com.ar/economia/pluspetrol-y-gyp-obtuvieron-el-rigi-para-un-proyecto-de-us12400-millones-en-vaca-muerta-nid02102026/; https://www.bloomberglinea.com/latinoamerica/argentina/pluspetrol-recibe-luz-verde-del-rigi-para-invertir-us12400-millones-en-vaca-muerta/</t>
-  </si>
-  <si>
-    <t>UT RIGI LOS TOLDOS</t>
-  </si>
-  <si>
-    <t>Tecpetrol S.A. Gas y Petróleo del Neuquén S.A. UT RIGI Los Toldos U.T.E.</t>
-  </si>
-  <si>
-    <t>33-71889684-9</t>
-  </si>
-  <si>
-    <t>Explotación y producción de nuevos desarrollos de hidrocarburos líquidos y gaseosos costa adentro</t>
-  </si>
-  <si>
-    <t>Departamento Pehuenches; área Los Toldos II Este; Engolfamiento/Bajo de Añelo</t>
-  </si>
-  <si>
-    <t>La resolución establece que la primera etapa comenzó el 01/11/2024, antes de la presentación y aprobación RIGI.</t>
-  </si>
-  <si>
-    <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/348768/20261009</t>
-  </si>
-  <si>
-    <t>https://www.argentina.gob.ar/normativa/nacional/norma-431089 ; https://www.tecpetrol.com/es/noticias/2026/rigi-los-toldos-ii-este</t>
-  </si>
-  <si>
-    <t>Desarrollo de hidrocarburos en el área Los Toldos II Este, Vaca Muerta, el cual consiste en la perforación de 380 pozos junto con su infraestructura asociada para el tratamiento de la producción por una capacidad máxima de 70 mil barriles de petróleo diarios. El proyecto prevé un total de 360 millones de barriles de petróleo de exportación durante su operación.</t>
-  </si>
-  <si>
-    <t>Res. 1771/2026</t>
-  </si>
-  <si>
-    <t>Res. 1771/2026; Tecpetrol</t>
   </si>
 </sst>
 </file>
@@ -1678,9 +1698,9 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1729,29 +1749,48 @@
       <name val="Carlito"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2937"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <u/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1788,7 +1827,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1811,6 +1850,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1818,7 +1866,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1835,6 +1883,48 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1847,97 +1937,7 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1955,25 +1955,49 @@
     <xf numFmtId="14" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1991,11 +2015,27 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/m/yy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2006,12 +2046,13 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
+      <numFmt numFmtId="19" formatCode="d/m/yy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2021,12 +2062,13 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
+      <numFmt numFmtId="19" formatCode="d/m/yy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2036,104 +2078,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <numFmt numFmtId="19" formatCode="d/m/yy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2145,11 +2094,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2160,11 +2109,114 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2179,11 +2231,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0000"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2199,11 +2251,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0000"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2219,11 +2271,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0000"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2235,11 +2287,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2251,11 +2303,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2267,11 +2319,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2283,11 +2335,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2298,11 +2350,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2313,11 +2365,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2328,11 +2380,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2343,11 +2395,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2359,11 +2411,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2374,11 +2426,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2389,11 +2441,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2405,11 +2457,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2421,11 +2473,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2436,11 +2488,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2451,26 +2503,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2480,9 +2517,6 @@
           <color theme="1"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2725,44 +2759,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7BB49DC-9D24-614F-848B-0F39C691B2B5}" name="Tabla22" displayName="Tabla22" ref="A1:AD45" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7BB49DC-9D24-614F-848B-0F39C691B2B5}" name="Tabla22" displayName="Tabla22" ref="A1:AD45" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" headerRowBorderDxfId="32">
   <autoFilter ref="A1:AD45" xr:uid="{C7BB49DC-9D24-614F-848B-0F39C691B2B5}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC41">
     <sortCondition ref="D1:D41"/>
   </sortState>
   <tableColumns count="30">
-    <tableColumn id="1" xr3:uid="{B0F75E5C-946A-644E-9EB4-93643A1ADB1D}" name="vpu" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{0955A7C4-B25E-574D-B27D-1FB04B3EECF0}" name="descripcion_proyecto" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{A18EE10B-7E84-2240-B4D3-1E345824A440}" name="peelp" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{16CBA668-029E-7948-A2E2-792901752FC7}" name="id_proyecto" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{0533A60E-9F7B-384C-8E9E-AF9F698F8BC8}" name="empresa" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{E1AB486A-B757-314A-924B-58FCED818ED9}" name="titular_proyecto" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{248B94B7-B222-6040-A333-51F513C1F6ED}" name="cuit" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{AD5B6DCF-9CBB-3846-858D-9D3985C6A3E4}" name="sector" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{4CA252E5-23F1-474A-A9B5-8A0EDF3EAF49}" name="subsector" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{F8D93550-E6F5-114D-949F-487B7BFA388C}" name="actividad_subsector_resolucion_mecon" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{1475CC17-5B24-3247-8DBA-0625A938B1B7}" name="provincia" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{47AF60A5-F6B3-8743-8C92-1EB7255A904F}" name="localidad_region" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{75050396-7FEE-5341-9B55-07F221AA6F90}" name="inversion_total_mill_usd" dataDxfId="17"/>
-    <tableColumn id="14" xr3:uid="{A7D4770F-B48F-9443-B4A0-4629A448E999}" name="inversion_total_resolucion_mill_usd" dataDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{1602558E-3054-8C4C-9A58-AB8CCCD77682}" name="inversion_activos_computables_mill_usd" dataDxfId="15"/>
-    <tableColumn id="28" xr3:uid="{87595E4D-D42F-354A-9940-89724D3641FE}" name="inversion_activos_computables_comprometida_anio_1_mill_usd" dataDxfId="14"/>
-    <tableColumn id="29" xr3:uid="{688CE13F-074F-304D-836A-8560E747EB65}" name="inversion_activos_computables_comprometida_anio_2_mill_usd" dataDxfId="13"/>
-    <tableColumn id="30" xr3:uid="{B6018A02-36C0-DD40-A886-EEE247A26505}" name="inversion_activos_computables_comprometida_2_anios_mill_usd" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{B0F75E5C-946A-644E-9EB4-93643A1ADB1D}" name="vpu" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{0955A7C4-B25E-574D-B27D-1FB04B3EECF0}" name="descripcion_proyecto" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{A18EE10B-7E84-2240-B4D3-1E345824A440}" name="peelp" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{16CBA668-029E-7948-A2E2-792901752FC7}" name="id_proyecto" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{0533A60E-9F7B-384C-8E9E-AF9F698F8BC8}" name="empresa" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{E1AB486A-B757-314A-924B-58FCED818ED9}" name="titular_proyecto" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{248B94B7-B222-6040-A333-51F513C1F6ED}" name="cuit" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{AD5B6DCF-9CBB-3846-858D-9D3985C6A3E4}" name="sector" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{4CA252E5-23F1-474A-A9B5-8A0EDF3EAF49}" name="subsector" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{F8D93550-E6F5-114D-949F-487B7BFA388C}" name="actividad_subsector_resolucion_mecon" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{1475CC17-5B24-3247-8DBA-0625A938B1B7}" name="provincia" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{47AF60A5-F6B3-8743-8C92-1EB7255A904F}" name="localidad_region" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{75050396-7FEE-5341-9B55-07F221AA6F90}" name="inversion_total_mill_usd" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{A7D4770F-B48F-9443-B4A0-4629A448E999}" name="inversion_total_resolucion_mill_usd" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{1602558E-3054-8C4C-9A58-AB8CCCD77682}" name="inversion_activos_computables_mill_usd" dataDxfId="17"/>
+    <tableColumn id="28" xr3:uid="{87595E4D-D42F-354A-9940-89724D3641FE}" name="inversion_activos_computables_comprometida_anio_1_mill_usd" dataDxfId="16"/>
+    <tableColumn id="29" xr3:uid="{688CE13F-074F-304D-836A-8560E747EB65}" name="inversion_activos_computables_comprometida_anio_2_mill_usd" dataDxfId="15"/>
+    <tableColumn id="30" xr3:uid="{B6018A02-36C0-DD40-A886-EEE247A26505}" name="inversion_activos_computables_comprometida_2_anios_mill_usd" dataDxfId="14">
       <calculatedColumnFormula>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D9B1B5B6-782F-2243-91BD-908F3BAD2DE1}" name="estado_administrativo" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{03E27E62-7FEF-084F-B60F-9D8063323ACC}" name="empleos_directos_indirectos_informados" dataDxfId="10"/>
-    <tableColumn id="27" xr3:uid="{D7C6BCCC-1B44-1443-8A03-2D0A63BC3776}" name="fecha_limite_inversion_minima_activos_computables" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{8E1C53B8-81DA-0043-91C5-F9A87892E325}" name="fecha_presentacion" dataDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{2487DCCA-74EE-1743-B2CF-7169CF1BEBD2}" name="fecha_adhesion_rigi" dataDxfId="7"/>
-    <tableColumn id="20" xr3:uid="{51CF8FC1-2018-404C-A94F-1B1821BFB436}" name="fecha_publicacion_bo" dataDxfId="6"/>
-    <tableColumn id="21" xr3:uid="{57FDDB6F-D25E-3742-BBE3-196B6D307586}" name="norma_aprobacion" dataDxfId="5"/>
-    <tableColumn id="22" xr3:uid="{5FB062D4-AACF-864F-BFDC-22BF7798BAE5}" name="clasificacion_preexistencia_boletin_oficial" dataDxfId="4"/>
-    <tableColumn id="23" xr3:uid="{2371D7C3-27BF-8B4D-9413-38667163C45E}" name="justificacion_preexistencia_boletin_oficial" dataDxfId="3"/>
-    <tableColumn id="24" xr3:uid="{6EB99972-175D-EC4A-8EB6-3F4E07EFB52D}" name="link_norma" dataDxfId="2"/>
-    <tableColumn id="25" xr3:uid="{968AE59F-CF82-D848-82E7-EE1B09768E94}" name="fuentes" dataDxfId="1"/>
-    <tableColumn id="26" xr3:uid="{254939B9-204E-4D4D-9217-E3D8F271ED16}" name="links_fuentes" dataDxfId="0"/>
+    <tableColumn id="16" xr3:uid="{D9B1B5B6-782F-2243-91BD-908F3BAD2DE1}" name="estado_administrativo" dataDxfId="13"/>
+    <tableColumn id="17" xr3:uid="{03E27E62-7FEF-084F-B60F-9D8063323ACC}" name="empleos_directos_indirectos_informados" dataDxfId="5"/>
+    <tableColumn id="27" xr3:uid="{D7C6BCCC-1B44-1443-8A03-2D0A63BC3776}" name="fecha_limite_inversion_minima_activos_computables" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{8E1C53B8-81DA-0043-91C5-F9A87892E325}" name="fecha_presentacion" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{2487DCCA-74EE-1743-B2CF-7169CF1BEBD2}" name="fecha_adhesion_rigi" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{51CF8FC1-2018-404C-A94F-1B1821BFB436}" name="fecha_publicacion_bo" dataDxfId="0"/>
+    <tableColumn id="21" xr3:uid="{57FDDB6F-D25E-3742-BBE3-196B6D307586}" name="norma_aprobacion" dataDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{5FB062D4-AACF-864F-BFDC-22BF7798BAE5}" name="clasificacion_preexistencia_boletin_oficial" dataDxfId="12"/>
+    <tableColumn id="23" xr3:uid="{2371D7C3-27BF-8B4D-9413-38667163C45E}" name="justificacion_preexistencia_boletin_oficial" dataDxfId="11"/>
+    <tableColumn id="24" xr3:uid="{6EB99972-175D-EC4A-8EB6-3F4E07EFB52D}" name="link_norma" dataDxfId="10"/>
+    <tableColumn id="25" xr3:uid="{968AE59F-CF82-D848-82E7-EE1B09768E94}" name="fuentes" dataDxfId="9"/>
+    <tableColumn id="26" xr3:uid="{254939B9-204E-4D4D-9217-E3D8F271ED16}" name="links_fuentes" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2974,11 +3008,11 @@
     <col min="10" max="10" width="36.6640625" customWidth="1"/>
     <col min="11" max="11" width="11.1640625" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
-    <col min="14" max="14" width="37.1640625" customWidth="1"/>
-    <col min="15" max="15" width="30" customWidth="1"/>
-    <col min="16" max="16" width="32.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="30" customWidth="1"/>
+    <col min="13" max="13" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="53.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="54.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="21.33203125" customWidth="1"/>
     <col min="20" max="21" width="28" customWidth="1"/>
     <col min="22" max="22" width="19" customWidth="1"/>
@@ -2990,3558 +3024,3582 @@
     <col min="28" max="28" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="32">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:30" ht="34">
+      <c r="A1" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="K1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="U1" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="V1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="W1" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="X1" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="102">
+      <c r="A2" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" s="15">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" ht="91">
-      <c r="A2" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="D2" s="14">
-        <v>1</v>
-      </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="M2" s="15">
+      <c r="M2" s="16">
         <v>550</v>
       </c>
-      <c r="N2" s="15">
+      <c r="N2" s="16">
         <v>550</v>
       </c>
-      <c r="O2" s="15">
+      <c r="O2" s="16">
         <v>513</v>
       </c>
-      <c r="P2" s="16">
+      <c r="P2" s="10">
         <v>393.61748899999998</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="Q2" s="10">
         <v>30.575689000000001</v>
       </c>
       <c r="R2" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>424.19317799999999</v>
       </c>
-      <c r="S2" s="13" t="s">
+      <c r="S2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T2" s="13">
+      <c r="T2" s="14">
         <v>7535</v>
       </c>
       <c r="U2" s="18">
         <v>46387</v>
       </c>
-      <c r="V2" s="19">
+      <c r="V2" s="40">
         <v>45957</v>
       </c>
-      <c r="W2" s="19">
+      <c r="W2" s="40">
         <v>46142</v>
       </c>
-      <c r="X2" s="19">
+      <c r="X2" s="40">
         <v>46154</v>
       </c>
-      <c r="Y2" s="13" t="s">
+      <c r="Y2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="Z2" s="13" t="s">
+      <c r="Z2" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="AA2" s="13" t="s">
+      <c r="AA2" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="AB2" s="20" t="s">
+      <c r="AB2" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="AC2" s="13" t="s">
+      <c r="AC2" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="AD2" s="21"/>
-    </row>
-    <row r="3" spans="1:30" ht="76">
-      <c r="A3" s="21" t="s">
+      <c r="AD2" s="6"/>
+    </row>
+    <row r="3" spans="1:30" ht="102">
+      <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="7">
         <v>2</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="K3" s="21" t="s">
+      <c r="K3" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="L3" s="21" t="s">
+      <c r="L3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="8">
         <v>764</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="8">
         <v>482</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="8">
         <v>482</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="10">
         <v>98.5</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="10">
         <v>253.9</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>352.4</v>
       </c>
-      <c r="S3" s="21" t="s">
+      <c r="S3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T3" s="21">
+      <c r="T3" s="6">
         <v>2013</v>
       </c>
       <c r="U3" s="18">
         <v>46721</v>
       </c>
-      <c r="V3" s="24">
+      <c r="V3" s="18">
         <v>45981</v>
       </c>
-      <c r="W3" s="24">
+      <c r="W3" s="18">
         <v>46080</v>
       </c>
-      <c r="X3" s="24">
+      <c r="X3" s="18">
         <v>46149</v>
       </c>
-      <c r="Y3" s="21" t="s">
+      <c r="Y3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="21" t="s">
+      <c r="Z3" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AA3" s="21" t="s">
+      <c r="AA3" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="AB3" s="25" t="s">
+      <c r="AB3" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="AC3" s="21" t="s">
+      <c r="AC3" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="AD3" s="21"/>
-    </row>
-    <row r="4" spans="1:30" ht="91">
-      <c r="A4" s="21" t="s">
+      <c r="AD3" s="6"/>
+    </row>
+    <row r="4" spans="1:30" ht="102">
+      <c r="A4" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="15">
         <v>3</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="L4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="8">
         <v>665</v>
       </c>
-      <c r="N4" s="23">
+      <c r="N4" s="8">
         <v>520</v>
       </c>
-      <c r="O4" s="23">
+      <c r="O4" s="8">
         <v>520</v>
       </c>
-      <c r="P4" s="16">
+      <c r="P4" s="10">
         <v>46.741253999999998</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="Q4" s="10">
         <v>43.858696000000002</v>
       </c>
-      <c r="R4" s="16">
+      <c r="R4" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>90.599950000000007</v>
       </c>
-      <c r="S4" s="21" t="s">
+      <c r="S4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="21">
+      <c r="T4" s="6">
         <v>4500</v>
       </c>
       <c r="U4" s="18">
         <v>47118</v>
       </c>
-      <c r="V4" s="24">
+      <c r="V4" s="18">
         <v>45814</v>
       </c>
-      <c r="W4" s="24">
+      <c r="W4" s="18">
         <v>45988</v>
       </c>
-      <c r="X4" s="24">
+      <c r="X4" s="18">
         <v>46035</v>
       </c>
-      <c r="Y4" s="21" t="s">
+      <c r="Y4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Z4" s="21" t="s">
+      <c r="Z4" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AA4" s="21" t="s">
+      <c r="AA4" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="AB4" s="25" t="s">
+      <c r="AB4" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="AC4" s="21" t="s">
+      <c r="AC4" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="AD4" s="21"/>
-    </row>
-    <row r="5" spans="1:30" ht="211">
-      <c r="A5" s="21" t="s">
+      <c r="AD4" s="6"/>
+    </row>
+    <row r="5" spans="1:30" ht="238">
+      <c r="A5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="7">
         <v>4</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="21" t="s">
+      <c r="K5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="L5" s="21" t="s">
+      <c r="L5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="8">
         <v>276</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="8">
         <v>276</v>
       </c>
-      <c r="O5" s="23">
+      <c r="O5" s="8">
         <v>255</v>
       </c>
-      <c r="P5" s="16">
+      <c r="P5" s="10">
         <v>80.371903000000003</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="Q5" s="10">
         <v>136.091475</v>
       </c>
-      <c r="R5" s="16">
+      <c r="R5" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>216.46337800000001</v>
       </c>
-      <c r="S5" s="21" t="s">
+      <c r="S5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="21">
+      <c r="T5" s="6">
         <v>165</v>
       </c>
       <c r="U5" s="18">
         <v>46721</v>
       </c>
-      <c r="V5" s="24">
+      <c r="V5" s="18">
         <v>45656</v>
       </c>
-      <c r="W5" s="24">
+      <c r="W5" s="18">
         <v>45863</v>
       </c>
-      <c r="X5" s="24">
+      <c r="X5" s="18">
         <v>45895</v>
       </c>
-      <c r="Y5" s="21" t="s">
+      <c r="Y5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="Z5" s="21" t="s">
+      <c r="Z5" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AA5" s="21" t="s">
+      <c r="AA5" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="AB5" s="25" t="s">
+      <c r="AB5" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="AC5" s="21" t="s">
+      <c r="AC5" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="AD5" s="21"/>
-    </row>
-    <row r="6" spans="1:30" ht="91">
-      <c r="A6" s="13" t="s">
+      <c r="AD5" s="6"/>
+    </row>
+    <row r="6" spans="1:30" ht="102">
+      <c r="A6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="15">
         <v>5</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="F6" s="13" t="s">
+      <c r="E6" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13" t="s">
+      <c r="J6" s="14"/>
+      <c r="K6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="16">
         <v>211</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="16">
         <v>212</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="16">
         <v>212</v>
       </c>
-      <c r="P6" s="16">
+      <c r="P6" s="10">
         <f>Tabla22[[#This Row],[inversion_activos_computables_comprometida_2_anios_mill_usd]]/2</f>
         <v>102.27200000000001</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="Q6" s="10">
         <f>Tabla22[[#This Row],[inversion_activos_computables_comprometida_2_anios_mill_usd]]/2</f>
         <v>102.27200000000001</v>
       </c>
-      <c r="R6" s="16">
+      <c r="R6" s="10">
         <v>204.54400000000001</v>
       </c>
-      <c r="S6" s="13" t="s">
+      <c r="S6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T6" s="13">
+      <c r="T6" s="14">
         <v>384</v>
       </c>
       <c r="U6" s="18">
         <v>46417</v>
       </c>
-      <c r="V6" s="19">
+      <c r="V6" s="40">
         <v>45590</v>
       </c>
-      <c r="W6" s="19">
+      <c r="W6" s="40">
         <v>45642</v>
       </c>
-      <c r="X6" s="19">
+      <c r="X6" s="40">
         <v>45664</v>
       </c>
-      <c r="Y6" s="13" t="s">
+      <c r="Y6" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="Z6" s="13" t="s">
+      <c r="Z6" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="AA6" s="13" t="s">
+      <c r="AA6" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="AB6" s="20" t="s">
+      <c r="AB6" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="AC6" s="13" t="s">
+      <c r="AC6" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="AD6" s="21"/>
-    </row>
-    <row r="7" spans="1:30" ht="181">
-      <c r="A7" s="13" t="s">
+      <c r="AD6" s="6"/>
+    </row>
+    <row r="7" spans="1:30" ht="221">
+      <c r="A7" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="7">
         <v>6</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="16">
         <v>15156</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="16">
         <v>6878</v>
       </c>
-      <c r="O7" s="15">
+      <c r="O7" s="16">
         <v>2825</v>
       </c>
-      <c r="P7" s="16">
+      <c r="P7" s="10">
         <v>105</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="10">
         <v>354</v>
       </c>
       <c r="R7" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>459</v>
       </c>
-      <c r="S7" s="13" t="s">
+      <c r="S7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T7" s="13">
+      <c r="T7" s="14">
         <v>836</v>
       </c>
       <c r="U7" s="18">
         <v>49674</v>
       </c>
-      <c r="V7" s="19">
+      <c r="V7" s="40">
         <v>45617</v>
       </c>
-      <c r="W7" s="19">
+      <c r="W7" s="40">
         <v>45775</v>
       </c>
-      <c r="X7" s="19">
+      <c r="X7" s="40">
         <v>45776</v>
       </c>
-      <c r="Y7" s="13" t="s">
+      <c r="Y7" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="Z7" s="13" t="s">
+      <c r="Z7" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="AA7" s="13" t="s">
+      <c r="AA7" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="AB7" s="26" t="s">
+      <c r="AB7" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="AC7" s="13" t="s">
+      <c r="AC7" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="AD7" s="21"/>
-    </row>
-    <row r="8" spans="1:30" ht="121">
-      <c r="A8" s="21" t="s">
+      <c r="AD7" s="6"/>
+    </row>
+    <row r="8" spans="1:30" ht="153">
+      <c r="A8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="15">
         <v>7</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="K8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="21" t="s">
+      <c r="L8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="8">
         <v>286</v>
       </c>
-      <c r="N8" s="23">
+      <c r="N8" s="8">
         <v>286</v>
       </c>
-      <c r="O8" s="23">
+      <c r="O8" s="8">
         <v>286</v>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="10">
         <v>142.874</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="10">
         <v>127.334</v>
       </c>
-      <c r="R8" s="16">
+      <c r="R8" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>270.20799999999997</v>
       </c>
-      <c r="S8" s="21" t="s">
+      <c r="S8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T8" s="21">
+      <c r="T8" s="6">
         <v>3800</v>
       </c>
       <c r="U8" s="18">
         <v>46326</v>
       </c>
-      <c r="V8" s="24">
+      <c r="V8" s="18">
         <v>45638</v>
       </c>
-      <c r="W8" s="24">
+      <c r="W8" s="18">
         <v>45807</v>
       </c>
-      <c r="X8" s="24">
+      <c r="X8" s="18">
         <v>45859</v>
       </c>
-      <c r="Y8" s="21" t="s">
+      <c r="Y8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="Z8" s="21" t="s">
+      <c r="Z8" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AA8" s="21" t="s">
+      <c r="AA8" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="AB8" s="27" t="s">
+      <c r="AB8" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="AC8" s="21" t="s">
+      <c r="AC8" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="AD8" s="21"/>
-    </row>
-    <row r="9" spans="1:30" ht="91">
-      <c r="A9" s="13" t="s">
+      <c r="AD8" s="6"/>
+    </row>
+    <row r="9" spans="1:30" ht="119">
+      <c r="A9" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="7">
         <v>8</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="L9" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="16">
         <v>891</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="16">
         <v>613</v>
       </c>
-      <c r="O9" s="15">
+      <c r="O9" s="16">
         <v>613</v>
       </c>
-      <c r="P9" s="16">
+      <c r="P9" s="10">
         <v>40.542000000000002</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9" s="10">
         <v>148.056566</v>
       </c>
       <c r="R9" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>188.59856600000001</v>
       </c>
-      <c r="S9" s="13" t="s">
+      <c r="S9" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T9" s="13">
+      <c r="T9" s="14">
         <v>6300</v>
       </c>
       <c r="U9" s="18">
         <v>46997</v>
       </c>
-      <c r="V9" s="19">
+      <c r="V9" s="40">
         <v>45967</v>
       </c>
-      <c r="W9" s="19">
+      <c r="W9" s="40">
         <v>46155</v>
       </c>
-      <c r="X9" s="19">
+      <c r="X9" s="40">
         <v>46168</v>
       </c>
-      <c r="Y9" s="13" t="s">
+      <c r="Y9" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="Z9" s="13" t="s">
+      <c r="Z9" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="AA9" s="13" t="s">
+      <c r="AA9" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="AB9" s="20" t="s">
+      <c r="AB9" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="AC9" s="13" t="s">
+      <c r="AC9" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="AD9" s="21"/>
-    </row>
-    <row r="10" spans="1:30" ht="106">
-      <c r="A10" s="21" t="s">
+      <c r="AD9" s="6"/>
+    </row>
+    <row r="10" spans="1:30" ht="136">
+      <c r="A10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="15">
         <v>9</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="K10" s="21" t="s">
+      <c r="K10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="L10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="8">
         <v>2744</v>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="8">
         <v>2744</v>
       </c>
-      <c r="O10" s="23">
+      <c r="O10" s="8">
         <v>2299</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="10">
         <v>516.96396300000004</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="10">
         <v>776.54763100000002</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>1293.5115940000001</v>
       </c>
-      <c r="S10" s="21" t="s">
+      <c r="S10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T10" s="21">
+      <c r="T10" s="6">
         <v>1985</v>
       </c>
       <c r="U10" s="18">
         <v>47299</v>
       </c>
-      <c r="V10" s="24">
+      <c r="V10" s="18">
         <v>45713</v>
       </c>
-      <c r="W10" s="24">
+      <c r="W10" s="18">
         <v>45796</v>
       </c>
-      <c r="X10" s="24">
+      <c r="X10" s="18">
         <v>45807</v>
       </c>
-      <c r="Y10" s="21" t="s">
+      <c r="Y10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="Z10" s="21" t="s">
+      <c r="Z10" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="AA10" s="21" t="s">
+      <c r="AA10" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="AB10" s="25" t="s">
+      <c r="AB10" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="AC10" s="21" t="s">
+      <c r="AC10" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="AD10" s="21"/>
-    </row>
-    <row r="11" spans="1:30" ht="226">
-      <c r="A11" s="13" t="s">
+      <c r="AD10" s="6"/>
+    </row>
+    <row r="11" spans="1:30" ht="255">
+      <c r="A11" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="7">
         <v>10</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="16">
         <v>531</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="16">
         <v>251</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11" s="16">
         <v>251</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="10">
         <v>92.662282000000005</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="10">
         <v>0</v>
       </c>
       <c r="R11" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>92.662282000000005</v>
       </c>
-      <c r="S11" s="13" t="s">
+      <c r="S11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T11" s="13">
+      <c r="T11" s="14">
         <v>1273</v>
       </c>
       <c r="U11" s="18">
         <v>46357</v>
       </c>
-      <c r="V11" s="19">
+      <c r="V11" s="40">
         <v>45898</v>
       </c>
-      <c r="W11" s="19">
+      <c r="W11" s="40">
         <v>46106</v>
       </c>
-      <c r="X11" s="19">
+      <c r="X11" s="40">
         <v>46112</v>
       </c>
-      <c r="Y11" s="13" t="s">
+      <c r="Y11" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="Z11" s="13" t="s">
+      <c r="Z11" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="AA11" s="13" t="s">
+      <c r="AA11" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="AB11" s="20" t="s">
+      <c r="AB11" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="AC11" s="13" t="s">
+      <c r="AC11" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="AD11" s="21"/>
-    </row>
-    <row r="12" spans="1:30" ht="106">
-      <c r="A12" s="13" t="s">
+      <c r="AD11" s="6"/>
+    </row>
+    <row r="12" spans="1:30" ht="136">
+      <c r="A12" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="15">
         <v>11</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="16">
         <v>277</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="16">
         <v>277</v>
       </c>
-      <c r="O12" s="15">
+      <c r="O12" s="16">
         <v>277</v>
       </c>
-      <c r="P12" s="16">
+      <c r="P12" s="10">
         <v>91.70244649</v>
       </c>
-      <c r="Q12" s="16">
+      <c r="Q12" s="10">
         <v>74.2</v>
       </c>
       <c r="R12" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>165.90244648999999</v>
       </c>
-      <c r="S12" s="13" t="s">
+      <c r="S12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T12" s="13">
+      <c r="T12" s="14">
         <v>9700</v>
       </c>
       <c r="U12" s="18">
         <v>46478</v>
       </c>
-      <c r="V12" s="19">
+      <c r="V12" s="40">
         <v>45757</v>
       </c>
-      <c r="W12" s="19">
+      <c r="W12" s="40">
         <v>45953</v>
       </c>
-      <c r="X12" s="19">
+      <c r="X12" s="40">
         <v>45980</v>
       </c>
-      <c r="Y12" s="13" t="s">
+      <c r="Y12" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="Z12" s="13" t="s">
+      <c r="Z12" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="AA12" s="13" t="s">
+      <c r="AA12" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="AB12" s="20" t="s">
+      <c r="AB12" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="AC12" s="13" t="s">
+      <c r="AC12" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="AD12" s="21"/>
-    </row>
-    <row r="13" spans="1:30" ht="315">
-      <c r="A13" s="21" t="s">
+      <c r="AD12" s="6"/>
+    </row>
+    <row r="13" spans="1:30" ht="372">
+      <c r="A13" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="7">
         <v>12</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="H13" s="23" t="s">
+      <c r="G13" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I13" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="J13" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="K13" s="21" t="s">
+      <c r="K13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="L13" s="21" t="s">
+      <c r="L13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M13" s="23">
+      <c r="M13" s="8">
         <v>2900</v>
       </c>
-      <c r="N13" s="23">
+      <c r="N13" s="8">
         <v>3050</v>
       </c>
-      <c r="O13" s="23">
+      <c r="O13" s="8">
         <v>2486</v>
       </c>
-      <c r="P13" s="16">
+      <c r="P13" s="10">
         <v>1318</v>
       </c>
-      <c r="Q13" s="16">
+      <c r="Q13" s="10">
         <v>1123</v>
       </c>
-      <c r="R13" s="16">
+      <c r="R13" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>2441</v>
       </c>
-      <c r="S13" s="21" t="s">
+      <c r="S13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T13" s="21">
+      <c r="T13" s="6">
         <v>3108</v>
       </c>
       <c r="U13" s="18">
         <v>47118</v>
       </c>
-      <c r="V13" s="24">
+      <c r="V13" s="18">
         <v>45611</v>
       </c>
-      <c r="W13" s="24">
+      <c r="W13" s="18">
         <v>45722</v>
       </c>
-      <c r="X13" s="24">
+      <c r="X13" s="18">
         <v>45736</v>
       </c>
-      <c r="Y13" s="21" t="s">
+      <c r="Y13" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="Z13" s="21" t="s">
+      <c r="Z13" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AA13" s="21" t="s">
+      <c r="AA13" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="AB13" s="25" t="s">
+      <c r="AB13" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="AC13" s="21" t="s">
+      <c r="AC13" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="AD13" s="21"/>
-    </row>
-    <row r="14" spans="1:30" ht="121">
-      <c r="A14" s="13" t="s">
+      <c r="AD13" s="6"/>
+    </row>
+    <row r="14" spans="1:30" ht="153">
+      <c r="A14" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="15">
         <v>13</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L14" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="16">
         <v>436</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="16">
         <v>380</v>
       </c>
-      <c r="O14" s="15">
+      <c r="O14" s="16">
         <v>380</v>
       </c>
-      <c r="P14" s="16">
+      <c r="P14" s="10">
         <v>79.228583</v>
       </c>
-      <c r="Q14" s="16">
+      <c r="Q14" s="10">
         <v>83.169123999999996</v>
       </c>
       <c r="R14" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>162.397707</v>
       </c>
-      <c r="S14" s="13" t="s">
+      <c r="S14" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T14" s="13">
+      <c r="T14" s="14">
         <v>1048</v>
       </c>
       <c r="U14" s="18">
         <v>47118</v>
       </c>
-      <c r="V14" s="19">
+      <c r="V14" s="40">
         <v>45873</v>
       </c>
-      <c r="W14" s="19">
+      <c r="W14" s="40">
         <v>46050</v>
       </c>
-      <c r="X14" s="19">
+      <c r="X14" s="40">
         <v>46111</v>
       </c>
-      <c r="Y14" s="13" t="s">
+      <c r="Y14" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="Z14" s="13" t="s">
+      <c r="Z14" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="AA14" s="13" t="s">
+      <c r="AA14" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="AB14" s="20" t="s">
+      <c r="AB14" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="AC14" s="13" t="s">
+      <c r="AC14" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="AD14" s="21"/>
+      <c r="AD14" s="6"/>
     </row>
     <row r="15" spans="1:30" ht="409.6">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22">
+      <c r="C15" s="6"/>
+      <c r="D15" s="7">
         <v>14</v>
       </c>
-      <c r="E15" s="21" t="s">
-        <v>457</v>
-      </c>
-      <c r="F15" s="21" t="s">
+      <c r="E15" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="G15" s="21"/>
-      <c r="H15" s="23" t="s">
+      <c r="G15" s="6"/>
+      <c r="H15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="21" t="s">
+      <c r="I15" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21" t="s">
+      <c r="J15" s="6"/>
+      <c r="K15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L15" s="21" t="s">
+      <c r="L15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="23">
+      <c r="M15" s="8">
         <v>726</v>
       </c>
-      <c r="N15" s="23">
+      <c r="N15" s="8">
         <v>726</v>
       </c>
-      <c r="O15" s="23"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16">
+      <c r="O15" s="8"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S15" s="21" t="s">
+      <c r="S15" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="T15" s="21"/>
+      <c r="T15" s="6"/>
       <c r="U15" s="18"/>
-      <c r="V15" s="24">
+      <c r="V15" s="18">
         <v>45671</v>
       </c>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
-      <c r="Y15" s="21"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="21"/>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="21" t="s">
+      <c r="W15" s="18"/>
+      <c r="X15" s="18"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="AD15" s="21" t="s">
+      <c r="AD15" s="6" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="399">
-      <c r="A16" s="13" t="s">
+    <row r="16" spans="1:30" ht="409.6">
+      <c r="A16" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14">
+      <c r="C16" s="14"/>
+      <c r="D16" s="15">
         <v>15</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="15" t="s">
+      <c r="G16" s="14"/>
+      <c r="H16" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="I16" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13" t="s">
+      <c r="J16" s="14"/>
+      <c r="K16" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="L16" s="13" t="s">
+      <c r="L16" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M16" s="15">
+      <c r="M16" s="16">
         <v>232</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16" s="16">
         <v>232</v>
       </c>
-      <c r="O16" s="15"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
       <c r="R16" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S16" s="13" t="s">
+      <c r="S16" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="T16" s="13"/>
+      <c r="T16" s="14"/>
       <c r="U16" s="18"/>
-      <c r="V16" s="19">
+      <c r="V16" s="40">
         <v>45874</v>
       </c>
-      <c r="W16" s="19"/>
-      <c r="X16" s="19"/>
-      <c r="Y16" s="13"/>
-      <c r="Z16" s="13"/>
-      <c r="AA16" s="13"/>
-      <c r="AB16" s="13"/>
-      <c r="AC16" s="13" t="s">
+      <c r="W16" s="40"/>
+      <c r="X16" s="40"/>
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="14"/>
+      <c r="AA16" s="14"/>
+      <c r="AB16" s="14"/>
+      <c r="AC16" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="AD16" s="21" t="s">
+      <c r="AD16" s="6" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="409.6">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="35" t="s">
+        <v>508</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="35">
+        <v>16</v>
+      </c>
+      <c r="E17" s="35" t="s">
         <v>300</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="22">
-        <v>16</v>
-      </c>
-      <c r="E17" s="23" t="s">
+      <c r="F17" s="35" t="s">
+        <v>509</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>510</v>
+      </c>
+      <c r="H17" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="I17" s="35" t="s">
         <v>301</v>
       </c>
-      <c r="F17" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="G17" s="21"/>
-      <c r="H17" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21" t="s">
+      <c r="J17" s="35" t="s">
+        <v>511</v>
+      </c>
+      <c r="K17" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="L17" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="M17" s="23">
-        <v>12400</v>
-      </c>
-      <c r="N17" s="23">
-        <v>12400</v>
-      </c>
-      <c r="O17" s="23"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16">
+      <c r="L17" s="35" t="s">
+        <v>512</v>
+      </c>
+      <c r="M17" s="36">
+        <v>12240</v>
+      </c>
+      <c r="N17" s="36">
+        <v>12240</v>
+      </c>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36">
+        <v>635</v>
+      </c>
+      <c r="Q17" s="36">
+        <v>892</v>
+      </c>
+      <c r="R17" s="36">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
-      <c r="S17" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="T17" s="21">
-        <v>6990</v>
-      </c>
-      <c r="U17" s="18"/>
-      <c r="V17" s="24">
-        <v>45771</v>
-      </c>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
-      <c r="Y17" s="21"/>
-      <c r="Z17" s="21"/>
-      <c r="AA17" s="21"/>
-      <c r="AB17" s="21"/>
-      <c r="AC17" s="21" t="s">
-        <v>500</v>
-      </c>
-      <c r="AD17" s="21" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" ht="106">
-      <c r="A18" s="13" t="s">
+        <v>1527</v>
+      </c>
+      <c r="S17" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="T17" s="35">
+        <v>2301</v>
+      </c>
+      <c r="U17" s="41">
+        <v>47238</v>
+      </c>
+      <c r="V17" s="41">
+        <v>46135</v>
+      </c>
+      <c r="W17" s="41">
+        <v>46275</v>
+      </c>
+      <c r="X17" s="41">
+        <v>46314</v>
+      </c>
+      <c r="Y17" s="35" t="s">
+        <v>516</v>
+      </c>
+      <c r="Z17" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA17" s="35" t="s">
+        <v>513</v>
+      </c>
+      <c r="AB17" s="35" t="s">
+        <v>514</v>
+      </c>
+      <c r="AC17" s="35" t="s">
+        <v>517</v>
+      </c>
+      <c r="AD17" s="35" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="119">
+      <c r="A18" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="C18" s="13" t="s">
+      <c r="B18" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="15">
         <v>17</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="I18" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="K18" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="L18" s="13" t="s">
+      <c r="L18" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="M18" s="15">
+      <c r="M18" s="16">
         <v>1241</v>
       </c>
-      <c r="N18" s="15">
+      <c r="N18" s="16">
         <v>1167</v>
       </c>
-      <c r="O18" s="15">
+      <c r="O18" s="16">
         <v>1167</v>
       </c>
-      <c r="P18" s="16">
+      <c r="P18" s="10">
         <v>37.967590000000001</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="Q18" s="10">
         <v>58.787877000000002</v>
       </c>
       <c r="R18" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>96.75546700000001</v>
       </c>
-      <c r="S18" s="13" t="s">
+      <c r="S18" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T18" s="13">
+      <c r="T18" s="14">
         <v>1787</v>
       </c>
       <c r="U18" s="18">
         <v>47665</v>
       </c>
-      <c r="V18" s="19">
+      <c r="V18" s="40">
         <v>45795</v>
       </c>
-      <c r="W18" s="19">
+      <c r="W18" s="40">
         <v>46151</v>
       </c>
-      <c r="X18" s="19">
+      <c r="X18" s="40">
         <v>46177</v>
       </c>
-      <c r="Y18" s="13" t="s">
+      <c r="Y18" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="Z18" s="13" t="s">
+      <c r="Z18" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="AA18" s="13" t="s">
+      <c r="AA18" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="AB18" s="20" t="s">
+      <c r="AB18" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="AC18" s="13" t="s">
+      <c r="AC18" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="AD18" s="21"/>
+      <c r="AD18" s="6"/>
     </row>
     <row r="19" spans="1:30" ht="409.6">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22">
+      <c r="B19" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7">
         <v>18</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="E19" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="21"/>
-      <c r="H19" s="23" t="s">
+      <c r="G19" s="6"/>
+      <c r="H19" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I19" s="21" t="s">
+      <c r="I19" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="L19" s="21" t="s">
+      <c r="J19" s="6"/>
+      <c r="K19" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M19" s="23">
+      <c r="M19" s="8">
         <v>380</v>
       </c>
-      <c r="N19" s="23">
+      <c r="N19" s="8">
         <v>380</v>
       </c>
-      <c r="O19" s="23"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16">
+      <c r="O19" s="8"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S19" s="21" t="s">
+      <c r="S19" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="T19" s="21"/>
+      <c r="T19" s="6"/>
       <c r="U19" s="18"/>
-      <c r="V19" s="24">
+      <c r="V19" s="18">
         <v>45859</v>
       </c>
-      <c r="W19" s="24"/>
-      <c r="X19" s="24"/>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="21"/>
-      <c r="AB19" s="21"/>
-      <c r="AC19" s="21" t="s">
+      <c r="W19" s="18"/>
+      <c r="X19" s="18"/>
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="6"/>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="AD19" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" ht="409.6">
+      <c r="A20" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="AD19" s="21" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" ht="409.6">
-      <c r="A20" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14">
+      <c r="C20" s="14"/>
+      <c r="D20" s="15">
         <v>19</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="15" t="s">
+      <c r="G20" s="14"/>
+      <c r="H20" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="13" t="s">
+      <c r="I20" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13" t="s">
+      <c r="J20" s="14"/>
+      <c r="K20" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="L20" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M20" s="16">
         <v>9500</v>
       </c>
-      <c r="N20" s="15">
+      <c r="N20" s="16">
         <v>9500</v>
       </c>
-      <c r="O20" s="15"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
       <c r="R20" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S20" s="13" t="s">
+      <c r="S20" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="T20" s="13"/>
+      <c r="T20" s="14"/>
       <c r="U20" s="18"/>
-      <c r="V20" s="19">
+      <c r="V20" s="40">
         <v>45887</v>
       </c>
-      <c r="W20" s="19"/>
-      <c r="X20" s="19"/>
-      <c r="Y20" s="13"/>
-      <c r="Z20" s="13"/>
-      <c r="AA20" s="13"/>
-      <c r="AB20" s="13"/>
-      <c r="AC20" s="13" t="s">
+      <c r="W20" s="40"/>
+      <c r="X20" s="40"/>
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="14"/>
+      <c r="AA20" s="14"/>
+      <c r="AB20" s="14"/>
+      <c r="AC20" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="AD20" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="409.6">
+      <c r="A21" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="AD20" s="21" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" ht="409.6">
-      <c r="A21" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>311</v>
-      </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="22">
+      <c r="C21" s="6"/>
+      <c r="D21" s="7">
         <v>20</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E21" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="G21" s="21"/>
-      <c r="H21" s="23" t="s">
+      <c r="F21" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I21" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21" t="s">
+      <c r="I21" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="L21" s="21" t="s">
+      <c r="L21" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M21" s="23">
+      <c r="M21" s="8">
         <v>13800</v>
       </c>
-      <c r="N21" s="23">
+      <c r="N21" s="8">
         <v>13800</v>
       </c>
-      <c r="O21" s="23"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16">
+      <c r="O21" s="8"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S21" s="21" t="s">
+      <c r="S21" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="T21" s="21"/>
+      <c r="T21" s="6"/>
       <c r="U21" s="18"/>
-      <c r="V21" s="24">
+      <c r="V21" s="18">
         <v>46175</v>
       </c>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="21"/>
-      <c r="Z21" s="21"/>
-      <c r="AA21" s="21"/>
-      <c r="AB21" s="21"/>
-      <c r="AC21" s="21" t="s">
+      <c r="W21" s="18"/>
+      <c r="X21" s="18"/>
+      <c r="Y21" s="6"/>
+      <c r="Z21" s="6"/>
+      <c r="AA21" s="6"/>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="AD21" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" ht="409.6">
+      <c r="A22" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="AD21" s="21" t="s">
+      <c r="C22" s="14"/>
+      <c r="D22" s="15">
+        <v>21</v>
+      </c>
+      <c r="E22" s="16" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="22" spans="1:30" ht="409.6">
-      <c r="A22" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B22" s="13" t="s">
+      <c r="F22" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="14">
-        <v>21</v>
-      </c>
-      <c r="E22" s="15" t="s">
+      <c r="G22" s="14"/>
+      <c r="H22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="L22" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="M22" s="15">
+      <c r="M22" s="16">
         <v>200</v>
       </c>
-      <c r="N22" s="15">
+      <c r="N22" s="16">
         <v>200</v>
       </c>
-      <c r="O22" s="15"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
       <c r="R22" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S22" s="13" t="s">
+      <c r="S22" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="T22" s="13"/>
+      <c r="T22" s="14"/>
       <c r="U22" s="18"/>
-      <c r="V22" s="19" t="s">
+      <c r="V22" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="W22" s="19"/>
-      <c r="X22" s="19"/>
-      <c r="Y22" s="13"/>
-      <c r="Z22" s="13"/>
-      <c r="AA22" s="13"/>
-      <c r="AB22" s="13"/>
-      <c r="AC22" s="13" t="s">
+      <c r="W22" s="40"/>
+      <c r="X22" s="40"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="14"/>
+      <c r="AB22" s="14"/>
+      <c r="AC22" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="AD22" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" ht="409.6">
+      <c r="A23" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="AD22" s="21" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" ht="399">
-      <c r="A23" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="22">
+      <c r="C23" s="6"/>
+      <c r="D23" s="7">
         <v>22</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="F23" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G23" s="21"/>
-      <c r="H23" s="23" t="s">
+      <c r="G23" s="6"/>
+      <c r="H23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I23" s="21" t="s">
+      <c r="I23" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21" t="s">
+      <c r="J23" s="6"/>
+      <c r="K23" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="L23" s="21" t="s">
+      <c r="L23" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="M23" s="23">
+      <c r="M23" s="8">
         <v>206</v>
       </c>
-      <c r="N23" s="23">
+      <c r="N23" s="8">
         <v>206</v>
       </c>
-      <c r="O23" s="23"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16">
+      <c r="O23" s="8"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S23" s="21" t="s">
+      <c r="S23" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="T23" s="21"/>
+      <c r="T23" s="6"/>
       <c r="U23" s="18"/>
-      <c r="V23" s="24">
+      <c r="V23" s="18">
         <v>45805</v>
       </c>
-      <c r="W23" s="24"/>
-      <c r="X23" s="24"/>
-      <c r="Y23" s="21"/>
-      <c r="Z23" s="21"/>
-      <c r="AA23" s="21"/>
-      <c r="AB23" s="21"/>
-      <c r="AC23" s="21" t="s">
-        <v>322</v>
-      </c>
-      <c r="AD23" s="21" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" ht="180">
-      <c r="A24" s="40" t="s">
-        <v>502</v>
-      </c>
-      <c r="B24" s="40" t="s">
-        <v>510</v>
-      </c>
-      <c r="C24" s="40" t="s">
+      <c r="W23" s="18"/>
+      <c r="X23" s="18"/>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="AD23" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="238">
+      <c r="A24" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D24" s="47">
+      <c r="D24" s="7">
         <v>23</v>
       </c>
-      <c r="E24" s="48" t="s">
+      <c r="E24" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="F24" s="40" t="s">
-        <v>503</v>
-      </c>
-      <c r="G24" s="49" t="s">
-        <v>504</v>
-      </c>
-      <c r="H24" s="48" t="s">
+      <c r="F24" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I24" s="40" t="s">
-        <v>303</v>
-      </c>
-      <c r="J24" s="40" t="s">
-        <v>505</v>
-      </c>
-      <c r="K24" s="40" t="s">
+      <c r="I24" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="K24" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="L24" s="40" t="s">
-        <v>506</v>
-      </c>
-      <c r="M24" s="48">
+      <c r="L24" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="M24" s="8">
         <v>6432</v>
       </c>
-      <c r="N24" s="48">
+      <c r="N24" s="8">
         <v>6432</v>
       </c>
-      <c r="O24" s="48"/>
-      <c r="P24" s="35">
+      <c r="O24" s="8"/>
+      <c r="P24" s="10">
         <v>1182.281332</v>
       </c>
-      <c r="Q24" s="35">
+      <c r="Q24" s="10">
         <v>577.93346799999995</v>
       </c>
-      <c r="R24" s="35">
+      <c r="R24" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>1760.2148</v>
       </c>
-      <c r="S24" s="40" t="s">
+      <c r="S24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T24" s="40">
+      <c r="T24" s="6">
         <v>7900</v>
       </c>
-      <c r="U24" s="50">
+      <c r="U24" s="11">
         <v>46630</v>
       </c>
-      <c r="V24" s="51">
+      <c r="V24" s="18">
         <v>46101</v>
       </c>
-      <c r="W24" s="51">
+      <c r="W24" s="18">
         <v>46274</v>
       </c>
-      <c r="X24" s="51">
+      <c r="X24" s="18">
         <v>46304</v>
       </c>
-      <c r="Y24" s="40" t="s">
-        <v>511</v>
-      </c>
-      <c r="Z24" s="40" t="s">
+      <c r="Y24" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="Z24" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="AA24" s="40" t="s">
+      <c r="AA24" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="AB24" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="AC24" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="AB24" s="52" t="s">
-        <v>508</v>
-      </c>
-      <c r="AC24" s="40" t="s">
-        <v>512</v>
-      </c>
-      <c r="AD24" s="40" t="s">
-        <v>509</v>
+      <c r="AD24" s="6" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="409.6">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="22">
+      <c r="B25" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="7">
         <v>24</v>
       </c>
-      <c r="E25" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="F25" s="21" t="s">
+      <c r="E25" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G25" s="21"/>
-      <c r="H25" s="23" t="s">
+      <c r="G25" s="6"/>
+      <c r="H25" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I25" s="21" t="s">
+      <c r="I25" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21" t="s">
+      <c r="J25" s="6"/>
+      <c r="K25" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L25" s="21" t="s">
+      <c r="L25" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M25" s="23">
+      <c r="M25" s="8">
         <v>4245</v>
       </c>
-      <c r="N25" s="23">
+      <c r="N25" s="8">
         <v>4245</v>
       </c>
-      <c r="O25" s="23"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16">
+      <c r="O25" s="8"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S25" s="21" t="s">
+      <c r="S25" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="T25" s="21"/>
+      <c r="T25" s="6"/>
       <c r="U25" s="18"/>
-      <c r="V25" s="24">
+      <c r="V25" s="18">
         <v>46081</v>
       </c>
-      <c r="W25" s="24"/>
-      <c r="X25" s="24"/>
-      <c r="Y25" s="21"/>
-      <c r="Z25" s="21"/>
-      <c r="AA25" s="21"/>
-      <c r="AB25" s="21"/>
-      <c r="AC25" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="AD25" s="21" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" ht="256">
-      <c r="A26" s="13" t="s">
+      <c r="W25" s="18"/>
+      <c r="X25" s="18"/>
+      <c r="Y25" s="6"/>
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="6"/>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="AD25" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" ht="306">
+      <c r="A26" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="15">
         <v>25</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F26" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="H26" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="I26" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="J26" s="13" t="s">
+      <c r="J26" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="K26" s="13" t="s">
+      <c r="K26" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="L26" s="13" t="s">
+      <c r="L26" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M26" s="15">
+      <c r="M26" s="16">
         <v>4522</v>
       </c>
-      <c r="N26" s="15">
+      <c r="N26" s="16">
         <v>4521</v>
       </c>
-      <c r="O26" s="15">
+      <c r="O26" s="16">
         <v>4521</v>
       </c>
-      <c r="P26" s="16">
+      <c r="P26" s="10">
         <v>521</v>
       </c>
-      <c r="Q26" s="16">
+      <c r="Q26" s="10">
         <v>578</v>
       </c>
       <c r="R26" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>1099</v>
       </c>
-      <c r="S26" s="13" t="s">
+      <c r="S26" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T26" s="13">
+      <c r="T26" s="14">
         <v>1733</v>
       </c>
       <c r="U26" s="18">
         <v>48030</v>
       </c>
-      <c r="V26" s="19">
+      <c r="V26" s="40">
         <v>46090</v>
       </c>
-      <c r="W26" s="19">
+      <c r="W26" s="40">
         <v>46198</v>
       </c>
-      <c r="X26" s="19">
+      <c r="X26" s="40">
         <v>46224</v>
       </c>
-      <c r="Y26" s="13" t="s">
+      <c r="Y26" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="Z26" s="13" t="s">
+      <c r="Z26" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="AA26" s="13" t="s">
+      <c r="AA26" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="AB26" s="20" t="s">
+      <c r="AB26" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="AC26" s="13" t="s">
+      <c r="AC26" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="AD26" s="21"/>
-    </row>
-    <row r="27" spans="1:30" ht="211">
-      <c r="A27" s="21" t="s">
+      <c r="AD26" s="6"/>
+    </row>
+    <row r="27" spans="1:30" ht="255">
+      <c r="A27" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="7">
         <v>26</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="F27" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="G27" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="H27" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I27" s="21" t="s">
+      <c r="I27" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J27" s="21" t="s">
+      <c r="J27" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="K27" s="21" t="s">
+      <c r="K27" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="L27" s="21" t="s">
+      <c r="L27" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M27" s="23">
+      <c r="M27" s="8">
         <v>547</v>
       </c>
-      <c r="N27" s="23">
+      <c r="N27" s="8">
         <v>547</v>
       </c>
-      <c r="O27" s="23">
+      <c r="O27" s="8">
         <v>208</v>
       </c>
-      <c r="P27" s="16">
+      <c r="P27" s="10">
         <v>90.916876000000002</v>
       </c>
-      <c r="Q27" s="16">
+      <c r="Q27" s="10">
         <v>7.0831239999999998</v>
       </c>
-      <c r="R27" s="16">
+      <c r="R27" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>98</v>
       </c>
-      <c r="S27" s="21" t="s">
+      <c r="S27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T27" s="21">
+      <c r="T27" s="6">
         <v>2335</v>
       </c>
       <c r="U27" s="18">
         <v>47330</v>
       </c>
-      <c r="V27" s="24">
+      <c r="V27" s="18">
         <v>45978</v>
       </c>
-      <c r="W27" s="24">
+      <c r="W27" s="18">
         <v>46185</v>
       </c>
-      <c r="X27" s="24">
+      <c r="X27" s="18">
         <v>46234</v>
       </c>
-      <c r="Y27" s="21" t="s">
+      <c r="Y27" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="Z27" s="21" t="s">
+      <c r="Z27" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="AA27" s="21" t="s">
+      <c r="AA27" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB27" s="28" t="s">
+      <c r="AB27" s="37" t="s">
         <v>282</v>
       </c>
-      <c r="AC27" s="21" t="s">
+      <c r="AC27" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="AD27" s="21"/>
+      <c r="AD27" s="6"/>
     </row>
     <row r="28" spans="1:30" ht="409.6">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14">
+      <c r="B28" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="15">
         <v>27</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="G28" s="13"/>
-      <c r="H28" s="15" t="s">
+      <c r="G28" s="14"/>
+      <c r="H28" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="I28" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13" t="s">
+      <c r="J28" s="14"/>
+      <c r="K28" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="L28" s="13" t="s">
+      <c r="L28" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="M28" s="15">
+      <c r="M28" s="16">
         <v>818</v>
       </c>
-      <c r="N28" s="15">
+      <c r="N28" s="16">
         <v>818</v>
       </c>
-      <c r="O28" s="15"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
       <c r="R28" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S28" s="13" t="s">
+      <c r="S28" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="T28" s="13"/>
+      <c r="T28" s="14"/>
       <c r="U28" s="18"/>
-      <c r="V28" s="19">
+      <c r="V28" s="40">
         <v>45758</v>
       </c>
-      <c r="W28" s="19"/>
-      <c r="X28" s="19"/>
-      <c r="Y28" s="13"/>
-      <c r="Z28" s="13"/>
-      <c r="AA28" s="13"/>
-      <c r="AB28" s="13"/>
-      <c r="AC28" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="AD28" s="21" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" ht="241">
-      <c r="A29" s="21" t="s">
+      <c r="W28" s="40"/>
+      <c r="X28" s="40"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="14"/>
+      <c r="AC28" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="AD28" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" ht="289">
+      <c r="A29" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="22">
+      <c r="C29" s="6"/>
+      <c r="D29" s="7">
         <v>28</v>
       </c>
-      <c r="E29" s="21" t="s">
-        <v>458</v>
-      </c>
-      <c r="F29" s="21" t="s">
+      <c r="E29" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="F29" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="G29" s="21" t="s">
+      <c r="G29" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="H29" s="23" t="s">
+      <c r="H29" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I29" s="21" t="s">
+      <c r="I29" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J29" s="21" t="s">
+      <c r="J29" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="K29" s="21" t="s">
+      <c r="K29" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="L29" s="21" t="s">
+      <c r="L29" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M29" s="23">
+      <c r="M29" s="8">
         <v>710</v>
       </c>
-      <c r="N29" s="23">
+      <c r="N29" s="8">
         <v>710</v>
       </c>
-      <c r="O29" s="23">
+      <c r="O29" s="8">
         <v>594</v>
       </c>
-      <c r="P29" s="16">
+      <c r="P29" s="10">
         <v>107.53700000000001</v>
       </c>
-      <c r="Q29" s="16">
+      <c r="Q29" s="10">
         <v>308.048</v>
       </c>
-      <c r="R29" s="16">
+      <c r="R29" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>415.58500000000004</v>
       </c>
-      <c r="S29" s="21" t="s">
+      <c r="S29" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T29" s="21">
+      <c r="T29" s="6">
         <v>4406</v>
       </c>
       <c r="U29" s="18">
         <v>46721</v>
       </c>
-      <c r="V29" s="24">
+      <c r="V29" s="18">
         <v>46063</v>
       </c>
-      <c r="W29" s="24">
+      <c r="W29" s="18">
         <v>46206</v>
       </c>
-      <c r="X29" s="24">
+      <c r="X29" s="18">
         <v>46232</v>
       </c>
-      <c r="Y29" s="21" t="s">
+      <c r="Y29" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="Z29" s="21" t="s">
+      <c r="Z29" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="AA29" s="21" t="s">
+      <c r="AA29" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="AB29" s="25" t="s">
+      <c r="AB29" s="32" t="s">
         <v>251</v>
       </c>
-      <c r="AC29" s="21" t="s">
+      <c r="AC29" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="AD29" s="21"/>
-    </row>
-    <row r="30" spans="1:30" ht="241">
-      <c r="A30" s="13" t="s">
+      <c r="AD29" s="6"/>
+    </row>
+    <row r="30" spans="1:30" ht="306">
+      <c r="A30" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="15">
         <v>29</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="H30" s="15" t="s">
+      <c r="H30" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="13" t="s">
+      <c r="I30" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="J30" s="13" t="s">
+      <c r="J30" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="K30" s="13" t="s">
+      <c r="K30" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="13" t="s">
+      <c r="L30" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M30" s="15">
+      <c r="M30" s="16">
         <v>9737</v>
       </c>
-      <c r="N30" s="15">
+      <c r="N30" s="16">
         <v>9737</v>
       </c>
-      <c r="O30" s="15">
+      <c r="O30" s="16">
         <v>9025</v>
       </c>
-      <c r="P30" s="16">
+      <c r="P30" s="10">
         <f>Tabla22[[#This Row],[inversion_activos_computables_comprometida_2_anios_mill_usd]]/2</f>
         <v>1004.6565000000001</v>
       </c>
-      <c r="Q30" s="16">
+      <c r="Q30" s="10">
         <f>Tabla22[[#This Row],[inversion_activos_computables_comprometida_2_anios_mill_usd]]/2</f>
         <v>1004.6565000000001</v>
       </c>
-      <c r="R30" s="16">
+      <c r="R30" s="10">
         <v>2009.3130000000001</v>
       </c>
-      <c r="S30" s="13" t="s">
+      <c r="S30" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T30" s="13">
+      <c r="T30" s="14">
         <v>31700</v>
       </c>
       <c r="U30" s="18">
         <v>47118</v>
       </c>
-      <c r="V30" s="19">
+      <c r="V30" s="40">
         <v>46002</v>
       </c>
-      <c r="W30" s="19">
+      <c r="W30" s="40">
         <v>46176</v>
       </c>
-      <c r="X30" s="19">
+      <c r="X30" s="40">
         <v>46233</v>
       </c>
-      <c r="Y30" s="13" t="s">
+      <c r="Y30" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="Z30" s="13" t="s">
+      <c r="Z30" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="AA30" s="13" t="s">
+      <c r="AA30" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="AB30" s="20" t="s">
+      <c r="AB30" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="AC30" s="13" t="s">
+      <c r="AC30" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="AD30" s="21"/>
-    </row>
-    <row r="31" spans="1:30" ht="329">
-      <c r="A31" s="13" t="s">
+      <c r="AD30" s="6"/>
+    </row>
+    <row r="31" spans="1:30" ht="409.6">
+      <c r="A31" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="22">
+      <c r="B31" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="C31" s="14"/>
+      <c r="D31" s="7">
         <v>30</v>
       </c>
-      <c r="E31" s="15" t="s">
-        <v>332</v>
-      </c>
-      <c r="F31" s="29" t="s">
-        <v>350</v>
-      </c>
-      <c r="G31" s="13"/>
-      <c r="H31" s="15" t="s">
+      <c r="E31" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>348</v>
+      </c>
+      <c r="G31" s="14"/>
+      <c r="H31" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13" t="s">
+      <c r="I31" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="L31" s="13" t="s">
+      <c r="L31" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M31" s="15">
+      <c r="M31" s="16">
         <v>1000</v>
       </c>
-      <c r="N31" s="15">
+      <c r="N31" s="16">
         <v>1000</v>
       </c>
-      <c r="O31" s="15"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
       <c r="R31" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S31" s="13" t="s">
+      <c r="S31" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="T31" s="13"/>
+      <c r="T31" s="14"/>
       <c r="U31" s="18"/>
-      <c r="V31" s="19">
+      <c r="V31" s="40">
         <v>46157</v>
       </c>
-      <c r="W31" s="19"/>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="13"/>
-      <c r="Z31" s="13"/>
-      <c r="AA31" s="13"/>
-      <c r="AB31" s="13"/>
-      <c r="AC31" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="AD31" s="21" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30" ht="106">
-      <c r="A32" s="13" t="s">
+      <c r="W31" s="40"/>
+      <c r="X31" s="40"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="AD31" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" ht="119">
+      <c r="A32" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="15">
         <v>31</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="H32" s="15" t="s">
+      <c r="H32" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I32" s="13" t="s">
+      <c r="I32" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="J32" s="13" t="s">
+      <c r="J32" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="K32" s="13" t="s">
+      <c r="K32" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L32" s="13" t="s">
+      <c r="L32" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M32" s="15">
+      <c r="M32" s="16">
         <v>2672</v>
       </c>
-      <c r="N32" s="15">
+      <c r="N32" s="16">
         <v>2672</v>
       </c>
-      <c r="O32" s="15">
+      <c r="O32" s="16">
         <v>2354</v>
       </c>
-      <c r="P32" s="16">
+      <c r="P32" s="10">
         <v>33.512551049999999</v>
       </c>
-      <c r="Q32" s="16">
+      <c r="Q32" s="10">
         <v>382.26276160999998</v>
       </c>
       <c r="R32" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>415.77531266</v>
       </c>
-      <c r="S32" s="13" t="s">
+      <c r="S32" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T32" s="13">
+      <c r="T32" s="14">
         <v>7391</v>
       </c>
       <c r="U32" s="18">
         <v>46752</v>
       </c>
-      <c r="V32" s="19">
+      <c r="V32" s="40">
         <v>45849</v>
       </c>
-      <c r="W32" s="19">
+      <c r="W32" s="40">
         <v>45925</v>
       </c>
-      <c r="X32" s="19">
+      <c r="X32" s="40">
         <v>45943</v>
       </c>
-      <c r="Y32" s="13" t="s">
+      <c r="Y32" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="Z32" s="13" t="s">
+      <c r="Z32" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="AA32" s="13" t="s">
+      <c r="AA32" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="AB32" s="20" t="s">
+      <c r="AB32" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="AC32" s="13" t="s">
+      <c r="AC32" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="AD32" s="21"/>
-    </row>
-    <row r="33" spans="1:30" ht="31">
-      <c r="A33" s="21" t="s">
+      <c r="AD32" s="6"/>
+    </row>
+    <row r="33" spans="1:30" ht="34">
+      <c r="A33" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="22">
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="7">
         <v>32</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="E33" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="21" t="s">
+      <c r="F33" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="G33" s="21"/>
-      <c r="H33" s="23" t="s">
+      <c r="G33" s="6"/>
+      <c r="H33" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I33" s="21" t="s">
+      <c r="I33" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21" t="s">
+      <c r="J33" s="6"/>
+      <c r="K33" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L33" s="21" t="s">
+      <c r="L33" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M33" s="23">
+      <c r="M33" s="8">
         <v>273</v>
       </c>
-      <c r="N33" s="23">
+      <c r="N33" s="8">
         <v>273</v>
       </c>
-      <c r="O33" s="23"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="16">
+      <c r="O33" s="8"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S33" s="21" t="s">
+      <c r="S33" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="T33" s="21"/>
+      <c r="T33" s="6"/>
       <c r="U33" s="18"/>
-      <c r="V33" s="24">
+      <c r="V33" s="18">
         <v>45717</v>
       </c>
-      <c r="W33" s="24"/>
-      <c r="X33" s="24"/>
-      <c r="Y33" s="21"/>
-      <c r="Z33" s="21"/>
-      <c r="AA33" s="21"/>
-      <c r="AB33" s="21"/>
-      <c r="AC33" s="21" t="s">
+      <c r="W33" s="18"/>
+      <c r="X33" s="18"/>
+      <c r="Y33" s="6"/>
+      <c r="Z33" s="6"/>
+      <c r="AA33" s="6"/>
+      <c r="AB33" s="6"/>
+      <c r="AC33" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="AD33" s="21"/>
-    </row>
-    <row r="34" spans="1:30" ht="121">
-      <c r="A34" s="21" t="s">
+      <c r="AD33" s="6"/>
+    </row>
+    <row r="34" spans="1:30" ht="136">
+      <c r="A34" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="7">
+        <v>33</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="B34" s="21" t="s">
-        <v>464</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="D34" s="22">
-        <v>33</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>460</v>
-      </c>
-      <c r="G34" s="21" t="s">
+      <c r="H34" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="J34" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="H34" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="I34" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="J34" s="21" t="s">
+      <c r="K34" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="K34" s="21" t="s">
-        <v>465</v>
-      </c>
-      <c r="L34" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="M34" s="30">
+      <c r="L34" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="M34" s="39">
         <v>365.39866899999998</v>
       </c>
-      <c r="N34" s="30">
+      <c r="N34" s="39">
         <v>365.39866899999998</v>
       </c>
-      <c r="O34" s="23">
+      <c r="O34" s="8">
         <v>359.16436099999999</v>
       </c>
-      <c r="P34" s="16">
+      <c r="P34" s="10">
         <v>121.613889</v>
       </c>
-      <c r="Q34" s="16">
+      <c r="Q34" s="10">
         <v>152.70910599999999</v>
       </c>
-      <c r="R34" s="16">
+      <c r="R34" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>274.32299499999999</v>
       </c>
-      <c r="S34" s="21" t="s">
+      <c r="S34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T34" s="23">
+      <c r="T34" s="8">
         <v>792</v>
       </c>
       <c r="U34" s="18">
         <v>46661</v>
       </c>
-      <c r="V34" s="24">
+      <c r="V34" s="18">
         <v>46099</v>
       </c>
-      <c r="W34" s="24">
+      <c r="W34" s="18">
         <v>46231</v>
       </c>
-      <c r="X34" s="24">
+      <c r="X34" s="18">
         <v>46260</v>
       </c>
-      <c r="Y34" s="21" t="s">
+      <c r="Y34" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="Z34" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA34" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="AB34" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="AC34" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="Z34" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA34" s="21" t="s">
-        <v>467</v>
-      </c>
-      <c r="AB34" s="21" t="s">
-        <v>462</v>
-      </c>
-      <c r="AC34" s="21" t="s">
-        <v>468</v>
-      </c>
-      <c r="AD34" s="21"/>
+      <c r="AD34" s="6"/>
     </row>
     <row r="35" spans="1:30" ht="409.6">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B35" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="22">
+      <c r="B35" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="7">
         <v>34</v>
       </c>
-      <c r="E35" s="23" t="s">
+      <c r="E35" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F35" s="21" t="s">
+      <c r="F35" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G35" s="21"/>
-      <c r="H35" s="23" t="s">
+      <c r="G35" s="6"/>
+      <c r="H35" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I35" s="21" t="s">
+      <c r="I35" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21" t="s">
+      <c r="J35" s="6"/>
+      <c r="K35" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="L35" s="21" t="s">
+      <c r="L35" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M35" s="23">
+      <c r="M35" s="8">
         <v>4000</v>
       </c>
-      <c r="N35" s="23">
+      <c r="N35" s="8">
         <v>4000</v>
       </c>
-      <c r="O35" s="23"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16">
+      <c r="O35" s="8"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S35" s="21" t="s">
+      <c r="S35" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="T35" s="21"/>
+      <c r="T35" s="6"/>
       <c r="U35" s="18"/>
-      <c r="V35" s="24">
+      <c r="V35" s="18">
         <v>45887</v>
       </c>
-      <c r="W35" s="24"/>
-      <c r="X35" s="24"/>
-      <c r="Y35" s="21"/>
-      <c r="Z35" s="21"/>
-      <c r="AA35" s="21"/>
-      <c r="AB35" s="21"/>
-      <c r="AC35" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="AD35" s="21" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="36" spans="1:30" ht="75">
-      <c r="A36" s="31" t="s">
-        <v>471</v>
-      </c>
-      <c r="B36" s="32" t="s">
-        <v>475</v>
-      </c>
-      <c r="C36" s="31" t="s">
+      <c r="W35" s="18"/>
+      <c r="X35" s="18"/>
+      <c r="Y35" s="6"/>
+      <c r="Z35" s="6"/>
+      <c r="AA35" s="6"/>
+      <c r="AB35" s="6"/>
+      <c r="AC35" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="AD35" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" ht="102">
+      <c r="A36" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>473</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="15">
         <v>35</v>
       </c>
-      <c r="E36" s="34" t="s">
+      <c r="E36" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="F36" s="31" t="s">
+      <c r="F36" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="G36" s="32" t="s">
+      <c r="G36" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="I36" s="30" t="s">
         <v>470</v>
       </c>
-      <c r="H36" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="I36" s="32" t="s">
+      <c r="J36" s="30" t="s">
+        <v>470</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" s="30" t="s">
         <v>472</v>
       </c>
-      <c r="J36" s="32" t="s">
-        <v>472</v>
-      </c>
-      <c r="K36" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="L36" s="32" t="s">
-        <v>474</v>
-      </c>
-      <c r="M36" s="34">
+      <c r="M36" s="16">
         <v>2693</v>
       </c>
-      <c r="N36" s="34">
+      <c r="N36" s="16">
         <v>2693</v>
       </c>
-      <c r="O36" s="34">
+      <c r="O36" s="16">
         <v>2693</v>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="10">
         <v>785</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="10">
         <v>881</v>
       </c>
-      <c r="R36" s="36">
+      <c r="R36" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>1666</v>
       </c>
-      <c r="S36" s="31" t="s">
+      <c r="S36" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="T36" s="31">
+      <c r="T36" s="14">
         <v>12500</v>
       </c>
-      <c r="U36" s="37">
+      <c r="U36" s="18">
         <v>47453</v>
       </c>
-      <c r="V36" s="38">
+      <c r="V36" s="40">
         <v>46133</v>
       </c>
-      <c r="W36" s="38">
+      <c r="W36" s="40">
         <v>46237</v>
       </c>
-      <c r="X36" s="38">
+      <c r="X36" s="40">
         <v>46272</v>
       </c>
-      <c r="Y36" s="31" t="s">
-        <v>473</v>
-      </c>
-      <c r="Z36" s="31" t="s">
+      <c r="Y36" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="Z36" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="AA36" s="32" t="s">
-        <v>478</v>
-      </c>
-      <c r="AB36" s="39" t="s">
+      <c r="AA36" s="30" t="s">
         <v>476</v>
       </c>
-      <c r="AC36" s="31" t="s">
-        <v>477</v>
-      </c>
-      <c r="AD36" s="40"/>
-    </row>
-    <row r="37" spans="1:30" ht="166">
-      <c r="A37" s="21" t="s">
+      <c r="AB36" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="AC36" s="14" t="s">
+        <v>475</v>
+      </c>
+      <c r="AD36" s="6"/>
+    </row>
+    <row r="37" spans="1:30" ht="204">
+      <c r="A37" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="7">
         <v>36</v>
       </c>
-      <c r="E37" s="23" t="s">
+      <c r="E37" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="F37" s="21" t="s">
-        <v>469</v>
-      </c>
-      <c r="G37" s="21" t="s">
+      <c r="F37" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="H37" s="23" t="s">
+      <c r="H37" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I37" s="21" t="s">
+      <c r="I37" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="J37" s="21" t="s">
+      <c r="J37" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="K37" s="21" t="s">
+      <c r="K37" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="L37" s="21" t="s">
+      <c r="L37" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="23">
+      <c r="M37" s="8">
         <v>1300</v>
       </c>
-      <c r="N37" s="23">
+      <c r="N37" s="8">
         <v>1300</v>
       </c>
-      <c r="O37" s="23">
+      <c r="O37" s="8">
         <v>955</v>
       </c>
-      <c r="P37" s="16">
+      <c r="P37" s="10">
         <v>454</v>
       </c>
-      <c r="Q37" s="16">
+      <c r="Q37" s="10">
         <v>501</v>
       </c>
-      <c r="R37" s="16">
+      <c r="R37" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>955</v>
       </c>
-      <c r="S37" s="21" t="s">
+      <c r="S37" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T37" s="21">
+      <c r="T37" s="6">
         <v>2489</v>
       </c>
       <c r="U37" s="18">
         <v>46538</v>
       </c>
-      <c r="V37" s="24">
+      <c r="V37" s="18">
         <v>45950</v>
       </c>
-      <c r="W37" s="24">
+      <c r="W37" s="18">
         <v>46174</v>
       </c>
-      <c r="X37" s="24">
+      <c r="X37" s="18">
         <v>46198</v>
       </c>
-      <c r="Y37" s="21" t="s">
+      <c r="Y37" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="Z37" s="21" t="s">
+      <c r="Z37" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="AA37" s="21" t="s">
-        <v>493</v>
-      </c>
-      <c r="AB37" s="28" t="s">
+      <c r="AA37" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="AB37" s="37" t="s">
         <v>240</v>
       </c>
-      <c r="AC37" s="21" t="s">
+      <c r="AC37" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="AD37" s="21"/>
-    </row>
-    <row r="38" spans="1:30" ht="91">
-      <c r="A38" s="21" t="s">
+      <c r="AD37" s="6"/>
+    </row>
+    <row r="38" spans="1:30" ht="102">
+      <c r="A38" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="C38" s="21" t="s">
+      <c r="C38" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="15">
         <v>37</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="E38" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="21" t="s">
+      <c r="F38" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G38" s="21" t="s">
+      <c r="G38" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="H38" s="23" t="s">
+      <c r="H38" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="I38" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J38" s="21" t="s">
+      <c r="J38" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="K38" s="21" t="s">
+      <c r="K38" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="L38" s="21" t="s">
+      <c r="L38" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M38" s="23">
+      <c r="M38" s="8">
         <v>292</v>
       </c>
-      <c r="N38" s="23">
+      <c r="N38" s="8">
         <v>217</v>
       </c>
-      <c r="O38" s="23">
+      <c r="O38" s="8">
         <v>217</v>
       </c>
-      <c r="P38" s="16">
+      <c r="P38" s="10">
         <v>31.112863000000001</v>
       </c>
-      <c r="Q38" s="16">
+      <c r="Q38" s="10">
         <v>51.531371</v>
       </c>
-      <c r="R38" s="16">
+      <c r="R38" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>82.644233999999997</v>
       </c>
-      <c r="S38" s="21" t="s">
+      <c r="S38" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="T38" s="21">
+      <c r="T38" s="6">
         <v>670</v>
       </c>
       <c r="U38" s="18">
         <v>47483</v>
       </c>
-      <c r="V38" s="24">
+      <c r="V38" s="18">
         <v>45594</v>
       </c>
-      <c r="W38" s="24">
+      <c r="W38" s="18">
         <v>45855</v>
       </c>
-      <c r="X38" s="24">
+      <c r="X38" s="18">
         <v>45896</v>
       </c>
-      <c r="Y38" s="21" t="s">
+      <c r="Y38" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="Z38" s="21" t="s">
+      <c r="Z38" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="AA38" s="21" t="s">
+      <c r="AA38" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="AB38" s="28" t="s">
+      <c r="AB38" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="AC38" s="21" t="s">
+      <c r="AC38" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="AD38" s="21"/>
+      <c r="AD38" s="6"/>
     </row>
     <row r="39" spans="1:30" ht="409.6">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="C39" s="14"/>
+      <c r="D39" s="7">
+        <v>38</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="F39" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="C39" s="13"/>
-      <c r="D39" s="22">
-        <v>38</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>338</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="G39" s="13"/>
-      <c r="H39" s="15" t="s">
+      <c r="G39" s="14"/>
+      <c r="H39" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I39" s="13" t="s">
+      <c r="I39" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13" t="s">
+      <c r="J39" s="14"/>
+      <c r="K39" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="L39" s="13" t="s">
+      <c r="L39" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="M39" s="15">
+      <c r="M39" s="16">
         <v>1151</v>
       </c>
-      <c r="N39" s="15">
+      <c r="N39" s="16">
         <v>1151</v>
       </c>
-      <c r="O39" s="15"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
       <c r="R39" s="17">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S39" s="13" t="s">
+      <c r="S39" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="T39" s="13"/>
+      <c r="T39" s="14"/>
       <c r="U39" s="18"/>
-      <c r="V39" s="19">
+      <c r="V39" s="40">
         <v>46111</v>
       </c>
-      <c r="W39" s="19"/>
-      <c r="X39" s="19"/>
-      <c r="Y39" s="13"/>
-      <c r="Z39" s="13"/>
-      <c r="AA39" s="13"/>
-      <c r="AB39" s="13"/>
-      <c r="AC39" s="13" t="s">
+      <c r="W39" s="40"/>
+      <c r="X39" s="40"/>
+      <c r="Y39" s="14"/>
+      <c r="Z39" s="14"/>
+      <c r="AA39" s="14"/>
+      <c r="AB39" s="14"/>
+      <c r="AC39" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD39" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" ht="409.6">
+      <c r="A40" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="AD39" s="21" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="40" spans="1:30" ht="385">
-      <c r="A40" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="C40" s="21"/>
-      <c r="D40" s="14">
+      <c r="C40" s="6"/>
+      <c r="D40" s="15">
         <v>39</v>
       </c>
-      <c r="E40" s="23" t="s">
+      <c r="E40" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="F40" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="G40" s="21"/>
-      <c r="H40" s="23" t="s">
+      <c r="F40" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="G40" s="6"/>
+      <c r="H40" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I40" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21" t="s">
+      <c r="I40" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="L40" s="21" t="s">
+      <c r="L40" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M40" s="23">
+      <c r="M40" s="8">
         <v>25000</v>
       </c>
-      <c r="N40" s="23">
+      <c r="N40" s="8">
         <v>25000</v>
       </c>
-      <c r="O40" s="23"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16">
+      <c r="O40" s="8"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S40" s="21" t="s">
+      <c r="S40" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="T40" s="21"/>
+      <c r="T40" s="6"/>
       <c r="U40" s="18"/>
-      <c r="V40" s="24">
+      <c r="V40" s="18">
         <v>46157</v>
       </c>
-      <c r="W40" s="24"/>
-      <c r="X40" s="24"/>
-      <c r="Y40" s="21"/>
-      <c r="Z40" s="21"/>
-      <c r="AA40" s="21"/>
-      <c r="AB40" s="21"/>
-      <c r="AC40" s="21" t="s">
+      <c r="W40" s="18"/>
+      <c r="X40" s="18"/>
+      <c r="Y40" s="6"/>
+      <c r="Z40" s="6"/>
+      <c r="AA40" s="6"/>
+      <c r="AB40" s="6"/>
+      <c r="AC40" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="AD40" s="6" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" ht="409.6">
+      <c r="A41" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="AD40" s="21" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="41" spans="1:30" ht="409.6">
-      <c r="A41" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="C41" s="21"/>
-      <c r="D41" s="22">
+      <c r="C41" s="6"/>
+      <c r="D41" s="7">
         <v>40</v>
       </c>
-      <c r="E41" s="23" t="s">
+      <c r="E41" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="F41" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="G41" s="21"/>
-      <c r="H41" s="23" t="s">
+      <c r="F41" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I41" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21" t="s">
+      <c r="I41" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="L41" s="21" t="s">
+      <c r="L41" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M41" s="23">
+      <c r="M41" s="8">
         <v>5800</v>
       </c>
-      <c r="N41" s="23">
+      <c r="N41" s="8">
         <v>5800</v>
       </c>
-      <c r="O41" s="23"/>
-      <c r="P41" s="16"/>
-      <c r="Q41" s="16"/>
-      <c r="R41" s="16">
+      <c r="O41" s="8"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S41" s="21" t="s">
+      <c r="S41" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="T41" s="24"/>
+      <c r="T41" s="12"/>
       <c r="U41" s="18"/>
-      <c r="V41" s="24">
+      <c r="V41" s="18">
         <v>46224</v>
       </c>
-      <c r="W41" s="24"/>
-      <c r="X41" s="24"/>
-      <c r="Y41" s="21"/>
-      <c r="Z41" s="21"/>
-      <c r="AA41" s="21"/>
-      <c r="AB41" s="21"/>
-      <c r="AC41" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="AD41" s="25" t="s">
-        <v>347</v>
+      <c r="W41" s="18"/>
+      <c r="X41" s="18"/>
+      <c r="Y41" s="6"/>
+      <c r="Z41" s="6"/>
+      <c r="AA41" s="6"/>
+      <c r="AB41" s="6"/>
+      <c r="AC41" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="AD41" s="32" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="409.6">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C42" s="6"/>
+      <c r="D42" s="7">
+        <v>41</v>
+      </c>
+      <c r="E42" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="B42" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="22">
-        <v>41</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>356</v>
-      </c>
-      <c r="F42" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="G42" s="21"/>
-      <c r="H42" s="23" t="s">
+      <c r="F42" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="G42" s="6"/>
+      <c r="H42" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I42" s="21" t="s">
+      <c r="I42" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="J42" s="21"/>
-      <c r="K42" s="21" t="s">
-        <v>305</v>
-      </c>
-      <c r="L42" s="21" t="s">
+      <c r="J42" s="6"/>
+      <c r="K42" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="L42" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="23">
+      <c r="M42" s="8">
         <v>51000</v>
       </c>
-      <c r="N42" s="23"/>
-      <c r="O42" s="23"/>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="16">
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S42" s="21" t="s">
+      <c r="S42" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="T42" s="23"/>
+      <c r="T42" s="8"/>
       <c r="U42" s="18"/>
-      <c r="V42" s="24">
+      <c r="V42" s="18">
         <v>46247</v>
       </c>
-      <c r="W42" s="24"/>
-      <c r="X42" s="24"/>
-      <c r="Y42" s="21"/>
-      <c r="Z42" s="21"/>
-      <c r="AA42" s="21"/>
-      <c r="AB42" s="21"/>
-      <c r="AC42" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="AD42" s="21" t="s">
-        <v>358</v>
+      <c r="W42" s="18"/>
+      <c r="X42" s="18"/>
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="6"/>
+      <c r="AA42" s="6"/>
+      <c r="AB42" s="6"/>
+      <c r="AC42" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="AD42" s="6" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="43" spans="1:30" ht="409.6">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="20" t="s">
+        <v>488</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>477</v>
+      </c>
+      <c r="C43" s="20"/>
+      <c r="D43" s="21">
+        <v>42</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="I43" s="20" t="s">
         <v>490</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7">
-        <v>42</v>
-      </c>
-      <c r="E43" s="8" t="s">
+      <c r="J43" s="20"/>
+      <c r="K43" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="L43" s="20" t="s">
         <v>480</v>
       </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="8" t="s">
+      <c r="M43" s="22">
+        <v>1341</v>
+      </c>
+      <c r="N43" s="22"/>
+      <c r="O43" s="22"/>
+      <c r="P43" s="23"/>
+      <c r="Q43" s="23"/>
+      <c r="R43" s="23"/>
+      <c r="S43" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="T43" s="22">
+        <v>6200</v>
+      </c>
+      <c r="U43" s="42"/>
+      <c r="V43" s="42">
+        <v>46295</v>
+      </c>
+      <c r="W43" s="42"/>
+      <c r="X43" s="42"/>
+      <c r="Y43" s="20"/>
+      <c r="Z43" s="20"/>
+      <c r="AA43" s="20"/>
+      <c r="AB43" s="20"/>
+      <c r="AC43" s="20" t="s">
         <v>481</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="AD43" s="20" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" ht="409.6">
+      <c r="A44" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="B44" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24">
+        <v>43</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="I44" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="J44" s="24"/>
+      <c r="K44" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="L44" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="M44" s="24">
+        <v>1200</v>
+      </c>
+      <c r="N44" s="24"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="24"/>
+      <c r="Q44" s="24"/>
+      <c r="R44" s="24"/>
+      <c r="S44" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="T44" s="24"/>
+      <c r="U44" s="43"/>
+      <c r="V44" s="42">
+        <v>46296</v>
+      </c>
+      <c r="W44" s="43"/>
+      <c r="X44" s="43"/>
+      <c r="Y44" s="24"/>
+      <c r="Z44" s="24"/>
+      <c r="AA44" s="24"/>
+      <c r="AB44" s="24"/>
+      <c r="AC44" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="AD44" s="24" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" ht="340">
+      <c r="A45" s="25" t="s">
+        <v>491</v>
+      </c>
+      <c r="B45" s="25" t="s">
         <v>492</v>
       </c>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="M43" s="8">
-        <v>1341</v>
-      </c>
-      <c r="N43" s="8"/>
-      <c r="O43" s="8"/>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="9"/>
-      <c r="R43" s="9"/>
-      <c r="S43" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="T43" s="8">
-        <v>6200</v>
-      </c>
-      <c r="U43" s="10"/>
-      <c r="V43" s="11">
-        <v>46295</v>
-      </c>
-      <c r="W43" s="11"/>
-      <c r="X43" s="11"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="6"/>
-      <c r="AB43" s="6"/>
-      <c r="AC43" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="AD43" s="6" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="44" spans="1:30" ht="409.6">
-      <c r="A44" s="12" t="s">
+      <c r="C45" s="25"/>
+      <c r="D45" s="26">
+        <v>44</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>493</v>
+      </c>
+      <c r="F45" s="25" t="s">
         <v>491</v>
       </c>
-      <c r="B44" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12">
-        <v>43</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>303</v>
-      </c>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12" t="s">
-        <v>486</v>
-      </c>
-      <c r="L44" s="12" t="s">
-        <v>487</v>
-      </c>
-      <c r="M44" s="12">
-        <v>1200</v>
-      </c>
-      <c r="N44" s="12"/>
-      <c r="O44" s="12"/>
-      <c r="P44" s="12"/>
-      <c r="Q44" s="12"/>
-      <c r="R44" s="12"/>
-      <c r="S44" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="T44" s="12"/>
-      <c r="U44" s="12"/>
-      <c r="V44" s="11">
-        <v>46296</v>
-      </c>
-      <c r="W44" s="12"/>
-      <c r="X44" s="12"/>
-      <c r="Y44" s="12"/>
-      <c r="Z44" s="12"/>
-      <c r="AA44" s="12"/>
-      <c r="AB44" s="12"/>
-      <c r="AC44" s="12" t="s">
-        <v>488</v>
-      </c>
-      <c r="AD44" s="12" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="45" spans="1:30" ht="240">
-      <c r="A45" s="41" t="s">
+      <c r="G45" s="25"/>
+      <c r="H45" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J45" s="25"/>
+      <c r="K45" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="25" t="s">
         <v>494</v>
       </c>
-      <c r="B45" s="41" t="s">
-        <v>495</v>
-      </c>
-      <c r="C45" s="41"/>
-      <c r="D45" s="42">
-        <v>44</v>
-      </c>
-      <c r="E45" s="43" t="s">
-        <v>496</v>
-      </c>
-      <c r="F45" s="41" t="s">
-        <v>494</v>
-      </c>
-      <c r="G45" s="41"/>
-      <c r="H45" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="I45" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="L45" s="41" t="s">
-        <v>497</v>
-      </c>
-      <c r="M45" s="43">
+      <c r="M45" s="27">
         <v>2437</v>
       </c>
-      <c r="N45" s="43"/>
-      <c r="O45" s="43"/>
-      <c r="P45" s="44"/>
-      <c r="Q45" s="44"/>
-      <c r="R45" s="44">
+      <c r="N45" s="27"/>
+      <c r="O45" s="27"/>
+      <c r="P45" s="28"/>
+      <c r="Q45" s="28"/>
+      <c r="R45" s="28">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S45" s="41" t="s">
+      <c r="S45" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="T45" s="41"/>
-      <c r="U45" s="45"/>
-      <c r="V45" s="46"/>
-      <c r="W45" s="46"/>
-      <c r="X45" s="46"/>
-      <c r="Y45" s="41"/>
-      <c r="Z45" s="41"/>
-      <c r="AA45" s="41"/>
-      <c r="AB45" s="41"/>
-      <c r="AC45" s="41" t="s">
-        <v>499</v>
-      </c>
-      <c r="AD45" s="41" t="s">
-        <v>498</v>
+      <c r="T45" s="25"/>
+      <c r="U45" s="29"/>
+      <c r="V45" s="44"/>
+      <c r="W45" s="44"/>
+      <c r="X45" s="44"/>
+      <c r="Y45" s="25"/>
+      <c r="Z45" s="25"/>
+      <c r="AA45" s="25"/>
+      <c r="AB45" s="25"/>
+      <c r="AC45" s="25" t="s">
+        <v>496</v>
+      </c>
+      <c r="AD45" s="25" t="s">
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -6596,22 +6654,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32">
       <c r="A1" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16">
@@ -6619,19 +6677,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>170</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16">
@@ -6639,19 +6697,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16">
@@ -6659,19 +6717,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16">
@@ -6682,16 +6740,16 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16">
@@ -6702,16 +6760,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16">
@@ -6722,16 +6780,16 @@
         <v>169</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16">
@@ -6739,19 +6797,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>141</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16">
@@ -6762,16 +6820,16 @@
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16">
@@ -6782,16 +6840,16 @@
         <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16">
@@ -6799,19 +6857,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16">
@@ -6822,16 +6880,16 @@
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16">
@@ -6842,16 +6900,16 @@
         <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16">
@@ -6859,19 +6917,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16">
@@ -6879,19 +6937,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16">
@@ -6899,19 +6957,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16">
@@ -6919,19 +6977,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16">
@@ -6939,19 +6997,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32">
@@ -6959,19 +7017,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16">
@@ -6979,19 +7037,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>124</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16">
@@ -6999,19 +7057,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16">
@@ -7019,19 +7077,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16">
@@ -7042,16 +7100,16 @@
         <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16">
@@ -7062,16 +7120,16 @@
         <v>151</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16">
@@ -7082,16 +7140,16 @@
         <v>152</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="16">
@@ -7102,16 +7160,16 @@
         <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="32">
@@ -7119,19 +7177,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16">
@@ -7139,19 +7197,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16">
@@ -7162,16 +7220,16 @@
         <v>126</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16">
@@ -7179,19 +7237,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>145</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16">
@@ -7199,19 +7257,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -7226,13 +7284,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="64">
       <c r="A1" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16">
@@ -7243,7 +7301,7 @@
         <v>170</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="48">
@@ -7254,7 +7312,7 @@
         <v>157</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="112">
@@ -7265,7 +7323,7 @@
         <v>249</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16">
@@ -7309,7 +7367,7 @@
         <v>141</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16">
@@ -7342,7 +7400,7 @@
         <v>186</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16">
@@ -7375,7 +7433,7 @@
         <v>122</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="64">
@@ -7386,7 +7444,7 @@
         <v>277</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="64">
@@ -7397,7 +7455,7 @@
         <v>123</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="96">
@@ -7405,10 +7463,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="96">
@@ -7416,10 +7474,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="96">
@@ -7427,10 +7485,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="48">
@@ -7441,7 +7499,7 @@
         <v>124</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="64">
@@ -7452,7 +7510,7 @@
         <v>219</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="80">
@@ -7460,10 +7518,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="32">
@@ -7518,7 +7576,7 @@
         <v>217</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="64">
@@ -7529,7 +7587,7 @@
         <v>218</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16">
@@ -7551,7 +7609,7 @@
         <v>145</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="32">
@@ -7562,7 +7620,7 @@
         <v>292</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Investigación/Tasks JCH/RIGI/base de datos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Library/CloudStorage/GoogleDrive-lucassebaord29@gmail.com/Mi unidad/EXCEL RIGI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F104212-E614-8743-9668-39DE40512F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD8FFFC-1241-2344-9120-B6D3DBC0B481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2920" yWindow="600" windowWidth="65860" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="7" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="536">
   <si>
     <t>id_proyecto</t>
   </si>
@@ -884,9 +884,6 @@
     <t>Instalación de una planta flotante de licuefacción de gas natural para obtener Gas Natural Licuado (GNL)</t>
   </si>
   <si>
-    <t>Consiste en la construcción y desarrollo de un oleoducto, Iincrementar la capacidad de transporte y almacenamiento de petróleo crudo viabilizando la exportación de hidrocarburos provenientes de la formación “Vaca Muerta”</t>
-  </si>
-  <si>
     <t>Desarrollo (factibilidad, permisos) y la construcción de mina, planta e infraestructura asociada para extraer y procesar cátodos de cobre</t>
   </si>
   <si>
@@ -1541,9 +1538,6 @@
     <t>Se identifican signos fuertes de preexistencia. El proyecto “Fertilizantes” de Fértil Pampa SAU fue aprobado bajo RIGI por la Resolución 1468/2026, publicada el 07/09/2026, pero existía públicamente antes de esa fecha. La sociedad Fértil Pampa SAU fue constituida en octubre de 2024 con objeto específico de construir y operar una planta de amoníaco, urea y otros fertilizantes. Antes de la aprobación RIGI ya existían divulgaciones financieras y ambientales ante BID Invest e IFC, solicitud RIGI presentada el 21/04/2026, memorándum de entendimiento con el Municipio de Bahía Blanca, decisión final de inversión de Pampa Energía del 17/07/2026, contrato EPC con Tecnimont–SACDE y trámites de participación pública ambiental. Por lo tanto, se clasifica como proyecto preexistente al anuncio/aprobación oficial, aunque corresponde a una inversión greenfield y no a una ampliación de una planta ya operativa.</t>
   </si>
   <si>
-    <t>Nueva planta dentro del complejo industrial de Toyota en Zárate para producir un vehículo electrificado —descripto por el ministro de Economía como 100% electrificado—, con aproximadamente 70% de la producción destinada a exportación.</t>
-  </si>
-  <si>
     <t>Toyota Argentina S.A. (Argentina)</t>
   </si>
   <si>
@@ -1553,12 +1547,6 @@
     <t>Zárate</t>
   </si>
   <si>
-    <t>Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026); ARCA / Decreto 105/2026 (19/02/2026)</t>
-  </si>
-  <si>
-    <t>https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/; https://biblioteca.afip.gob.ar/dcp/DEC_C_000749_2024_08_22</t>
-  </si>
-  <si>
     <t>Desarrollo de recuperación terciaria de petróleo convencional en Cerro Dragón: 22 plantas de inyección de polímeros, perforación de 100 pozos productores e inyectores, adecuación de pozos, intervención de otros 600 pozos productores e infraestructura complementaria de superficie. Producción incremental estimada: 46 millones de barriles de petróleo y 30 BCF de gas natural.</t>
   </si>
   <si>
@@ -1580,9 +1568,6 @@
     <t>PAE Cerro Dragón</t>
   </si>
   <si>
-    <t xml:space="preserve">Automotriz </t>
-  </si>
-  <si>
     <t>Pampa Exploración S.A.</t>
   </si>
   <si>
@@ -1662,6 +1647,72 @@
   </si>
   <si>
     <t>Res. 1808/2026; Gobierno de la Provincia del Neuquén; Casa Rosada</t>
+  </si>
+  <si>
+    <t>Consiste en la construcción y desarrollo de un oleoducto, incrementar la capacidad de transporte y almacenamiento de petróleo crudo viabilizando la exportación de hidrocarburos provenientes de la formación “Vaca Muerta”</t>
+  </si>
+  <si>
+    <t>Ampliación de la planta industrial de Toyota en Zárate mediante la construcción, instalación, puesta en funcionamiento y operación de una tercera planta para fabricar un vehículo híbrido eléctrico no enchufable (full HEV), inicialmente tipo pick-up y con posibilidad de versión SUV.</t>
+  </si>
+  <si>
+    <t>Toyota Argentina S.A. Sucursal Dedicada</t>
+  </si>
+  <si>
+    <t>30-71944240-0</t>
+  </si>
+  <si>
+    <t>Automotriz</t>
+  </si>
+  <si>
+    <t>Fabricación, ensamblado y montaje de vehículos de nueva tecnología de motorización</t>
+  </si>
+  <si>
+    <t>Res. 1848/2026</t>
+  </si>
+  <si>
+    <t>La Resolución 1848/2026 aprueba la ampliación de un proyecto preexistente no adherido: una tercera planta dentro del complejo industrial existente de Toyota en Zárate. Los beneficios se aplican exclusivamente a la ampliación.</t>
+  </si>
+  <si>
+    <t>Procesamiento de NGLs en Tratayén</t>
+  </si>
+  <si>
+    <t>Construcción de un gasoducto de segregación de corrientes de aproximadamente 100 km y nuevas instalaciones de procesamiento en Tratayén, con capacidad para 43 millones de m³ diarios, para separar líquidos del gas natural. Integra un paquete de dos proyectos de TGS con inversión conjunta superior a USD 3.200 millones; el monto actualizado por VPU no fue publicado.</t>
+  </si>
+  <si>
+    <t>Transportadora de Gas del Sur S.A. (TGS) (Argentina)</t>
+  </si>
+  <si>
+    <t>Procesadora de Gas del Sur S.A. (PGS)</t>
+  </si>
+  <si>
+    <t>Tratayén, Neuquén</t>
+  </si>
+  <si>
+    <t>Luis Caputo / Ministerio de Economía (X, 19/10/2026); Shale24 (19/10/2026); TGS, estados financieros 2T 2026 (04/08/2026)</t>
+  </si>
+  <si>
+    <t>https://x.com/LuisCaputoAR/status/2112170371310858454; https://www.shale24.com/oil-gas/tgs-entra-rigi-us-3200-millones-bahia-blanca-ya-suma-dos-obras-liquidos-vaca-muerta-regimen-n1864; https://api.mziq.com/mzfilemanager/v2/d/78ce1f91-b610-429f-b020-add32c211c1f/dcfe21a3-8a28-44d7-5aeb-2e1a49a861e2?origin=2</t>
+  </si>
+  <si>
+    <t>Poliducto Tratayén–Bahía Blanca y complejo NGL Puerto Galván</t>
+  </si>
+  <si>
+    <t>Construcción de un poliducto de 577 km desde Tratayén hasta Bahía Blanca, una planta de fraccionamiento, instalaciones de almacenamiento y obras en la terminal marítima de Puerto Galván para exportar aproximadamente 2,7 millones de toneladas anuales de propano, butano y gasolina natural. Integra un paquete de dos proyectos de TGS con inversión conjunta superior a USD 3.200 millones; el monto actualizado por VPU no fue publicado.</t>
+  </si>
+  <si>
+    <t>Midstream de Gas del Sur S.A. (MGS)</t>
+  </si>
+  <si>
+    <t>Tratayén–Bahía Blanca / Puerto Galván</t>
+  </si>
+  <si>
+    <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349428/20261022</t>
+  </si>
+  <si>
+    <t>Res. 1848/2026 (B.O. 22/10/2026); Luis Caputo / Ministerio de Economía (X, 30/09/2026); Reuters (30/09/2026); La Nación / Toyota Argentina (30/09/2026)</t>
+  </si>
+  <si>
+    <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349428/20261022; https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/</t>
   </si>
   <si>
     <r>
@@ -1672,9 +1723,8 @@
         <b/>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
       <t>Hilli Episeyo</t>
     </r>
@@ -1682,9 +1732,8 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
       <t xml:space="preserve"> en Argentina.</t>
     </r>
@@ -1694,13 +1743,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="168" formatCode="0.######"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1756,41 +1806,42 @@
       <scheme val="major"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="major"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="major"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="major"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="major"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="major"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1827,7 +1878,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1859,6 +1910,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD7E0EA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD7E0EA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD7E0EA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD7E0EA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD7E0EA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD7E0EA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD7E0EA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1866,7 +1945,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1886,118 +1965,139 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2017,9 +2117,114 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="19" formatCode="d/m/yy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2033,24 +2238,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="19" formatCode="d/m/yy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2064,9 +2254,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="19" formatCode="d/m/yy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2080,12 +2270,12 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="19" formatCode="d/m/yy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2096,9 +2286,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2111,112 +2301,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2233,9 +2320,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0000"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2253,9 +2340,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0000"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2273,9 +2360,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0000"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2289,9 +2376,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2305,9 +2392,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2321,9 +2408,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2337,9 +2424,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2352,9 +2439,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2367,9 +2454,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2382,9 +2469,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2397,9 +2484,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2413,9 +2500,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2428,9 +2515,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2443,9 +2530,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2459,9 +2546,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2475,9 +2562,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2490,9 +2577,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2505,9 +2592,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="major"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2517,6 +2604,19 @@
           <color theme="1"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2759,44 +2859,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7BB49DC-9D24-614F-848B-0F39C691B2B5}" name="Tabla22" displayName="Tabla22" ref="A1:AD45" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" headerRowBorderDxfId="32">
-  <autoFilter ref="A1:AD45" xr:uid="{C7BB49DC-9D24-614F-848B-0F39C691B2B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C7BB49DC-9D24-614F-848B-0F39C691B2B5}" name="Tabla22" displayName="Tabla22" ref="A1:AD47" totalsRowShown="0" headerRowDxfId="32" dataDxfId="0" headerRowBorderDxfId="31">
+  <autoFilter ref="A1:AD47" xr:uid="{C7BB49DC-9D24-614F-848B-0F39C691B2B5}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC41">
     <sortCondition ref="D1:D41"/>
   </sortState>
   <tableColumns count="30">
-    <tableColumn id="1" xr3:uid="{B0F75E5C-946A-644E-9EB4-93643A1ADB1D}" name="vpu" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{0955A7C4-B25E-574D-B27D-1FB04B3EECF0}" name="descripcion_proyecto" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{A18EE10B-7E84-2240-B4D3-1E345824A440}" name="peelp" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{16CBA668-029E-7948-A2E2-792901752FC7}" name="id_proyecto" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{0533A60E-9F7B-384C-8E9E-AF9F698F8BC8}" name="empresa" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{E1AB486A-B757-314A-924B-58FCED818ED9}" name="titular_proyecto" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{248B94B7-B222-6040-A333-51F513C1F6ED}" name="cuit" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{AD5B6DCF-9CBB-3846-858D-9D3985C6A3E4}" name="sector" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{4CA252E5-23F1-474A-A9B5-8A0EDF3EAF49}" name="subsector" dataDxfId="23"/>
-    <tableColumn id="10" xr3:uid="{F8D93550-E6F5-114D-949F-487B7BFA388C}" name="actividad_subsector_resolucion_mecon" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{1475CC17-5B24-3247-8DBA-0625A938B1B7}" name="provincia" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{47AF60A5-F6B3-8743-8C92-1EB7255A904F}" name="localidad_region" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{75050396-7FEE-5341-9B55-07F221AA6F90}" name="inversion_total_mill_usd" dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{A7D4770F-B48F-9443-B4A0-4629A448E999}" name="inversion_total_resolucion_mill_usd" dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{1602558E-3054-8C4C-9A58-AB8CCCD77682}" name="inversion_activos_computables_mill_usd" dataDxfId="17"/>
-    <tableColumn id="28" xr3:uid="{87595E4D-D42F-354A-9940-89724D3641FE}" name="inversion_activos_computables_comprometida_anio_1_mill_usd" dataDxfId="16"/>
-    <tableColumn id="29" xr3:uid="{688CE13F-074F-304D-836A-8560E747EB65}" name="inversion_activos_computables_comprometida_anio_2_mill_usd" dataDxfId="15"/>
-    <tableColumn id="30" xr3:uid="{B6018A02-36C0-DD40-A886-EEE247A26505}" name="inversion_activos_computables_comprometida_2_anios_mill_usd" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{B0F75E5C-946A-644E-9EB4-93643A1ADB1D}" name="vpu" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{0955A7C4-B25E-574D-B27D-1FB04B3EECF0}" name="descripcion_proyecto" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{A18EE10B-7E84-2240-B4D3-1E345824A440}" name="peelp" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{16CBA668-029E-7948-A2E2-792901752FC7}" name="id_proyecto" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{0533A60E-9F7B-384C-8E9E-AF9F698F8BC8}" name="empresa" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{E1AB486A-B757-314A-924B-58FCED818ED9}" name="titular_proyecto" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{248B94B7-B222-6040-A333-51F513C1F6ED}" name="cuit" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{AD5B6DCF-9CBB-3846-858D-9D3985C6A3E4}" name="sector" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{4CA252E5-23F1-474A-A9B5-8A0EDF3EAF49}" name="subsector" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{F8D93550-E6F5-114D-949F-487B7BFA388C}" name="actividad_subsector_resolucion_mecon" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{1475CC17-5B24-3247-8DBA-0625A938B1B7}" name="provincia" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{47AF60A5-F6B3-8743-8C92-1EB7255A904F}" name="localidad_region" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{75050396-7FEE-5341-9B55-07F221AA6F90}" name="inversion_total_mill_usd" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{A7D4770F-B48F-9443-B4A0-4629A448E999}" name="inversion_total_resolucion_mill_usd" dataDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{1602558E-3054-8C4C-9A58-AB8CCCD77682}" name="inversion_activos_computables_mill_usd" dataDxfId="16"/>
+    <tableColumn id="28" xr3:uid="{87595E4D-D42F-354A-9940-89724D3641FE}" name="inversion_activos_computables_comprometida_anio_1_mill_usd" dataDxfId="15"/>
+    <tableColumn id="29" xr3:uid="{688CE13F-074F-304D-836A-8560E747EB65}" name="inversion_activos_computables_comprometida_anio_2_mill_usd" dataDxfId="14"/>
+    <tableColumn id="30" xr3:uid="{B6018A02-36C0-DD40-A886-EEE247A26505}" name="inversion_activos_computables_comprometida_2_anios_mill_usd" dataDxfId="13">
       <calculatedColumnFormula>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D9B1B5B6-782F-2243-91BD-908F3BAD2DE1}" name="estado_administrativo" dataDxfId="13"/>
-    <tableColumn id="17" xr3:uid="{03E27E62-7FEF-084F-B60F-9D8063323ACC}" name="empleos_directos_indirectos_informados" dataDxfId="5"/>
-    <tableColumn id="27" xr3:uid="{D7C6BCCC-1B44-1443-8A03-2D0A63BC3776}" name="fecha_limite_inversion_minima_activos_computables" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{8E1C53B8-81DA-0043-91C5-F9A87892E325}" name="fecha_presentacion" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{2487DCCA-74EE-1743-B2CF-7169CF1BEBD2}" name="fecha_adhesion_rigi" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{51CF8FC1-2018-404C-A94F-1B1821BFB436}" name="fecha_publicacion_bo" dataDxfId="0"/>
-    <tableColumn id="21" xr3:uid="{57FDDB6F-D25E-3742-BBE3-196B6D307586}" name="norma_aprobacion" dataDxfId="1"/>
-    <tableColumn id="22" xr3:uid="{5FB062D4-AACF-864F-BFDC-22BF7798BAE5}" name="clasificacion_preexistencia_boletin_oficial" dataDxfId="12"/>
-    <tableColumn id="23" xr3:uid="{2371D7C3-27BF-8B4D-9413-38667163C45E}" name="justificacion_preexistencia_boletin_oficial" dataDxfId="11"/>
-    <tableColumn id="24" xr3:uid="{6EB99972-175D-EC4A-8EB6-3F4E07EFB52D}" name="link_norma" dataDxfId="10"/>
-    <tableColumn id="25" xr3:uid="{968AE59F-CF82-D848-82E7-EE1B09768E94}" name="fuentes" dataDxfId="9"/>
-    <tableColumn id="26" xr3:uid="{254939B9-204E-4D4D-9217-E3D8F271ED16}" name="links_fuentes" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{D9B1B5B6-782F-2243-91BD-908F3BAD2DE1}" name="estado_administrativo" dataDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{03E27E62-7FEF-084F-B60F-9D8063323ACC}" name="empleos_directos_indirectos_informados" dataDxfId="11"/>
+    <tableColumn id="27" xr3:uid="{D7C6BCCC-1B44-1443-8A03-2D0A63BC3776}" name="fecha_limite_inversion_minima_activos_computables" dataDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{8E1C53B8-81DA-0043-91C5-F9A87892E325}" name="fecha_presentacion" dataDxfId="9"/>
+    <tableColumn id="19" xr3:uid="{2487DCCA-74EE-1743-B2CF-7169CF1BEBD2}" name="fecha_adhesion_rigi" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{51CF8FC1-2018-404C-A94F-1B1821BFB436}" name="fecha_publicacion_bo" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{57FDDB6F-D25E-3742-BBE3-196B6D307586}" name="norma_aprobacion" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{5FB062D4-AACF-864F-BFDC-22BF7798BAE5}" name="clasificacion_preexistencia_boletin_oficial" dataDxfId="5"/>
+    <tableColumn id="23" xr3:uid="{2371D7C3-27BF-8B4D-9413-38667163C45E}" name="justificacion_preexistencia_boletin_oficial" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{6EB99972-175D-EC4A-8EB6-3F4E07EFB52D}" name="link_norma" dataDxfId="3"/>
+    <tableColumn id="25" xr3:uid="{968AE59F-CF82-D848-82E7-EE1B09768E94}" name="fuentes" dataDxfId="2"/>
+    <tableColumn id="26" xr3:uid="{254939B9-204E-4D4D-9217-E3D8F271ED16}" name="links_fuentes" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2994,7 +3094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19742F29-8880-E54E-B5B1-A7D7707C4679}">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A1:AD47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -3026,13 +3126,13 @@
   <sheetData>
     <row r="1" spans="1:30" ht="34">
       <c r="A1" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>362</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>363</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>0</v>
@@ -3044,7 +3144,7 @@
         <v>169</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>2</v>
@@ -3053,7 +3153,7 @@
         <v>3</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>4</v>
@@ -3062,3544 +3162,3665 @@
         <v>5</v>
       </c>
       <c r="M1" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="N1" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="T1" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="U1" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="V1" s="18" t="s">
+      <c r="U1" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="V1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="W1" s="18" t="s">
+      <c r="W1" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="X1" s="18" t="s">
+      <c r="X1" s="7" t="s">
         <v>152</v>
       </c>
       <c r="Y1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="Z1" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="AA1" s="6" t="s">
         <v>374</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>375</v>
       </c>
       <c r="AB1" s="6" t="s">
         <v>126</v>
       </c>
       <c r="AC1" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="AD1" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="AD1" s="6" t="s">
-        <v>377</v>
-      </c>
     </row>
     <row r="2" spans="1:30" ht="102">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="B2" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="9">
         <v>1</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="M2" s="16">
+      <c r="M2" s="10">
         <v>550</v>
       </c>
-      <c r="N2" s="16">
+      <c r="N2" s="10">
         <v>550</v>
       </c>
-      <c r="O2" s="16">
+      <c r="O2" s="10">
         <v>513</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="11">
         <v>393.61748899999998</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="11">
         <v>30.575689000000001</v>
       </c>
-      <c r="R2" s="17">
+      <c r="R2" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>424.19317799999999</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="S2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T2" s="14">
+      <c r="T2" s="8">
         <v>7535</v>
       </c>
-      <c r="U2" s="18">
+      <c r="U2" s="13">
         <v>46387</v>
       </c>
-      <c r="V2" s="40">
+      <c r="V2" s="14">
         <v>45957</v>
       </c>
-      <c r="W2" s="40">
+      <c r="W2" s="14">
         <v>46142</v>
       </c>
-      <c r="X2" s="40">
+      <c r="X2" s="14">
         <v>46154</v>
       </c>
-      <c r="Y2" s="14" t="s">
+      <c r="Y2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="Z2" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AA2" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="AB2" s="31" t="s">
+      <c r="AB2" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="AC2" s="14" t="s">
+      <c r="AC2" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="AD2" s="6"/>
+      <c r="AD2" s="16"/>
     </row>
     <row r="3" spans="1:30" ht="102">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="17">
         <v>2</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="18">
         <v>764</v>
       </c>
-      <c r="N3" s="8">
+      <c r="N3" s="18">
         <v>482</v>
       </c>
-      <c r="O3" s="8">
+      <c r="O3" s="18">
         <v>482</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="11">
         <v>98.5</v>
       </c>
-      <c r="Q3" s="10">
+      <c r="Q3" s="11">
         <v>253.9</v>
       </c>
-      <c r="R3" s="10">
+      <c r="R3" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>352.4</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T3" s="6">
+      <c r="T3" s="16">
         <v>2013</v>
       </c>
-      <c r="U3" s="18">
+      <c r="U3" s="13">
         <v>46721</v>
       </c>
-      <c r="V3" s="18">
+      <c r="V3" s="13">
         <v>45981</v>
       </c>
-      <c r="W3" s="18">
+      <c r="W3" s="13">
         <v>46080</v>
       </c>
-      <c r="X3" s="18">
+      <c r="X3" s="13">
         <v>46149</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Y3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="Z3" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="AA3" s="6" t="s">
+      <c r="AA3" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="AB3" s="32" t="s">
+      <c r="AB3" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="AC3" s="6" t="s">
+      <c r="AC3" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="AD3" s="6"/>
+      <c r="AD3" s="16"/>
     </row>
     <row r="4" spans="1:30" ht="102">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="9">
         <v>3</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="18">
         <v>665</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4" s="18">
         <v>520</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O4" s="18">
         <v>520</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="11">
         <v>46.741253999999998</v>
       </c>
-      <c r="Q4" s="10">
+      <c r="Q4" s="11">
         <v>43.858696000000002</v>
       </c>
-      <c r="R4" s="10">
+      <c r="R4" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>90.599950000000007</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="16">
         <v>4500</v>
       </c>
-      <c r="U4" s="18">
+      <c r="U4" s="13">
         <v>47118</v>
       </c>
-      <c r="V4" s="18">
+      <c r="V4" s="13">
         <v>45814</v>
       </c>
-      <c r="W4" s="18">
+      <c r="W4" s="13">
         <v>45988</v>
       </c>
-      <c r="X4" s="18">
+      <c r="X4" s="13">
         <v>46035</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Y4" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="Z4" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AA4" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="AB4" s="32" t="s">
+      <c r="AB4" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="AC4" s="6" t="s">
+      <c r="AC4" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="AD4" s="6"/>
+      <c r="AD4" s="16"/>
     </row>
     <row r="5" spans="1:30" ht="238">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="17">
         <v>4</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="18">
         <v>276</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="18">
         <v>276</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="18">
         <v>255</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="11">
         <v>80.371903000000003</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="11">
         <v>136.091475</v>
       </c>
-      <c r="R5" s="10">
+      <c r="R5" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>216.46337800000001</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="S5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="6">
+      <c r="T5" s="16">
         <v>165</v>
       </c>
-      <c r="U5" s="18">
+      <c r="U5" s="13">
         <v>46721</v>
       </c>
-      <c r="V5" s="18">
+      <c r="V5" s="13">
         <v>45656</v>
       </c>
-      <c r="W5" s="18">
+      <c r="W5" s="13">
         <v>45863</v>
       </c>
-      <c r="X5" s="18">
+      <c r="X5" s="13">
         <v>45895</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Y5" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="Z5" s="6" t="s">
+      <c r="Z5" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="AA5" s="6" t="s">
+      <c r="AA5" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="AB5" s="32" t="s">
+      <c r="AB5" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="AC5" s="6" t="s">
+      <c r="AC5" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="AD5" s="6"/>
+      <c r="AD5" s="16"/>
     </row>
     <row r="6" spans="1:30" ht="102">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="9">
         <v>5</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>454</v>
-      </c>
-      <c r="F6" s="14" t="s">
+      <c r="E6" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14" t="s">
+      <c r="J6" s="8"/>
+      <c r="K6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="10">
         <v>211</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N6" s="10">
         <v>212</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O6" s="10">
         <v>212</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="11">
         <f>Tabla22[[#This Row],[inversion_activos_computables_comprometida_2_anios_mill_usd]]/2</f>
         <v>102.27200000000001</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q6" s="11">
         <f>Tabla22[[#This Row],[inversion_activos_computables_comprometida_2_anios_mill_usd]]/2</f>
         <v>102.27200000000001</v>
       </c>
-      <c r="R6" s="10">
+      <c r="R6" s="11">
         <v>204.54400000000001</v>
       </c>
-      <c r="S6" s="14" t="s">
+      <c r="S6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T6" s="14">
+      <c r="T6" s="8">
         <v>384</v>
       </c>
-      <c r="U6" s="18">
+      <c r="U6" s="13">
         <v>46417</v>
       </c>
-      <c r="V6" s="40">
+      <c r="V6" s="14">
         <v>45590</v>
       </c>
-      <c r="W6" s="40">
+      <c r="W6" s="14">
         <v>45642</v>
       </c>
-      <c r="X6" s="40">
+      <c r="X6" s="14">
         <v>45664</v>
       </c>
-      <c r="Y6" s="14" t="s">
+      <c r="Y6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="Z6" s="14" t="s">
+      <c r="Z6" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="AA6" s="14" t="s">
+      <c r="AA6" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="AB6" s="31" t="s">
+      <c r="AB6" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="AC6" s="14" t="s">
+      <c r="AC6" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="AD6" s="6"/>
+      <c r="AD6" s="16"/>
     </row>
     <row r="7" spans="1:30" ht="221">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="17">
         <v>6</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="10">
         <v>15156</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="10">
         <v>6878</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O7" s="10">
         <v>2825</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="11">
         <v>105</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="Q7" s="11">
         <v>354</v>
       </c>
-      <c r="R7" s="17">
+      <c r="R7" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>459</v>
       </c>
-      <c r="S7" s="14" t="s">
+      <c r="S7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T7" s="14">
+      <c r="T7" s="8">
         <v>836</v>
       </c>
-      <c r="U7" s="18">
+      <c r="U7" s="13">
         <v>49674</v>
       </c>
-      <c r="V7" s="40">
+      <c r="V7" s="14">
         <v>45617</v>
       </c>
-      <c r="W7" s="40">
+      <c r="W7" s="14">
         <v>45775</v>
       </c>
-      <c r="X7" s="40">
+      <c r="X7" s="14">
         <v>45776</v>
       </c>
-      <c r="Y7" s="14" t="s">
+      <c r="Y7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="Z7" s="14" t="s">
+      <c r="Z7" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="AA7" s="14" t="s">
+      <c r="AA7" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="AB7" s="33" t="s">
+      <c r="AB7" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="AC7" s="14" t="s">
+      <c r="AC7" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="AD7" s="6"/>
-    </row>
-    <row r="8" spans="1:30" ht="153">
-      <c r="A8" s="6" t="s">
+      <c r="AD7" s="16"/>
+    </row>
+    <row r="8" spans="1:30" ht="136">
+      <c r="A8" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="9">
         <v>7</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="18">
         <v>286</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="18">
         <v>286</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="18">
         <v>286</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="11">
         <v>142.874</v>
       </c>
-      <c r="Q8" s="10">
+      <c r="Q8" s="11">
         <v>127.334</v>
       </c>
-      <c r="R8" s="10">
+      <c r="R8" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>270.20799999999997</v>
       </c>
-      <c r="S8" s="6" t="s">
+      <c r="S8" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T8" s="6">
+      <c r="T8" s="16">
         <v>3800</v>
       </c>
-      <c r="U8" s="18">
+      <c r="U8" s="13">
         <v>46326</v>
       </c>
-      <c r="V8" s="18">
+      <c r="V8" s="13">
         <v>45638</v>
       </c>
-      <c r="W8" s="18">
+      <c r="W8" s="13">
         <v>45807</v>
       </c>
-      <c r="X8" s="18">
+      <c r="X8" s="13">
         <v>45859</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Y8" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="Z8" s="6" t="s">
+      <c r="Z8" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="AA8" s="6" t="s">
+      <c r="AA8" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="AB8" s="34" t="s">
+      <c r="AB8" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="AC8" s="6" t="s">
+      <c r="AC8" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="AD8" s="6"/>
-    </row>
-    <row r="9" spans="1:30" ht="119">
-      <c r="A9" s="14" t="s">
+      <c r="AD8" s="16"/>
+    </row>
+    <row r="9" spans="1:30" ht="102">
+      <c r="A9" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="17">
         <v>8</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="10">
         <v>891</v>
       </c>
-      <c r="N9" s="16">
+      <c r="N9" s="10">
         <v>613</v>
       </c>
-      <c r="O9" s="16">
+      <c r="O9" s="10">
         <v>613</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="11">
         <v>40.542000000000002</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="Q9" s="11">
         <v>148.056566</v>
       </c>
-      <c r="R9" s="17">
+      <c r="R9" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>188.59856600000001</v>
       </c>
-      <c r="S9" s="14" t="s">
+      <c r="S9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T9" s="14">
+      <c r="T9" s="8">
         <v>6300</v>
       </c>
-      <c r="U9" s="18">
+      <c r="U9" s="13">
         <v>46997</v>
       </c>
-      <c r="V9" s="40">
+      <c r="V9" s="14">
         <v>45967</v>
       </c>
-      <c r="W9" s="40">
+      <c r="W9" s="14">
         <v>46155</v>
       </c>
-      <c r="X9" s="40">
+      <c r="X9" s="14">
         <v>46168</v>
       </c>
-      <c r="Y9" s="14" t="s">
+      <c r="Y9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="Z9" s="14" t="s">
+      <c r="Z9" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="AA9" s="14" t="s">
+      <c r="AA9" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="AB9" s="31" t="s">
+      <c r="AB9" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="AC9" s="14" t="s">
+      <c r="AC9" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="AD9" s="6"/>
-    </row>
-    <row r="10" spans="1:30" ht="136">
-      <c r="A10" s="6" t="s">
+      <c r="AD9" s="16"/>
+    </row>
+    <row r="10" spans="1:30" ht="119">
+      <c r="A10" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="9">
         <v>9</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="18">
         <v>2744</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="18">
         <v>2744</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="18">
         <v>2299</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="11">
         <v>516.96396300000004</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="Q10" s="11">
         <v>776.54763100000002</v>
       </c>
-      <c r="R10" s="10">
+      <c r="R10" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>1293.5115940000001</v>
       </c>
-      <c r="S10" s="6" t="s">
+      <c r="S10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T10" s="6">
+      <c r="T10" s="16">
         <v>1985</v>
       </c>
-      <c r="U10" s="18">
+      <c r="U10" s="13">
         <v>47299</v>
       </c>
-      <c r="V10" s="18">
+      <c r="V10" s="13">
         <v>45713</v>
       </c>
-      <c r="W10" s="18">
+      <c r="W10" s="13">
         <v>45796</v>
       </c>
-      <c r="X10" s="18">
+      <c r="X10" s="13">
         <v>45807</v>
       </c>
-      <c r="Y10" s="6" t="s">
+      <c r="Y10" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="Z10" s="6" t="s">
+      <c r="Z10" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="AA10" s="6" t="s">
+      <c r="AA10" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="AB10" s="32" t="s">
+      <c r="AB10" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="AC10" s="6" t="s">
+      <c r="AC10" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="AD10" s="6"/>
+      <c r="AD10" s="16"/>
     </row>
     <row r="11" spans="1:30" ht="255">
-      <c r="A11" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="17">
         <v>10</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="10">
         <v>531</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="10">
         <v>251</v>
       </c>
-      <c r="O11" s="16">
+      <c r="O11" s="10">
         <v>251</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="11">
         <v>92.662282000000005</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="Q11" s="11">
         <v>0</v>
       </c>
-      <c r="R11" s="17">
+      <c r="R11" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>92.662282000000005</v>
       </c>
-      <c r="S11" s="14" t="s">
+      <c r="S11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T11" s="14">
+      <c r="T11" s="8">
         <v>1273</v>
       </c>
-      <c r="U11" s="18">
+      <c r="U11" s="13">
         <v>46357</v>
       </c>
-      <c r="V11" s="40">
+      <c r="V11" s="14">
         <v>45898</v>
       </c>
-      <c r="W11" s="40">
+      <c r="W11" s="14">
         <v>46106</v>
       </c>
-      <c r="X11" s="40">
+      <c r="X11" s="14">
         <v>46112</v>
       </c>
-      <c r="Y11" s="14" t="s">
+      <c r="Y11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="Z11" s="14" t="s">
+      <c r="Z11" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AA11" s="14" t="s">
+      <c r="AA11" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="AB11" s="31" t="s">
+      <c r="AB11" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="AC11" s="14" t="s">
+      <c r="AC11" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="AD11" s="6"/>
-    </row>
-    <row r="12" spans="1:30" ht="136">
-      <c r="A12" s="14" t="s">
+      <c r="AD11" s="16"/>
+    </row>
+    <row r="12" spans="1:30" ht="119">
+      <c r="A12" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="9">
         <v>11</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="L12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="10">
         <v>277</v>
       </c>
-      <c r="N12" s="16">
+      <c r="N12" s="10">
         <v>277</v>
       </c>
-      <c r="O12" s="16">
+      <c r="O12" s="10">
         <v>277</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="11">
         <v>91.70244649</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="Q12" s="11">
         <v>74.2</v>
       </c>
-      <c r="R12" s="17">
+      <c r="R12" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>165.90244648999999</v>
       </c>
-      <c r="S12" s="14" t="s">
+      <c r="S12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T12" s="14">
+      <c r="T12" s="8">
         <v>9700</v>
       </c>
-      <c r="U12" s="18">
+      <c r="U12" s="13">
         <v>46478</v>
       </c>
-      <c r="V12" s="40">
+      <c r="V12" s="14">
         <v>45757</v>
       </c>
-      <c r="W12" s="40">
+      <c r="W12" s="14">
         <v>45953</v>
       </c>
-      <c r="X12" s="40">
+      <c r="X12" s="14">
         <v>45980</v>
       </c>
-      <c r="Y12" s="14" t="s">
+      <c r="Y12" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="Z12" s="14" t="s">
+      <c r="Z12" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="AA12" s="14" t="s">
+      <c r="AA12" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="AB12" s="31" t="s">
+      <c r="AB12" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="AC12" s="14" t="s">
+      <c r="AC12" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="AD12" s="6"/>
+      <c r="AD12" s="16"/>
     </row>
     <row r="13" spans="1:30" ht="372">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="B13" s="16" t="s">
+        <v>513</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="17">
         <v>12</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="H13" s="8" t="s">
+      <c r="G13" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="H13" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="18">
         <v>2900</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="18">
         <v>3050</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="18">
         <v>2486</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="11">
         <v>1318</v>
       </c>
-      <c r="Q13" s="10">
+      <c r="Q13" s="11">
         <v>1123</v>
       </c>
-      <c r="R13" s="10">
+      <c r="R13" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>2441</v>
       </c>
-      <c r="S13" s="6" t="s">
+      <c r="S13" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T13" s="6">
+      <c r="T13" s="16">
         <v>3108</v>
       </c>
-      <c r="U13" s="18">
+      <c r="U13" s="13">
         <v>47118</v>
       </c>
-      <c r="V13" s="18">
+      <c r="V13" s="13">
         <v>45611</v>
       </c>
-      <c r="W13" s="18">
+      <c r="W13" s="13">
         <v>45722</v>
       </c>
-      <c r="X13" s="18">
+      <c r="X13" s="13">
         <v>45736</v>
       </c>
-      <c r="Y13" s="6" t="s">
+      <c r="Y13" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="Z13" s="6" t="s">
+      <c r="Z13" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="AA13" s="6" t="s">
+      <c r="AA13" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="AB13" s="32" t="s">
+      <c r="AB13" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="AC13" s="6" t="s">
+      <c r="AC13" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="AD13" s="6"/>
-    </row>
-    <row r="14" spans="1:30" ht="153">
-      <c r="A14" s="14" t="s">
+      <c r="AD13" s="16"/>
+    </row>
+    <row r="14" spans="1:30" ht="136">
+      <c r="A14" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="9">
         <v>13</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="L14" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="10">
         <v>436</v>
       </c>
-      <c r="N14" s="16">
+      <c r="N14" s="10">
         <v>380</v>
       </c>
-      <c r="O14" s="16">
+      <c r="O14" s="10">
         <v>380</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="11">
         <v>79.228583</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="Q14" s="11">
         <v>83.169123999999996</v>
       </c>
-      <c r="R14" s="17">
+      <c r="R14" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>162.397707</v>
       </c>
-      <c r="S14" s="14" t="s">
+      <c r="S14" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T14" s="14">
+      <c r="T14" s="8">
         <v>1048</v>
       </c>
-      <c r="U14" s="18">
+      <c r="U14" s="13">
         <v>47118</v>
       </c>
-      <c r="V14" s="40">
+      <c r="V14" s="14">
         <v>45873</v>
       </c>
-      <c r="W14" s="40">
+      <c r="W14" s="14">
         <v>46050</v>
       </c>
-      <c r="X14" s="40">
+      <c r="X14" s="14">
         <v>46111</v>
       </c>
-      <c r="Y14" s="14" t="s">
+      <c r="Y14" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="Z14" s="14" t="s">
+      <c r="Z14" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AA14" s="14" t="s">
+      <c r="AA14" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="AB14" s="31" t="s">
+      <c r="AB14" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="AC14" s="14" t="s">
+      <c r="AC14" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="AD14" s="6"/>
+      <c r="AD14" s="16"/>
     </row>
     <row r="15" spans="1:30" ht="409.6">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17">
+        <v>14</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="F15" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="7">
-        <v>14</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="8" t="s">
+      <c r="G15" s="16"/>
+      <c r="H15" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6" t="s">
+      <c r="J15" s="16"/>
+      <c r="K15" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="18">
         <v>726</v>
       </c>
-      <c r="N15" s="8">
-        <v>726</v>
-      </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10">
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S15" s="6" t="s">
+      <c r="S15" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="T15" s="6"/>
-      <c r="U15" s="18"/>
-      <c r="V15" s="18">
+      <c r="T15" s="16"/>
+      <c r="U15" s="13"/>
+      <c r="V15" s="13">
         <v>45671</v>
       </c>
-      <c r="W15" s="18"/>
-      <c r="X15" s="18"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
-      <c r="AB15" s="6"/>
-      <c r="AC15" s="6" t="s">
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="16"/>
+      <c r="Z15" s="16"/>
+      <c r="AA15" s="16"/>
+      <c r="AB15" s="16"/>
+      <c r="AC15" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="AD15" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="AD15" s="6" t="s">
+    </row>
+    <row r="16" spans="1:30" ht="409.6">
+      <c r="A16" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" ht="409.6">
-      <c r="A16" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15">
+      <c r="C16" s="8"/>
+      <c r="D16" s="9">
         <v>15</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="14"/>
-      <c r="H16" s="16" t="s">
+      <c r="G16" s="8"/>
+      <c r="H16" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14" t="s">
+      <c r="J16" s="8"/>
+      <c r="K16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="L16" s="14" t="s">
+      <c r="L16" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="10">
         <v>232</v>
       </c>
-      <c r="N16" s="16">
-        <v>232</v>
-      </c>
-      <c r="O16" s="16"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="17">
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S16" s="14" t="s">
+      <c r="S16" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="T16" s="14"/>
-      <c r="U16" s="18"/>
-      <c r="V16" s="40">
+      <c r="T16" s="8"/>
+      <c r="U16" s="13"/>
+      <c r="V16" s="14">
         <v>45874</v>
       </c>
-      <c r="W16" s="40"/>
-      <c r="X16" s="40"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14"/>
-      <c r="AB16" s="14"/>
-      <c r="AC16" s="14" t="s">
+      <c r="W16" s="14"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="8"/>
+      <c r="AA16" s="8"/>
+      <c r="AB16" s="8"/>
+      <c r="AC16" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="AD16" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="AD16" s="6" t="s">
+    </row>
+    <row r="17" spans="1:30" ht="409.6">
+      <c r="A17" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="22">
+        <v>16</v>
+      </c>
+      <c r="E17" s="22" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="17" spans="1:30" ht="409.6">
-      <c r="A17" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>508</v>
-      </c>
-      <c r="C17" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="D17" s="35">
-        <v>16</v>
-      </c>
-      <c r="E17" s="35" t="s">
+      <c r="F17" s="22" t="s">
+        <v>504</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="I17" s="22" t="s">
         <v>300</v>
       </c>
-      <c r="F17" s="35" t="s">
-        <v>509</v>
-      </c>
-      <c r="G17" s="35" t="s">
-        <v>510</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="I17" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="J17" s="35" t="s">
-        <v>511</v>
-      </c>
-      <c r="K17" s="35" t="s">
+      <c r="J17" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="K17" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="L17" s="35" t="s">
-        <v>512</v>
-      </c>
-      <c r="M17" s="36">
+      <c r="L17" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="M17" s="23">
         <v>12240</v>
       </c>
-      <c r="N17" s="36">
+      <c r="N17" s="23">
         <v>12240</v>
       </c>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36">
+      <c r="O17" s="23"/>
+      <c r="P17" s="23">
         <v>635</v>
       </c>
-      <c r="Q17" s="36">
+      <c r="Q17" s="23">
         <v>892</v>
       </c>
-      <c r="R17" s="36">
+      <c r="R17" s="23">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>1527</v>
       </c>
-      <c r="S17" s="35" t="s">
+      <c r="S17" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="T17" s="35">
+      <c r="T17" s="22">
         <v>2301</v>
       </c>
-      <c r="U17" s="41">
+      <c r="U17" s="24">
         <v>47238</v>
       </c>
-      <c r="V17" s="41">
+      <c r="V17" s="24">
         <v>46135</v>
       </c>
-      <c r="W17" s="41">
+      <c r="W17" s="24">
         <v>46275</v>
       </c>
-      <c r="X17" s="41">
+      <c r="X17" s="24">
         <v>46314</v>
       </c>
-      <c r="Y17" s="35" t="s">
-        <v>516</v>
-      </c>
-      <c r="Z17" s="35" t="s">
+      <c r="Y17" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="Z17" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="AA17" s="35" t="s">
-        <v>513</v>
-      </c>
-      <c r="AB17" s="35" t="s">
-        <v>514</v>
-      </c>
-      <c r="AC17" s="35" t="s">
-        <v>517</v>
-      </c>
-      <c r="AD17" s="35" t="s">
-        <v>515</v>
+      <c r="AA17" s="22" t="s">
+        <v>508</v>
+      </c>
+      <c r="AB17" s="22" t="s">
+        <v>509</v>
+      </c>
+      <c r="AC17" s="22" t="s">
+        <v>512</v>
+      </c>
+      <c r="AD17" s="22" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="119">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="C18" s="14" t="s">
+      <c r="B18" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="9">
         <v>17</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="J18" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="K18" s="14" t="s">
+      <c r="K18" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="L18" s="14" t="s">
+      <c r="L18" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="10">
         <v>1241</v>
       </c>
-      <c r="N18" s="16">
+      <c r="N18" s="10">
         <v>1167</v>
       </c>
-      <c r="O18" s="16">
+      <c r="O18" s="10">
         <v>1167</v>
       </c>
-      <c r="P18" s="10">
+      <c r="P18" s="11">
         <v>37.967590000000001</v>
       </c>
-      <c r="Q18" s="10">
+      <c r="Q18" s="11">
         <v>58.787877000000002</v>
       </c>
-      <c r="R18" s="17">
+      <c r="R18" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>96.75546700000001</v>
       </c>
-      <c r="S18" s="14" t="s">
+      <c r="S18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T18" s="14">
+      <c r="T18" s="8">
         <v>1787</v>
       </c>
-      <c r="U18" s="18">
+      <c r="U18" s="13">
         <v>47665</v>
       </c>
-      <c r="V18" s="40">
+      <c r="V18" s="14">
         <v>45795</v>
       </c>
-      <c r="W18" s="40">
+      <c r="W18" s="14">
         <v>46151</v>
       </c>
-      <c r="X18" s="40">
+      <c r="X18" s="14">
         <v>46177</v>
       </c>
-      <c r="Y18" s="14" t="s">
+      <c r="Y18" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="Z18" s="14" t="s">
+      <c r="Z18" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AA18" s="14" t="s">
+      <c r="AA18" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="AB18" s="31" t="s">
+      <c r="AB18" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="AC18" s="14" t="s">
+      <c r="AC18" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AD18" s="6"/>
+      <c r="AD18" s="16"/>
     </row>
     <row r="19" spans="1:30" ht="409.6">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17">
+        <v>18</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="16"/>
+      <c r="H19" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7">
-        <v>18</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="L19" s="6" t="s">
+      <c r="L19" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="18">
         <v>380</v>
       </c>
-      <c r="N19" s="8">
-        <v>380</v>
-      </c>
-      <c r="O19" s="8"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10">
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S19" s="6" t="s">
+      <c r="S19" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="T19" s="6"/>
-      <c r="U19" s="18"/>
-      <c r="V19" s="18">
+      <c r="T19" s="16"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13">
         <v>45859</v>
       </c>
-      <c r="W19" s="18"/>
-      <c r="X19" s="18"/>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="6"/>
-      <c r="AA19" s="6"/>
-      <c r="AB19" s="6"/>
-      <c r="AC19" s="6" t="s">
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="16"/>
+      <c r="Z19" s="16"/>
+      <c r="AA19" s="16"/>
+      <c r="AB19" s="16"/>
+      <c r="AC19" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="AD19" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="AD19" s="6" t="s">
+    </row>
+    <row r="20" spans="1:30" ht="409.6">
+      <c r="A20" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="20" spans="1:30" ht="409.6">
-      <c r="A20" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15">
+      <c r="C20" s="8"/>
+      <c r="D20" s="9">
         <v>19</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="G20" s="14"/>
-      <c r="H20" s="16" t="s">
+      <c r="G20" s="8"/>
+      <c r="H20" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14" t="s">
+      <c r="J20" s="8"/>
+      <c r="K20" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L20" s="14" t="s">
+      <c r="L20" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="10">
         <v>9500</v>
       </c>
-      <c r="N20" s="16">
-        <v>9500</v>
-      </c>
-      <c r="O20" s="16"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="17">
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S20" s="14" t="s">
+      <c r="S20" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="T20" s="14"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="40">
+      <c r="T20" s="8"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="14">
         <v>45887</v>
       </c>
-      <c r="W20" s="40"/>
-      <c r="X20" s="40"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="14"/>
-      <c r="AC20" s="14" t="s">
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="8"/>
+      <c r="Z20" s="8"/>
+      <c r="AA20" s="8"/>
+      <c r="AB20" s="8"/>
+      <c r="AC20" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="AD20" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="AD20" s="6" t="s">
+    </row>
+    <row r="21" spans="1:30" ht="409.6">
+      <c r="A21" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="16" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="21" spans="1:30" ht="409.6">
-      <c r="A21" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7">
+      <c r="C21" s="16"/>
+      <c r="D21" s="17">
         <v>20</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="8" t="s">
+      <c r="F21" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="G21" s="16"/>
+      <c r="H21" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6" t="s">
+      <c r="I21" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="L21" s="6" t="s">
+      <c r="L21" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="18">
         <v>13800</v>
       </c>
-      <c r="N21" s="8">
-        <v>13800</v>
-      </c>
-      <c r="O21" s="8"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10">
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S21" s="6" t="s">
+      <c r="S21" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="T21" s="6"/>
-      <c r="U21" s="18"/>
-      <c r="V21" s="18">
+      <c r="T21" s="16"/>
+      <c r="U21" s="13"/>
+      <c r="V21" s="13">
         <v>46175</v>
       </c>
-      <c r="W21" s="18"/>
-      <c r="X21" s="18"/>
-      <c r="Y21" s="6"/>
-      <c r="Z21" s="6"/>
-      <c r="AA21" s="6"/>
-      <c r="AB21" s="6"/>
-      <c r="AC21" s="6" t="s">
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="16"/>
+      <c r="Z21" s="16"/>
+      <c r="AA21" s="16"/>
+      <c r="AB21" s="16"/>
+      <c r="AC21" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="AD21" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="AD21" s="6" t="s">
+    </row>
+    <row r="22" spans="1:30" ht="409.6">
+      <c r="A22" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="22" spans="1:30" ht="409.6">
-      <c r="A22" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="B22" s="14" t="s">
+      <c r="C22" s="8"/>
+      <c r="D22" s="9">
+        <v>21</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15">
-        <v>21</v>
-      </c>
-      <c r="E22" s="16" t="s">
+      <c r="F22" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="G22" s="8"/>
+      <c r="H22" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="G22" s="14"/>
-      <c r="H22" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14" t="s">
+      <c r="L22" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="L22" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="M22" s="16">
+      <c r="M22" s="10">
         <v>200</v>
       </c>
-      <c r="N22" s="16">
-        <v>200</v>
-      </c>
-      <c r="O22" s="16"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="17">
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S22" s="14" t="s">
+      <c r="S22" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="T22" s="14"/>
-      <c r="U22" s="18"/>
-      <c r="V22" s="40" t="s">
+      <c r="T22" s="8"/>
+      <c r="U22" s="13"/>
+      <c r="V22" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="W22" s="40"/>
-      <c r="X22" s="40"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-      <c r="AB22" s="14"/>
-      <c r="AC22" s="14" t="s">
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="8"/>
+      <c r="Z22" s="8"/>
+      <c r="AA22" s="8"/>
+      <c r="AB22" s="8"/>
+      <c r="AC22" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="AD22" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="AD22" s="6" t="s">
+    </row>
+    <row r="23" spans="1:30" ht="409.6">
+      <c r="A23" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="16" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="23" spans="1:30" ht="409.6">
-      <c r="A23" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7">
+      <c r="C23" s="16"/>
+      <c r="D23" s="17">
         <v>22</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="8" t="s">
+      <c r="G23" s="16"/>
+      <c r="H23" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6" t="s">
+      <c r="J23" s="16"/>
+      <c r="K23" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="L23" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="18">
         <v>206</v>
       </c>
-      <c r="N23" s="8">
-        <v>206</v>
-      </c>
-      <c r="O23" s="8"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10">
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S23" s="6" t="s">
+      <c r="S23" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="T23" s="6"/>
-      <c r="U23" s="18"/>
-      <c r="V23" s="18">
+      <c r="T23" s="16"/>
+      <c r="U23" s="13"/>
+      <c r="V23" s="13">
         <v>45805</v>
       </c>
-      <c r="W23" s="18"/>
-      <c r="X23" s="18"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="6"/>
-      <c r="AB23" s="6"/>
-      <c r="AC23" s="6" t="s">
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
+      <c r="Y23" s="16"/>
+      <c r="Z23" s="16"/>
+      <c r="AA23" s="16"/>
+      <c r="AB23" s="16"/>
+      <c r="AC23" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="AD23" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="AD23" s="6" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" ht="238">
-      <c r="A24" s="6" t="s">
-        <v>497</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="C24" s="6" t="s">
+    </row>
+    <row r="24" spans="1:30" ht="221">
+      <c r="A24" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="17">
         <v>23</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="H24" s="8" t="s">
+      <c r="F24" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>494</v>
+      </c>
+      <c r="H24" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="I24" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="K24" s="6" t="s">
+      <c r="I24" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="K24" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>501</v>
-      </c>
-      <c r="M24" s="8">
+      <c r="L24" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="M24" s="18">
         <v>6432</v>
       </c>
-      <c r="N24" s="8">
+      <c r="N24" s="18">
         <v>6432</v>
       </c>
-      <c r="O24" s="8"/>
-      <c r="P24" s="10">
+      <c r="O24" s="18"/>
+      <c r="P24" s="11">
         <v>1182.281332</v>
       </c>
-      <c r="Q24" s="10">
+      <c r="Q24" s="11">
         <v>577.93346799999995</v>
       </c>
-      <c r="R24" s="10">
+      <c r="R24" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>1760.2148</v>
       </c>
-      <c r="S24" s="6" t="s">
+      <c r="S24" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T24" s="6">
+      <c r="T24" s="16">
         <v>7900</v>
       </c>
-      <c r="U24" s="11">
+      <c r="U24" s="13">
         <v>46630</v>
       </c>
-      <c r="V24" s="18">
+      <c r="V24" s="13">
         <v>46101</v>
       </c>
-      <c r="W24" s="18">
+      <c r="W24" s="13">
         <v>46274</v>
       </c>
-      <c r="X24" s="18">
+      <c r="X24" s="13">
         <v>46304</v>
       </c>
-      <c r="Y24" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="Z24" s="6" t="s">
+      <c r="Y24" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="Z24" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="AA24" s="6" t="s">
+      <c r="AA24" s="16" t="s">
+        <v>497</v>
+      </c>
+      <c r="AB24" s="26" t="s">
+        <v>498</v>
+      </c>
+      <c r="AC24" s="16" t="s">
         <v>502</v>
       </c>
-      <c r="AB24" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="AC24" s="6" t="s">
-        <v>507</v>
-      </c>
-      <c r="AD24" s="6" t="s">
-        <v>504</v>
+      <c r="AD24" s="16" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="409.6">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17">
+        <v>24</v>
+      </c>
+      <c r="E25" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7">
-        <v>24</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="8" t="s">
+      <c r="G25" s="16"/>
+      <c r="H25" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6" t="s">
+      <c r="J25" s="16"/>
+      <c r="K25" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="L25" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="18">
         <v>4245</v>
       </c>
-      <c r="N25" s="8">
-        <v>4245</v>
-      </c>
-      <c r="O25" s="8"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10">
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S25" s="6" t="s">
+      <c r="S25" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="T25" s="6"/>
-      <c r="U25" s="18"/>
-      <c r="V25" s="18">
+      <c r="T25" s="16"/>
+      <c r="U25" s="13"/>
+      <c r="V25" s="13">
         <v>46081</v>
       </c>
-      <c r="W25" s="18"/>
-      <c r="X25" s="18"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="6"/>
-      <c r="AB25" s="6"/>
-      <c r="AC25" s="6" t="s">
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="16"/>
+      <c r="Z25" s="16"/>
+      <c r="AA25" s="16"/>
+      <c r="AB25" s="16"/>
+      <c r="AC25" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="AD25" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="AD25" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" ht="306">
-      <c r="A26" s="14" t="s">
+    </row>
+    <row r="26" spans="1:30" ht="289">
+      <c r="A26" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="9">
         <v>25</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="I26" s="16" t="s">
+      <c r="I26" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="J26" s="14" t="s">
+      <c r="J26" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="K26" s="14" t="s">
+      <c r="K26" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="L26" s="14" t="s">
+      <c r="L26" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="10">
         <v>4522</v>
       </c>
-      <c r="N26" s="16">
+      <c r="N26" s="10">
         <v>4521</v>
       </c>
-      <c r="O26" s="16">
+      <c r="O26" s="10">
         <v>4521</v>
       </c>
-      <c r="P26" s="10">
+      <c r="P26" s="11">
         <v>521</v>
       </c>
-      <c r="Q26" s="10">
+      <c r="Q26" s="11">
         <v>578</v>
       </c>
-      <c r="R26" s="17">
+      <c r="R26" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>1099</v>
       </c>
-      <c r="S26" s="14" t="s">
+      <c r="S26" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T26" s="14">
+      <c r="T26" s="8">
         <v>1733</v>
       </c>
-      <c r="U26" s="18">
+      <c r="U26" s="13">
         <v>48030</v>
       </c>
-      <c r="V26" s="40">
+      <c r="V26" s="14">
         <v>46090</v>
       </c>
-      <c r="W26" s="40">
+      <c r="W26" s="14">
         <v>46198</v>
       </c>
-      <c r="X26" s="40">
+      <c r="X26" s="14">
         <v>46224</v>
       </c>
-      <c r="Y26" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="Z26" s="14" t="s">
+      <c r="Y26" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="Z26" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AA26" s="14" t="s">
+      <c r="AA26" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="AB26" s="31" t="s">
+      <c r="AB26" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="AC26" s="14" t="s">
+      <c r="AC26" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="AD26" s="6"/>
+      <c r="AD26" s="16"/>
     </row>
     <row r="27" spans="1:30" ht="255">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="17">
+        <v>26</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D27" s="7">
-        <v>26</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="H27" s="8" t="s">
+      <c r="G27" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="H27" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="K27" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="L27" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="M27" s="8">
+      <c r="M27" s="18">
         <v>547</v>
       </c>
-      <c r="N27" s="8">
+      <c r="N27" s="18">
         <v>547</v>
       </c>
-      <c r="O27" s="8">
+      <c r="O27" s="18">
         <v>208</v>
       </c>
-      <c r="P27" s="10">
+      <c r="P27" s="11">
         <v>90.916876000000002</v>
       </c>
-      <c r="Q27" s="10">
+      <c r="Q27" s="11">
         <v>7.0831239999999998</v>
       </c>
-      <c r="R27" s="10">
+      <c r="R27" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>98</v>
       </c>
-      <c r="S27" s="6" t="s">
+      <c r="S27" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T27" s="6">
+      <c r="T27" s="16">
         <v>2335</v>
       </c>
-      <c r="U27" s="18">
+      <c r="U27" s="13">
         <v>47330</v>
       </c>
-      <c r="V27" s="18">
+      <c r="V27" s="13">
         <v>45978</v>
       </c>
-      <c r="W27" s="18">
+      <c r="W27" s="13">
         <v>46185</v>
       </c>
-      <c r="X27" s="18">
+      <c r="X27" s="13">
         <v>46234</v>
       </c>
-      <c r="Y27" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z27" s="6" t="s">
+      <c r="Y27" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="Z27" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="AA27" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="AB27" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="AC27" s="6" t="s">
+      <c r="AA27" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="AB27" s="27" t="s">
         <v>281</v>
       </c>
-      <c r="AD27" s="6"/>
+      <c r="AC27" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="AD27" s="16"/>
     </row>
     <row r="28" spans="1:30" ht="409.6">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="15">
+      <c r="B28" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="C28" s="8"/>
+      <c r="D28" s="9">
         <v>27</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G28" s="14"/>
-      <c r="H28" s="16" t="s">
+      <c r="G28" s="8"/>
+      <c r="H28" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I28" s="14" t="s">
+      <c r="I28" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14" t="s">
+      <c r="J28" s="8"/>
+      <c r="K28" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="L28" s="14" t="s">
+      <c r="L28" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="10">
         <v>818</v>
       </c>
-      <c r="N28" s="16">
-        <v>818</v>
-      </c>
-      <c r="O28" s="16"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="17">
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S28" s="14" t="s">
+      <c r="S28" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="T28" s="14"/>
-      <c r="U28" s="18"/>
-      <c r="V28" s="40">
+      <c r="T28" s="8"/>
+      <c r="U28" s="13"/>
+      <c r="V28" s="14">
         <v>45758</v>
       </c>
-      <c r="W28" s="40"/>
-      <c r="X28" s="40"/>
-      <c r="Y28" s="14"/>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="14"/>
-      <c r="AB28" s="14"/>
-      <c r="AC28" s="14" t="s">
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="8"/>
+      <c r="Z28" s="8"/>
+      <c r="AA28" s="8"/>
+      <c r="AB28" s="8"/>
+      <c r="AC28" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="AD28" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="AD28" s="6" t="s">
-        <v>328</v>
-      </c>
     </row>
     <row r="29" spans="1:30" ht="289">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7">
+      <c r="C29" s="16"/>
+      <c r="D29" s="17">
         <v>28</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="F29" s="6" t="s">
+      <c r="E29" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J29" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K29" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L29" s="6" t="s">
+      <c r="L29" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="M29" s="8">
+      <c r="M29" s="18">
         <v>710</v>
       </c>
-      <c r="N29" s="8">
+      <c r="N29" s="18">
         <v>710</v>
       </c>
-      <c r="O29" s="8">
+      <c r="O29" s="18">
         <v>594</v>
       </c>
-      <c r="P29" s="10">
+      <c r="P29" s="11">
         <v>107.53700000000001</v>
       </c>
-      <c r="Q29" s="10">
+      <c r="Q29" s="11">
         <v>308.048</v>
       </c>
-      <c r="R29" s="10">
+      <c r="R29" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>415.58500000000004</v>
       </c>
-      <c r="S29" s="6" t="s">
+      <c r="S29" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T29" s="6">
+      <c r="T29" s="16">
         <v>4406</v>
       </c>
-      <c r="U29" s="18">
+      <c r="U29" s="13">
         <v>46721</v>
       </c>
-      <c r="V29" s="18">
+      <c r="V29" s="13">
         <v>46063</v>
       </c>
-      <c r="W29" s="18">
+      <c r="W29" s="13">
         <v>46206</v>
       </c>
-      <c r="X29" s="18">
+      <c r="X29" s="13">
         <v>46232</v>
       </c>
-      <c r="Y29" s="6" t="s">
+      <c r="Y29" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="Z29" s="6" t="s">
+      <c r="Z29" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="AA29" s="6" t="s">
+      <c r="AA29" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="AB29" s="32" t="s">
+      <c r="AB29" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="AC29" s="6" t="s">
+      <c r="AC29" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="AD29" s="6"/>
-    </row>
-    <row r="30" spans="1:30" ht="306">
-      <c r="A30" s="14" t="s">
+      <c r="AD29" s="16"/>
+    </row>
+    <row r="30" spans="1:30" ht="289">
+      <c r="A30" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="C30" s="14" t="s">
+      <c r="B30" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="9">
         <v>29</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="G30" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="H30" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="I30" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="J30" s="14" t="s">
+      <c r="J30" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="K30" s="14" t="s">
+      <c r="K30" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L30" s="14" t="s">
+      <c r="L30" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M30" s="16">
+      <c r="M30" s="10">
         <v>9737</v>
       </c>
-      <c r="N30" s="16">
+      <c r="N30" s="10">
         <v>9737</v>
       </c>
-      <c r="O30" s="16">
+      <c r="O30" s="10">
         <v>9025</v>
       </c>
-      <c r="P30" s="10">
+      <c r="P30" s="11">
         <f>Tabla22[[#This Row],[inversion_activos_computables_comprometida_2_anios_mill_usd]]/2</f>
         <v>1004.6565000000001</v>
       </c>
-      <c r="Q30" s="10">
+      <c r="Q30" s="11">
         <f>Tabla22[[#This Row],[inversion_activos_computables_comprometida_2_anios_mill_usd]]/2</f>
         <v>1004.6565000000001</v>
       </c>
-      <c r="R30" s="10">
+      <c r="R30" s="11">
         <v>2009.3130000000001</v>
       </c>
-      <c r="S30" s="14" t="s">
+      <c r="S30" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T30" s="14">
+      <c r="T30" s="8">
         <v>31700</v>
       </c>
-      <c r="U30" s="18">
+      <c r="U30" s="13">
         <v>47118</v>
       </c>
-      <c r="V30" s="40">
+      <c r="V30" s="14">
         <v>46002</v>
       </c>
-      <c r="W30" s="40">
+      <c r="W30" s="14">
         <v>46176</v>
       </c>
-      <c r="X30" s="40">
+      <c r="X30" s="14">
         <v>46233</v>
       </c>
-      <c r="Y30" s="14" t="s">
+      <c r="Y30" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="Z30" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA30" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="AB30" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="Z30" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA30" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="AB30" s="31" t="s">
+      <c r="AC30" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="AC30" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="AD30" s="6"/>
-    </row>
-    <row r="31" spans="1:30" ht="409.6">
-      <c r="A31" s="14" t="s">
+      <c r="AD30" s="16"/>
+    </row>
+    <row r="31" spans="1:30" ht="388">
+      <c r="A31" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="17">
+        <v>30</v>
+      </c>
+      <c r="E31" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="7">
-        <v>30</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="F31" s="38" t="s">
-        <v>348</v>
-      </c>
-      <c r="G31" s="14"/>
-      <c r="H31" s="16" t="s">
+      <c r="F31" s="28" t="s">
+        <v>347</v>
+      </c>
+      <c r="G31" s="8"/>
+      <c r="H31" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="I31" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14" t="s">
+      <c r="I31" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="L31" s="14" t="s">
+      <c r="L31" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M31" s="16">
+      <c r="M31" s="10">
         <v>1000</v>
       </c>
-      <c r="N31" s="16">
-        <v>1000</v>
-      </c>
-      <c r="O31" s="16"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="17">
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S31" s="14" t="s">
+      <c r="S31" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="T31" s="14"/>
-      <c r="U31" s="18"/>
-      <c r="V31" s="40">
+      <c r="T31" s="8"/>
+      <c r="U31" s="13"/>
+      <c r="V31" s="14">
         <v>46157</v>
       </c>
-      <c r="W31" s="40"/>
-      <c r="X31" s="40"/>
-      <c r="Y31" s="14"/>
-      <c r="Z31" s="14"/>
-      <c r="AA31" s="14"/>
-      <c r="AB31" s="14"/>
-      <c r="AC31" s="14" t="s">
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="8"/>
+      <c r="Z31" s="8"/>
+      <c r="AA31" s="8"/>
+      <c r="AB31" s="8"/>
+      <c r="AC31" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="AD31" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="AD31" s="6" t="s">
-        <v>332</v>
-      </c>
     </row>
     <row r="32" spans="1:30" ht="119">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B32" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="C32" s="14" t="s">
+      <c r="B32" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="9">
         <v>31</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="H32" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I32" s="14" t="s">
+      <c r="I32" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="J32" s="14" t="s">
+      <c r="J32" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="K32" s="14" t="s">
+      <c r="K32" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L32" s="14" t="s">
+      <c r="L32" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M32" s="16">
+      <c r="M32" s="10">
         <v>2672</v>
       </c>
-      <c r="N32" s="16">
+      <c r="N32" s="10">
         <v>2672</v>
       </c>
-      <c r="O32" s="16">
+      <c r="O32" s="10">
         <v>2354</v>
       </c>
-      <c r="P32" s="10">
+      <c r="P32" s="11">
         <v>33.512551049999999</v>
       </c>
-      <c r="Q32" s="10">
+      <c r="Q32" s="11">
         <v>382.26276160999998</v>
       </c>
-      <c r="R32" s="17">
+      <c r="R32" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>415.77531266</v>
       </c>
-      <c r="S32" s="14" t="s">
+      <c r="S32" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T32" s="14">
+      <c r="T32" s="8">
         <v>7391</v>
       </c>
-      <c r="U32" s="18">
+      <c r="U32" s="13">
         <v>46752</v>
       </c>
-      <c r="V32" s="40">
+      <c r="V32" s="14">
         <v>45849</v>
       </c>
-      <c r="W32" s="40">
+      <c r="W32" s="14">
         <v>45925</v>
       </c>
-      <c r="X32" s="40">
+      <c r="X32" s="14">
         <v>45943</v>
       </c>
-      <c r="Y32" s="14" t="s">
+      <c r="Y32" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="Z32" s="14" t="s">
+      <c r="Z32" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="AA32" s="14" t="s">
+      <c r="AA32" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="AB32" s="31" t="s">
+      <c r="AB32" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="AC32" s="14" t="s">
+      <c r="AC32" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="AD32" s="6"/>
+      <c r="AD32" s="16"/>
     </row>
     <row r="33" spans="1:30" ht="34">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7">
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17">
         <v>32</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="G33" s="6"/>
-      <c r="H33" s="8" t="s">
+      <c r="G33" s="16"/>
+      <c r="H33" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6" t="s">
+      <c r="J33" s="16"/>
+      <c r="K33" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="L33" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="M33" s="8">
+      <c r="M33" s="18">
         <v>273</v>
       </c>
-      <c r="N33" s="8">
-        <v>273</v>
-      </c>
-      <c r="O33" s="8"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10">
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S33" s="6" t="s">
+      <c r="S33" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="T33" s="6"/>
-      <c r="U33" s="18"/>
-      <c r="V33" s="18">
+      <c r="T33" s="16"/>
+      <c r="U33" s="13"/>
+      <c r="V33" s="13">
         <v>45717</v>
       </c>
-      <c r="W33" s="18"/>
-      <c r="X33" s="18"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="6"/>
-      <c r="AA33" s="6"/>
-      <c r="AB33" s="6"/>
-      <c r="AC33" s="6" t="s">
+      <c r="W33" s="13"/>
+      <c r="X33" s="13"/>
+      <c r="Y33" s="16"/>
+      <c r="Z33" s="16"/>
+      <c r="AA33" s="16"/>
+      <c r="AB33" s="16"/>
+      <c r="AC33" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="AD33" s="6"/>
+      <c r="AD33" s="16"/>
     </row>
     <row r="34" spans="1:30" ht="136">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="17">
+        <v>33</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="F34" s="16" t="s">
         <v>457</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="G34" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="K34" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D34" s="7">
-        <v>33</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="L34" s="14" t="s">
-        <v>316</v>
-      </c>
-      <c r="M34" s="39">
+      <c r="L34" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="M34" s="29">
         <v>365.39866899999998</v>
       </c>
-      <c r="N34" s="39">
+      <c r="N34" s="29">
         <v>365.39866899999998</v>
       </c>
-      <c r="O34" s="8">
+      <c r="O34" s="18">
         <v>359.16436099999999</v>
       </c>
-      <c r="P34" s="10">
+      <c r="P34" s="11">
         <v>121.613889</v>
       </c>
-      <c r="Q34" s="10">
+      <c r="Q34" s="11">
         <v>152.70910599999999</v>
       </c>
-      <c r="R34" s="10">
+      <c r="R34" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>274.32299499999999</v>
       </c>
-      <c r="S34" s="6" t="s">
+      <c r="S34" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T34" s="8">
+      <c r="T34" s="18">
         <v>792</v>
       </c>
-      <c r="U34" s="18">
+      <c r="U34" s="13">
         <v>46661</v>
       </c>
-      <c r="V34" s="18">
+      <c r="V34" s="13">
         <v>46099</v>
       </c>
-      <c r="W34" s="18">
+      <c r="W34" s="13">
         <v>46231</v>
       </c>
-      <c r="X34" s="18">
+      <c r="X34" s="13">
         <v>46260</v>
       </c>
-      <c r="Y34" s="6" t="s">
+      <c r="Y34" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="Z34" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA34" s="16" t="s">
         <v>464</v>
       </c>
-      <c r="Z34" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA34" s="6" t="s">
+      <c r="AB34" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="AC34" s="16" t="s">
         <v>465</v>
       </c>
-      <c r="AB34" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="AC34" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="AD34" s="6"/>
+      <c r="AD34" s="16"/>
     </row>
     <row r="35" spans="1:30" ht="409.6">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7">
+      <c r="B35" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="C35" s="16"/>
+      <c r="D35" s="17">
         <v>34</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G35" s="6"/>
-      <c r="H35" s="8" t="s">
+      <c r="G35" s="16"/>
+      <c r="H35" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6" t="s">
+      <c r="J35" s="16"/>
+      <c r="K35" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L35" s="6" t="s">
+      <c r="L35" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="M35" s="8">
+      <c r="M35" s="18">
         <v>4000</v>
       </c>
-      <c r="N35" s="8">
-        <v>4000</v>
-      </c>
-      <c r="O35" s="8"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10">
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S35" s="6" t="s">
+      <c r="S35" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="T35" s="6"/>
-      <c r="U35" s="18"/>
-      <c r="V35" s="18">
+      <c r="T35" s="16"/>
+      <c r="U35" s="13"/>
+      <c r="V35" s="13">
         <v>45887</v>
       </c>
-      <c r="W35" s="18"/>
-      <c r="X35" s="18"/>
-      <c r="Y35" s="6"/>
-      <c r="Z35" s="6"/>
-      <c r="AA35" s="6"/>
-      <c r="AB35" s="6"/>
-      <c r="AC35" s="6" t="s">
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="16"/>
+      <c r="Z35" s="16"/>
+      <c r="AA35" s="16"/>
+      <c r="AB35" s="16"/>
+      <c r="AC35" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="AD35" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="AD35" s="6" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="36" spans="1:30" ht="102">
-      <c r="A36" s="14" t="s">
+    </row>
+    <row r="36" spans="1:30" ht="372">
+      <c r="A36" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" s="9">
+        <v>35</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="I36" s="16" t="s">
         <v>469</v>
       </c>
-      <c r="B36" s="30" t="s">
-        <v>473</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D36" s="15">
-        <v>35</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="G36" s="30" t="s">
-        <v>468</v>
-      </c>
-      <c r="H36" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="I36" s="30" t="s">
-        <v>470</v>
-      </c>
-      <c r="J36" s="30" t="s">
-        <v>470</v>
-      </c>
-      <c r="K36" s="14" t="s">
+      <c r="J36" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="K36" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="L36" s="30" t="s">
-        <v>472</v>
-      </c>
-      <c r="M36" s="16">
+      <c r="L36" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="M36" s="10">
         <v>2693</v>
       </c>
-      <c r="N36" s="16">
+      <c r="N36" s="10">
         <v>2693</v>
       </c>
-      <c r="O36" s="16">
+      <c r="O36" s="10">
         <v>2693</v>
       </c>
-      <c r="P36" s="10">
+      <c r="P36" s="11">
         <v>785</v>
       </c>
-      <c r="Q36" s="10">
+      <c r="Q36" s="11">
         <v>881</v>
       </c>
-      <c r="R36" s="17">
+      <c r="R36" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>1666</v>
       </c>
-      <c r="S36" s="14" t="s">
+      <c r="S36" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="T36" s="14">
+      <c r="T36" s="8">
         <v>12500</v>
       </c>
-      <c r="U36" s="18">
+      <c r="U36" s="13">
         <v>47453</v>
       </c>
-      <c r="V36" s="40">
+      <c r="V36" s="14">
         <v>46133</v>
       </c>
-      <c r="W36" s="40">
+      <c r="W36" s="14">
         <v>46237</v>
       </c>
-      <c r="X36" s="40">
+      <c r="X36" s="14">
         <v>46272</v>
       </c>
-      <c r="Y36" s="14" t="s">
-        <v>471</v>
-      </c>
-      <c r="Z36" s="14" t="s">
+      <c r="Y36" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="Z36" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AA36" s="30" t="s">
-        <v>476</v>
-      </c>
-      <c r="AB36" s="19" t="s">
+      <c r="AA36" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="AB36" s="30" t="s">
+        <v>473</v>
+      </c>
+      <c r="AC36" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="AC36" s="14" t="s">
-        <v>475</v>
-      </c>
-      <c r="AD36" s="6"/>
+      <c r="AD36" s="16"/>
     </row>
     <row r="37" spans="1:30" ht="204">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="C37" s="6" t="s">
+      <c r="B37" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="C37" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="17">
         <v>36</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="G37" s="6" t="s">
+      <c r="F37" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="G37" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="I37" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J37" s="6" t="s">
+      <c r="J37" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="K37" s="6" t="s">
+      <c r="K37" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="L37" s="6" t="s">
+      <c r="L37" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M37" s="8">
+      <c r="M37" s="18">
         <v>1300</v>
       </c>
-      <c r="N37" s="8">
+      <c r="N37" s="18">
         <v>1300</v>
       </c>
-      <c r="O37" s="8">
+      <c r="O37" s="18">
         <v>955</v>
       </c>
-      <c r="P37" s="10">
+      <c r="P37" s="11">
         <v>454</v>
       </c>
-      <c r="Q37" s="10">
+      <c r="Q37" s="11">
         <v>501</v>
       </c>
-      <c r="R37" s="10">
+      <c r="R37" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>955</v>
       </c>
-      <c r="S37" s="6" t="s">
+      <c r="S37" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T37" s="6">
+      <c r="T37" s="16">
         <v>2489</v>
       </c>
-      <c r="U37" s="18">
+      <c r="U37" s="13">
         <v>46538</v>
       </c>
-      <c r="V37" s="18">
+      <c r="V37" s="13">
         <v>45950</v>
       </c>
-      <c r="W37" s="18">
+      <c r="W37" s="13">
         <v>46174</v>
       </c>
-      <c r="X37" s="18">
+      <c r="X37" s="13">
         <v>46198</v>
       </c>
-      <c r="Y37" s="6" t="s">
+      <c r="Y37" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="Z37" s="6" t="s">
+      <c r="Z37" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="AA37" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="AB37" s="37" t="s">
+      <c r="AA37" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="AB37" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="AC37" s="6" t="s">
+      <c r="AC37" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="AD37" s="6"/>
+      <c r="AD37" s="16"/>
     </row>
     <row r="38" spans="1:30" ht="102">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="C38" s="6" t="s">
+      <c r="B38" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C38" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="9">
         <v>37</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I38" s="6" t="s">
+      <c r="I38" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="J38" s="6" t="s">
+      <c r="J38" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="K38" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L38" s="6" t="s">
+      <c r="L38" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="M38" s="8">
+      <c r="M38" s="18">
         <v>292</v>
       </c>
-      <c r="N38" s="8">
+      <c r="N38" s="18">
         <v>217</v>
       </c>
-      <c r="O38" s="8">
+      <c r="O38" s="18">
         <v>217</v>
       </c>
-      <c r="P38" s="10">
+      <c r="P38" s="11">
         <v>31.112863000000001</v>
       </c>
-      <c r="Q38" s="10">
+      <c r="Q38" s="11">
         <v>51.531371</v>
       </c>
-      <c r="R38" s="10">
+      <c r="R38" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>82.644233999999997</v>
       </c>
-      <c r="S38" s="6" t="s">
+      <c r="S38" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T38" s="6">
+      <c r="T38" s="16">
         <v>670</v>
       </c>
-      <c r="U38" s="18">
+      <c r="U38" s="13">
         <v>47483</v>
       </c>
-      <c r="V38" s="18">
+      <c r="V38" s="13">
         <v>45594</v>
       </c>
-      <c r="W38" s="18">
+      <c r="W38" s="13">
         <v>45855</v>
       </c>
-      <c r="X38" s="18">
+      <c r="X38" s="13">
         <v>45896</v>
       </c>
-      <c r="Y38" s="6" t="s">
+      <c r="Y38" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="Z38" s="6" t="s">
+      <c r="Z38" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="AA38" s="6" t="s">
+      <c r="AA38" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="AB38" s="37" t="s">
+      <c r="AB38" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="AC38" s="6" t="s">
+      <c r="AC38" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="AD38" s="6"/>
+      <c r="AD38" s="16"/>
     </row>
     <row r="39" spans="1:30" ht="409.6">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="17">
+        <v>38</v>
+      </c>
+      <c r="E39" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="7">
-        <v>38</v>
-      </c>
-      <c r="E39" s="16" t="s">
+      <c r="F39" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="F39" s="14" t="s">
-        <v>337</v>
-      </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="16" t="s">
+      <c r="G39" s="8"/>
+      <c r="H39" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I39" s="14" t="s">
+      <c r="I39" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14" t="s">
+      <c r="J39" s="8"/>
+      <c r="K39" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="L39" s="14" t="s">
+      <c r="L39" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="M39" s="16">
+      <c r="M39" s="10">
         <v>1151</v>
       </c>
-      <c r="N39" s="16">
-        <v>1151</v>
-      </c>
-      <c r="O39" s="16"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="17">
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="11"/>
+      <c r="Q39" s="11"/>
+      <c r="R39" s="12">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S39" s="14" t="s">
+      <c r="S39" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="T39" s="14"/>
-      <c r="U39" s="18"/>
-      <c r="V39" s="40">
+      <c r="T39" s="8"/>
+      <c r="U39" s="13"/>
+      <c r="V39" s="14">
         <v>46111</v>
       </c>
-      <c r="W39" s="40"/>
-      <c r="X39" s="40"/>
-      <c r="Y39" s="14"/>
-      <c r="Z39" s="14"/>
-      <c r="AA39" s="14"/>
-      <c r="AB39" s="14"/>
-      <c r="AC39" s="14" t="s">
+      <c r="W39" s="14"/>
+      <c r="X39" s="14"/>
+      <c r="Y39" s="8"/>
+      <c r="Z39" s="8"/>
+      <c r="AA39" s="8"/>
+      <c r="AB39" s="8"/>
+      <c r="AC39" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="AD39" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="AD39" s="6" t="s">
+    </row>
+    <row r="40" spans="1:30" ht="409.6">
+      <c r="A40" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B40" s="16" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="40" spans="1:30" ht="409.6">
-      <c r="A40" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="15">
+      <c r="C40" s="16"/>
+      <c r="D40" s="9">
         <v>39</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="G40" s="6"/>
-      <c r="H40" s="8" t="s">
+      <c r="F40" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="G40" s="16"/>
+      <c r="H40" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="I40" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6" t="s">
+      <c r="I40" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="L40" s="6" t="s">
+      <c r="L40" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M40" s="8">
+      <c r="M40" s="18">
         <v>25000</v>
       </c>
-      <c r="N40" s="8">
-        <v>25000</v>
-      </c>
-      <c r="O40" s="8"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
-      <c r="R40" s="10">
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S40" s="6" t="s">
+      <c r="S40" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="T40" s="6"/>
-      <c r="U40" s="18"/>
-      <c r="V40" s="18">
+      <c r="T40" s="16"/>
+      <c r="U40" s="13"/>
+      <c r="V40" s="13">
         <v>46157</v>
       </c>
-      <c r="W40" s="18"/>
-      <c r="X40" s="18"/>
-      <c r="Y40" s="6"/>
-      <c r="Z40" s="6"/>
-      <c r="AA40" s="6"/>
-      <c r="AB40" s="6"/>
-      <c r="AC40" s="6" t="s">
+      <c r="W40" s="13"/>
+      <c r="X40" s="13"/>
+      <c r="Y40" s="16"/>
+      <c r="Z40" s="16"/>
+      <c r="AA40" s="16"/>
+      <c r="AB40" s="16"/>
+      <c r="AC40" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="AD40" s="16" t="s">
         <v>341</v>
       </c>
-      <c r="AD40" s="6" t="s">
+    </row>
+    <row r="41" spans="1:30" ht="409.6">
+      <c r="A41" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="B41" s="16" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="41" spans="1:30" ht="409.6">
-      <c r="A41" s="6" t="s">
+      <c r="C41" s="16"/>
+      <c r="D41" s="17">
+        <v>40</v>
+      </c>
+      <c r="E41" s="18" t="s">
         <v>290</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7">
-        <v>40</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="G41" s="6"/>
-      <c r="H41" s="8" t="s">
+      <c r="F41" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="G41" s="16"/>
+      <c r="H41" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="I41" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6" t="s">
+      <c r="I41" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="L41" s="6" t="s">
+      <c r="L41" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M41" s="8">
+      <c r="M41" s="18">
         <v>5800</v>
       </c>
-      <c r="N41" s="8">
-        <v>5800</v>
-      </c>
-      <c r="O41" s="8"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10">
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="11"/>
+      <c r="R41" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S41" s="6" t="s">
+      <c r="S41" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="T41" s="12"/>
-      <c r="U41" s="18"/>
-      <c r="V41" s="18">
+      <c r="T41" s="31"/>
+      <c r="U41" s="13"/>
+      <c r="V41" s="13">
         <v>46224</v>
       </c>
-      <c r="W41" s="18"/>
-      <c r="X41" s="18"/>
-      <c r="Y41" s="6"/>
-      <c r="Z41" s="6"/>
-      <c r="AA41" s="6"/>
-      <c r="AB41" s="6"/>
-      <c r="AC41" s="6" t="s">
+      <c r="W41" s="13"/>
+      <c r="X41" s="13"/>
+      <c r="Y41" s="16"/>
+      <c r="Z41" s="16"/>
+      <c r="AA41" s="16"/>
+      <c r="AB41" s="16"/>
+      <c r="AC41" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="AD41" s="19" t="s">
         <v>344</v>
       </c>
-      <c r="AD41" s="32" t="s">
-        <v>345</v>
-      </c>
     </row>
     <row r="42" spans="1:30" ht="409.6">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="B42" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="C42" s="16"/>
+      <c r="D42" s="17">
+        <v>41</v>
+      </c>
+      <c r="E42" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="7">
-        <v>41</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="8" t="s">
+      <c r="F42" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="G42" s="16"/>
+      <c r="H42" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="I42" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="L42" s="6" t="s">
+      <c r="J42" s="16"/>
+      <c r="K42" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="L42" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M42" s="8">
+      <c r="M42" s="18">
         <v>51000</v>
       </c>
-      <c r="N42" s="8"/>
-      <c r="O42" s="8"/>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
-      <c r="R42" s="10">
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="11"/>
+      <c r="R42" s="11">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S42" s="6" t="s">
+      <c r="S42" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="T42" s="8"/>
-      <c r="U42" s="18"/>
-      <c r="V42" s="18">
+      <c r="T42" s="18"/>
+      <c r="U42" s="13"/>
+      <c r="V42" s="13">
         <v>46247</v>
       </c>
-      <c r="W42" s="18"/>
-      <c r="X42" s="18"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="6"/>
-      <c r="AB42" s="6"/>
-      <c r="AC42" s="6" t="s">
+      <c r="W42" s="13"/>
+      <c r="X42" s="13"/>
+      <c r="Y42" s="16"/>
+      <c r="Z42" s="16"/>
+      <c r="AA42" s="16"/>
+      <c r="AB42" s="16"/>
+      <c r="AC42" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="AD42" s="16" t="s">
         <v>355</v>
       </c>
-      <c r="AD42" s="6" t="s">
-        <v>356</v>
-      </c>
     </row>
     <row r="43" spans="1:30" ht="409.6">
-      <c r="A43" s="20" t="s">
+      <c r="A43" s="46" t="s">
+        <v>484</v>
+      </c>
+      <c r="B43" s="46" t="s">
+        <v>514</v>
+      </c>
+      <c r="C43" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="D43" s="47">
+        <v>42</v>
+      </c>
+      <c r="E43" s="46" t="s">
+        <v>476</v>
+      </c>
+      <c r="F43" s="46" t="s">
+        <v>515</v>
+      </c>
+      <c r="G43" s="48" t="s">
+        <v>516</v>
+      </c>
+      <c r="H43" s="46" t="s">
+        <v>477</v>
+      </c>
+      <c r="I43" s="46" t="s">
+        <v>517</v>
+      </c>
+      <c r="J43" s="46" t="s">
+        <v>518</v>
+      </c>
+      <c r="K43" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="L43" s="46" t="s">
+        <v>478</v>
+      </c>
+      <c r="M43" s="49">
+        <v>1341</v>
+      </c>
+      <c r="N43" s="49">
+        <v>1252.9261080000001</v>
+      </c>
+      <c r="O43" s="49">
+        <v>1252.9261080000001</v>
+      </c>
+      <c r="P43" s="49">
+        <v>19.5</v>
+      </c>
+      <c r="Q43" s="49">
+        <v>147.75303099999999</v>
+      </c>
+      <c r="R43" s="49">
+        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
+        <v>167.25303099999999</v>
+      </c>
+      <c r="S43" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="T43" s="47">
+        <v>6225</v>
+      </c>
+      <c r="U43" s="50">
+        <v>47026</v>
+      </c>
+      <c r="V43" s="50">
+        <v>46181</v>
+      </c>
+      <c r="W43" s="50">
+        <v>46294</v>
+      </c>
+      <c r="X43" s="50">
+        <v>46317</v>
+      </c>
+      <c r="Y43" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="Z43" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA43" s="46" t="s">
+        <v>520</v>
+      </c>
+      <c r="AB43" s="51" t="s">
+        <v>532</v>
+      </c>
+      <c r="AC43" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="AD43" s="46" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" ht="409.6">
+      <c r="A44" s="32" t="s">
+        <v>485</v>
+      </c>
+      <c r="B44" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32">
+        <v>43</v>
+      </c>
+      <c r="E44" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="I44" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32" t="s">
+        <v>480</v>
+      </c>
+      <c r="L44" s="32" t="s">
+        <v>481</v>
+      </c>
+      <c r="M44" s="32">
+        <v>1200</v>
+      </c>
+      <c r="N44" s="32"/>
+      <c r="O44" s="32"/>
+      <c r="P44" s="32"/>
+      <c r="Q44" s="32"/>
+      <c r="R44" s="32"/>
+      <c r="S44" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="T44" s="32"/>
+      <c r="U44" s="33"/>
+      <c r="V44" s="34">
+        <v>46296</v>
+      </c>
+      <c r="W44" s="33"/>
+      <c r="X44" s="33"/>
+      <c r="Y44" s="32"/>
+      <c r="Z44" s="32"/>
+      <c r="AA44" s="32"/>
+      <c r="AB44" s="32"/>
+      <c r="AC44" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="AD44" s="32" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" ht="272">
+      <c r="A45" s="35" t="s">
+        <v>486</v>
+      </c>
+      <c r="B45" s="35" t="s">
+        <v>487</v>
+      </c>
+      <c r="C45" s="35"/>
+      <c r="D45" s="36">
+        <v>44</v>
+      </c>
+      <c r="E45" s="37" t="s">
         <v>488</v>
       </c>
-      <c r="B43" s="20" t="s">
-        <v>477</v>
-      </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="21">
-        <v>42</v>
-      </c>
-      <c r="E43" s="22" t="s">
-        <v>478</v>
-      </c>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="22" t="s">
-        <v>479</v>
-      </c>
-      <c r="I43" s="20" t="s">
-        <v>490</v>
-      </c>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="L43" s="20" t="s">
-        <v>480</v>
-      </c>
-      <c r="M43" s="22">
-        <v>1341</v>
-      </c>
-      <c r="N43" s="22"/>
-      <c r="O43" s="22"/>
-      <c r="P43" s="23"/>
-      <c r="Q43" s="23"/>
-      <c r="R43" s="23"/>
-      <c r="S43" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="T43" s="22">
-        <v>6200</v>
-      </c>
-      <c r="U43" s="42"/>
-      <c r="V43" s="42">
-        <v>46295</v>
-      </c>
-      <c r="W43" s="42"/>
-      <c r="X43" s="42"/>
-      <c r="Y43" s="20"/>
-      <c r="Z43" s="20"/>
-      <c r="AA43" s="20"/>
-      <c r="AB43" s="20"/>
-      <c r="AC43" s="20" t="s">
-        <v>481</v>
-      </c>
-      <c r="AD43" s="20" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="44" spans="1:30" ht="409.6">
-      <c r="A44" s="24" t="s">
+      <c r="F45" s="35" t="s">
+        <v>486</v>
+      </c>
+      <c r="G45" s="35"/>
+      <c r="H45" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="J45" s="35"/>
+      <c r="K45" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="B44" s="24" t="s">
-        <v>483</v>
-      </c>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24">
-        <v>43</v>
-      </c>
-      <c r="E44" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="I44" s="24" t="s">
-        <v>301</v>
-      </c>
-      <c r="J44" s="24"/>
-      <c r="K44" s="24" t="s">
-        <v>484</v>
-      </c>
-      <c r="L44" s="24" t="s">
-        <v>485</v>
-      </c>
-      <c r="M44" s="24">
-        <v>1200</v>
-      </c>
-      <c r="N44" s="24"/>
-      <c r="O44" s="24"/>
-      <c r="P44" s="24"/>
-      <c r="Q44" s="24"/>
-      <c r="R44" s="24"/>
-      <c r="S44" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="T44" s="24"/>
-      <c r="U44" s="43"/>
-      <c r="V44" s="42">
-        <v>46296</v>
-      </c>
-      <c r="W44" s="43"/>
-      <c r="X44" s="43"/>
-      <c r="Y44" s="24"/>
-      <c r="Z44" s="24"/>
-      <c r="AA44" s="24"/>
-      <c r="AB44" s="24"/>
-      <c r="AC44" s="24" t="s">
-        <v>486</v>
-      </c>
-      <c r="AD44" s="24" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="45" spans="1:30" ht="340">
-      <c r="A45" s="25" t="s">
-        <v>491</v>
-      </c>
-      <c r="B45" s="25" t="s">
-        <v>492</v>
-      </c>
-      <c r="C45" s="25"/>
-      <c r="D45" s="26">
-        <v>44</v>
-      </c>
-      <c r="E45" s="27" t="s">
-        <v>493</v>
-      </c>
-      <c r="F45" s="25" t="s">
-        <v>491</v>
-      </c>
-      <c r="G45" s="25"/>
-      <c r="H45" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="I45" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="J45" s="25"/>
-      <c r="K45" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="L45" s="25" t="s">
-        <v>494</v>
-      </c>
-      <c r="M45" s="27">
+      <c r="M45" s="37">
         <v>2437</v>
       </c>
-      <c r="N45" s="27"/>
-      <c r="O45" s="27"/>
-      <c r="P45" s="28"/>
-      <c r="Q45" s="28"/>
-      <c r="R45" s="28">
+      <c r="N45" s="37"/>
+      <c r="O45" s="37"/>
+      <c r="P45" s="38"/>
+      <c r="Q45" s="38"/>
+      <c r="R45" s="38">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>0</v>
       </c>
-      <c r="S45" s="25" t="s">
+      <c r="S45" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="T45" s="25"/>
-      <c r="U45" s="29"/>
-      <c r="V45" s="44"/>
-      <c r="W45" s="44"/>
-      <c r="X45" s="44"/>
-      <c r="Y45" s="25"/>
-      <c r="Z45" s="25"/>
-      <c r="AA45" s="25"/>
-      <c r="AB45" s="25"/>
-      <c r="AC45" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="AD45" s="25" t="s">
-        <v>495</v>
+      <c r="T45" s="35"/>
+      <c r="U45" s="39"/>
+      <c r="V45" s="39"/>
+      <c r="W45" s="39"/>
+      <c r="X45" s="39"/>
+      <c r="Y45" s="35"/>
+      <c r="Z45" s="35"/>
+      <c r="AA45" s="35"/>
+      <c r="AB45" s="35"/>
+      <c r="AC45" s="35" t="s">
+        <v>491</v>
+      </c>
+      <c r="AD45" s="35" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" ht="409.6">
+      <c r="A46" s="40" t="s">
+        <v>521</v>
+      </c>
+      <c r="B46" s="40" t="s">
+        <v>522</v>
+      </c>
+      <c r="C46" s="40"/>
+      <c r="D46" s="41">
+        <v>45</v>
+      </c>
+      <c r="E46" s="42" t="s">
+        <v>523</v>
+      </c>
+      <c r="F46" s="40" t="s">
+        <v>524</v>
+      </c>
+      <c r="G46" s="43"/>
+      <c r="H46" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="I46" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="J46" s="40"/>
+      <c r="K46" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="L46" s="40" t="s">
+        <v>525</v>
+      </c>
+      <c r="M46" s="42"/>
+      <c r="N46" s="42"/>
+      <c r="O46" s="42"/>
+      <c r="P46" s="44"/>
+      <c r="Q46" s="44"/>
+      <c r="R46" s="44">
+        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
+        <v>0</v>
+      </c>
+      <c r="S46" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="T46" s="41"/>
+      <c r="U46" s="45"/>
+      <c r="V46" s="45"/>
+      <c r="W46" s="45"/>
+      <c r="X46" s="45"/>
+      <c r="Y46" s="40"/>
+      <c r="Z46" s="40"/>
+      <c r="AA46" s="40"/>
+      <c r="AB46" s="40"/>
+      <c r="AC46" s="40" t="s">
+        <v>526</v>
+      </c>
+      <c r="AD46" s="40" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" ht="409.6">
+      <c r="A47" s="40" t="s">
+        <v>528</v>
+      </c>
+      <c r="B47" s="40" t="s">
+        <v>529</v>
+      </c>
+      <c r="C47" s="40"/>
+      <c r="D47" s="41">
+        <v>46</v>
+      </c>
+      <c r="E47" s="42" t="s">
+        <v>523</v>
+      </c>
+      <c r="F47" s="40" t="s">
+        <v>530</v>
+      </c>
+      <c r="G47" s="43"/>
+      <c r="H47" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="I47" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="J47" s="40"/>
+      <c r="K47" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="L47" s="40" t="s">
+        <v>531</v>
+      </c>
+      <c r="M47" s="42"/>
+      <c r="N47" s="42"/>
+      <c r="O47" s="42"/>
+      <c r="P47" s="44"/>
+      <c r="Q47" s="44"/>
+      <c r="R47" s="44">
+        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
+        <v>0</v>
+      </c>
+      <c r="S47" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="T47" s="41"/>
+      <c r="U47" s="45"/>
+      <c r="V47" s="45"/>
+      <c r="W47" s="45"/>
+      <c r="X47" s="45"/>
+      <c r="Y47" s="40"/>
+      <c r="Z47" s="40"/>
+      <c r="AA47" s="40"/>
+      <c r="AB47" s="40"/>
+      <c r="AC47" s="40" t="s">
+        <v>526</v>
+      </c>
+      <c r="AD47" s="40" t="s">
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -6629,12 +6850,13 @@
     <hyperlink ref="AB37" r:id="rId22" xr:uid="{95B4063F-E390-2F4C-97F4-22710E08828D}"/>
     <hyperlink ref="AB36" r:id="rId23" xr:uid="{58EFA9E3-F5DD-7244-B47A-5A35FCC395E1}"/>
     <hyperlink ref="AB24" r:id="rId24" xr:uid="{8FAD3DFA-392A-1846-AD7B-B2015845524B}"/>
+    <hyperlink ref="AB43" r:id="rId25" xr:uid="{90467AD9-CA04-EB46-8DEF-7CFABD5FF4FC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId25"/>
-  <legacyDrawing r:id="rId26"/>
+  <drawing r:id="rId26"/>
+  <legacyDrawing r:id="rId27"/>
   <tableParts count="1">
-    <tablePart r:id="rId27"/>
+    <tablePart r:id="rId28"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6654,22 +6876,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32">
       <c r="A1" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>453</v>
-      </c>
       <c r="D1" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16">
@@ -6677,19 +6899,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>170</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16">
@@ -6697,19 +6919,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16">
@@ -6717,19 +6939,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16">
@@ -6740,16 +6962,16 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16">
@@ -6760,16 +6982,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16">
@@ -6780,16 +7002,16 @@
         <v>169</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16">
@@ -6797,19 +7019,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>141</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16">
@@ -6820,16 +7042,16 @@
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16">
@@ -6840,16 +7062,16 @@
         <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16">
@@ -6857,19 +7079,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16">
@@ -6880,16 +7102,16 @@
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16">
@@ -6900,16 +7122,16 @@
         <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16">
@@ -6917,19 +7139,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16">
@@ -6937,19 +7159,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16">
@@ -6957,19 +7179,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16">
@@ -6977,19 +7199,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16">
@@ -6997,19 +7219,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32">
@@ -7017,19 +7239,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16">
@@ -7037,19 +7259,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>124</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16">
@@ -7057,19 +7279,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16">
@@ -7077,19 +7299,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16">
@@ -7100,16 +7322,16 @@
         <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>433</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16">
@@ -7120,16 +7342,16 @@
         <v>151</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16">
@@ -7140,16 +7362,16 @@
         <v>152</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>437</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="16">
@@ -7160,16 +7382,16 @@
         <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="32">
@@ -7177,19 +7399,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16">
@@ -7197,19 +7419,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16">
@@ -7220,16 +7442,16 @@
         <v>126</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16">
@@ -7237,19 +7459,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>145</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16">
@@ -7257,19 +7479,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -7284,13 +7506,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="64">
       <c r="A1" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16">
@@ -7301,7 +7523,7 @@
         <v>170</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="48">
@@ -7312,7 +7534,7 @@
         <v>157</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="112">
@@ -7323,7 +7545,7 @@
         <v>249</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16">
@@ -7367,7 +7589,7 @@
         <v>141</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16">
@@ -7400,7 +7622,7 @@
         <v>186</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16">
@@ -7433,7 +7655,7 @@
         <v>122</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="64">
@@ -7441,10 +7663,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="64">
@@ -7455,7 +7677,7 @@
         <v>123</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="96">
@@ -7463,10 +7685,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="96">
@@ -7474,10 +7696,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="96">
@@ -7485,10 +7707,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="48">
@@ -7499,7 +7721,7 @@
         <v>124</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="64">
@@ -7510,7 +7732,7 @@
         <v>219</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="80">
@@ -7518,10 +7740,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="32">
@@ -7576,7 +7798,7 @@
         <v>217</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="64">
@@ -7587,7 +7809,7 @@
         <v>218</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16">
@@ -7609,7 +7831,7 @@
         <v>145</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="32">
@@ -7617,10 +7839,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>

--- a/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
+++ b/data/RIGI_tracker_data_final_con_proyectos_integrados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucasordonez/Library/CloudStorage/GoogleDrive-lucassebaord29@gmail.com/Mi unidad/EXCEL RIGI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD8FFFC-1241-2344-9120-B6D3DBC0B481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3213AAFD-2D68-3145-859A-660F69FD6243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="68800" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Proyectos" sheetId="7" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="542">
   <si>
     <t>id_proyecto</t>
   </si>
@@ -269,9 +269,6 @@
     <t>Rio Tinto (Reino Unido)</t>
   </si>
   <si>
-    <t>Rincón Mining Pty Ltd.</t>
-  </si>
-  <si>
     <t>Litio</t>
   </si>
   <si>
@@ -455,9 +452,6 @@
     <t>Rechazado</t>
   </si>
   <si>
-    <t>Minera Agua Rica (MARA)</t>
-  </si>
-  <si>
     <t>Minera Agua Rica LLC Sucursal Argentina</t>
   </si>
   <si>
@@ -584,9 +578,6 @@
     <t>Descripción_del_proyecto</t>
   </si>
   <si>
-    <t>30-70708643-9</t>
-  </si>
-  <si>
     <t>Proyecto Rincón</t>
   </si>
   <si>
@@ -1715,28 +1706,34 @@
     <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349428/20261022; https://x.com/LuisCaputoAR/status/2105382049758523681; https://www.reuters.com/world/asia-pacific/toyota-invest-134-billion-argentina-production-plant-2026-09-30/; https://www.lanacion.com.ar/autos/toyota-invertira-us1341-millones-para-fabricar-un-nuevo-vehiculo-en-la-argentina-nid30092026/</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">PAE ya informaba en 2024 que el esquema de GNL requería infraestructura adicional: interconexión a gasoductos troncales, estación compresora, gasoducto terrestre hasta la costa, gasoducto submarino y sistema de amarre. También indicaba que PAE y Golar habían firmado en julio de 2024 un acuerdo por 20 años para instalar el buque </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Hilli Episeyo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> en Argentina.</t>
-    </r>
+    <t>RIGI - RINCON MINING PTY LIMITED</t>
+  </si>
+  <si>
+    <t>30-71899954-1</t>
+  </si>
+  <si>
+    <t>Res. 1854/2026</t>
+  </si>
+  <si>
+    <t>https://www.boletinoficial.gob.ar/detalleAviso/primera/349616/20261027</t>
+  </si>
+  <si>
+    <t>https://www.glencore.com/media-and-insights/news/glencore-submits-RIGI-applications-in-respect-of-its-argentine-copper-projects; https://x.com/LuisCaputoAR/status/1957458679835594969; https://www.reuters.com/latam/negocio/7X5ZW2SXG5IYNBUILMTT6GMS6U-2025-08-21/; https://www.boletinoficial.gob.ar/detalleAviso/primera/349616/20261027; https://www.cda.org.ar/detalle_normativa.php?id=9497; https://tn.com.ar/economia/2026/10/27/el-gobierno-aprobo-el-ingreso-al-rigi-de-un-proyecto-minero-de-us6393-millones-en-catamarca/?outputType=amp</t>
+  </si>
+  <si>
+    <t>30-70769036-0</t>
+  </si>
+  <si>
+    <t>Minera Agua Rica</t>
+  </si>
+  <si>
+    <t>Globaris; Glencore; Luis Caputo; Reuters; Res. 1854/2026; Boletín Oficial; TN</t>
+  </si>
+  <si>
+    <t>El proyecto Agua Rica cuenta con estudios de factibilidad desde al menos 1997, actualizados en 2006. En marzo de 2019, Yamana, Glencore y Goldcorp acordaron y anunciaron públicamente su desarrollo mediante la integración con la infraestructura de Alumbrera, formalizada en diciembre de 2020 como proyecto MARA. En 2023, Glencore adquirió la participación restante y alcanzó el control total del proyecto, antes de solicitar su adhesión al RIGI el 18/08/2025. Por lo tanto, se clasifica como proyecto preexistente, aunque no se encontró evidencia concluyente de una decisión final e irreversible de ejecutar la inversión aprobada antes del RIGI.</t>
+  </si>
+  <si>
+    <t>PAE ya informaba en 2024 que el esquema de GNL requería infraestructura adicional: interconexión a gasoductos troncales, estación compresora, gasoducto terrestre hasta la costa, gasoducto submarino y sistema de amarre. También indicaba que PAE y Golar habían firmado en julio de 2024 un acuerdo por 20 años para instalar el buque Hilli Episeyo en Argentina.</t>
   </si>
 </sst>
 </file>
@@ -1750,11 +1747,18 @@
     <numFmt numFmtId="167" formatCode="#,##0.000000"/>
     <numFmt numFmtId="168" formatCode="0.######"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1807,44 +1811,49 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF1F2937"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF172033"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF212529"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1877,8 +1886,13 @@
         <fgColor rgb="FFF7FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1927,87 +1941,164 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD7E0EA"/>
+        <color rgb="FFE8ECF2"/>
       </left>
       <right style="thin">
-        <color rgb="FFD7E0EA"/>
+        <color rgb="FFE8ECF2"/>
       </right>
       <top style="thin">
-        <color rgb="FFD7E0EA"/>
+        <color rgb="FFE8ECF2"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFE8ECF2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD8DEE9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE8ECF2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE8ECF2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE8ECF2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE8ECF2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD8DEE9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE8ECF2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE8ECF2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD8DEE9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE8ECF2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE8ECF2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD8DEE9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE8ECF2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE8ECF2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE8ECF2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD8DEE9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE8ECF2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD8DEE9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE8ECF2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD8DEE9"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2019,7 +2110,7 @@
     <xf numFmtId="14" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -2028,58 +2119,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2100,6 +2146,78 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2110,6 +2228,7 @@
   <dxfs count="33">
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2117,14 +2236,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2132,14 +2252,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2147,14 +2268,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2162,14 +2284,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2177,14 +2300,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2192,14 +2316,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2207,14 +2332,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2222,15 +2348,16 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="19" formatCode="d/m/yy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2238,15 +2365,16 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="19" formatCode="d/m/yy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2254,15 +2382,16 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="19" formatCode="d/m/yy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2270,15 +2399,16 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="19" formatCode="d/m/yy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2286,14 +2416,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2301,9 +2432,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2320,9 +2451,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0000"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2340,9 +2471,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0000"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2360,15 +2491,16 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="165" formatCode="0.0000"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2376,15 +2508,16 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2392,15 +2525,16 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2408,15 +2542,16 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2424,14 +2559,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2439,14 +2575,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2454,14 +2591,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2469,14 +2607,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2484,15 +2623,16 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2500,14 +2640,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2515,14 +2656,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2530,15 +2672,16 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2546,15 +2689,16 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2562,14 +2706,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2577,14 +2722,15 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2592,9 +2738,9 @@
         <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -3126,13 +3272,13 @@
   <sheetData>
     <row r="1" spans="1:30" ht="34">
       <c r="A1" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>0</v>
@@ -3141,10 +3287,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>2</v>
@@ -3153,7 +3299,7 @@
         <v>3</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>4</v>
@@ -3162,69 +3308,69 @@
         <v>5</v>
       </c>
       <c r="M1" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="P1" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="R1" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>372</v>
-      </c>
       <c r="U1" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="V1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="X1" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Y1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="Z1" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="AD1" s="6" t="s">
         <v>373</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="AC1" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="AD1" s="6" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="102">
       <c r="A2" s="8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D2" s="9">
         <v>1</v>
@@ -3236,22 +3382,22 @@
         <v>9</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>171</v>
-      </c>
       <c r="L2" s="8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M2" s="10">
         <v>550</v>
@@ -3294,16 +3440,16 @@
         <v>12</v>
       </c>
       <c r="Z2" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA2" s="8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AB2" s="15" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AC2" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AD2" s="16"/>
     </row>
@@ -3312,10 +3458,10 @@
         <v>15</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D3" s="17">
         <v>2</v>
@@ -3327,19 +3473,19 @@
         <v>17</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H3" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J3" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L3" s="16" t="s">
         <v>20</v>
@@ -3385,28 +3531,28 @@
         <v>21</v>
       </c>
       <c r="Z3" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA3" s="16" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AB3" s="19" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AC3" s="16" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AD3" s="16"/>
     </row>
     <row r="4" spans="1:30" ht="102">
       <c r="A4" s="16" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D4" s="9">
         <v>3</v>
@@ -3418,16 +3564,16 @@
         <v>23</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H4" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K4" s="16" t="s">
         <v>24</v>
@@ -3476,16 +3622,16 @@
         <v>26</v>
       </c>
       <c r="Z4" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA4" s="16" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AB4" s="19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AC4" s="16" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AD4" s="16"/>
     </row>
@@ -3494,10 +3640,10 @@
         <v>27</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D5" s="17">
         <v>4</v>
@@ -3509,7 +3655,7 @@
         <v>29</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H5" s="18" t="s">
         <v>10</v>
@@ -3567,16 +3713,16 @@
         <v>33</v>
       </c>
       <c r="Z5" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA5" s="16" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AB5" s="19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC5" s="16" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AD5" s="16"/>
     </row>
@@ -3585,28 +3731,28 @@
         <v>34</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D6" s="9">
         <v>5</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>35</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>10</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8" t="s">
@@ -3657,16 +3803,16 @@
         <v>37</v>
       </c>
       <c r="Z6" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA6" s="8" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AB6" s="15" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AC6" s="8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AD6" s="16"/>
     </row>
@@ -3675,10 +3821,10 @@
         <v>38</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D7" s="17">
         <v>6</v>
@@ -3687,19 +3833,19 @@
         <v>39</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>40</v>
@@ -3748,28 +3894,28 @@
         <v>41</v>
       </c>
       <c r="Z7" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA7" s="8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AB7" s="20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AC7" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AD7" s="16"/>
     </row>
-    <row r="8" spans="1:30" ht="136">
+    <row r="8" spans="1:30" ht="153">
       <c r="A8" s="16" t="s">
         <v>42</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D8" s="9">
         <v>7</v>
@@ -3781,7 +3927,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H8" s="18" t="s">
         <v>45</v>
@@ -3790,7 +3936,7 @@
         <v>45</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>31</v>
@@ -3839,28 +3985,28 @@
         <v>46</v>
       </c>
       <c r="Z8" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA8" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AB8" s="21" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AC8" s="16" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AD8" s="16"/>
     </row>
-    <row r="9" spans="1:30" ht="102">
+    <row r="9" spans="1:30" ht="119">
       <c r="A9" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D9" s="17">
         <v>8</v>
@@ -3872,7 +4018,7 @@
         <v>49</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>18</v>
@@ -3881,7 +4027,7 @@
         <v>50</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>36</v>
@@ -3930,28 +4076,28 @@
         <v>51</v>
       </c>
       <c r="Z9" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA9" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB9" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="AC9" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="AD9" s="16"/>
+    </row>
+    <row r="10" spans="1:30" ht="136">
+      <c r="A10" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="AA9" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="AB9" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="AC9" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="AD9" s="16"/>
-    </row>
-    <row r="10" spans="1:30" ht="119">
-      <c r="A10" s="16" t="s">
-        <v>159</v>
-      </c>
       <c r="B10" s="16" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D10" s="9">
         <v>9</v>
@@ -3959,20 +4105,20 @@
       <c r="E10" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>158</v>
+      <c r="F10" s="45" t="s">
+        <v>532</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>533</v>
       </c>
       <c r="H10" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>19</v>
@@ -4018,31 +4164,31 @@
         <v>45807</v>
       </c>
       <c r="Y10" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Z10" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA10" s="16" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AB10" s="19" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AC10" s="16" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AD10" s="16"/>
     </row>
     <row r="11" spans="1:30" ht="255">
       <c r="A11" s="8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D11" s="17">
         <v>10</v>
@@ -4051,22 +4197,22 @@
         <v>52</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L11" s="8" t="s">
         <v>20</v>
@@ -4109,55 +4255,55 @@
         <v>46112</v>
       </c>
       <c r="Y11" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z11" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA11" s="8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AB11" s="15" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AC11" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AD11" s="16"/>
     </row>
-    <row r="12" spans="1:30" ht="119">
+    <row r="12" spans="1:30" ht="136">
       <c r="A12" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D12" s="9">
         <v>11</v>
       </c>
       <c r="E12" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="G12" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H12" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" s="10" t="s">
+      <c r="I12" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="J12" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="K12" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>32</v>
@@ -4200,52 +4346,52 @@
         <v>45980</v>
       </c>
       <c r="Y12" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Z12" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA12" s="8" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AB12" s="15" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AC12" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AD12" s="16"/>
     </row>
     <row r="13" spans="1:30" ht="372">
       <c r="A13" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D13" s="17">
         <v>12</v>
       </c>
       <c r="E13" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="16" t="s">
-        <v>65</v>
-      </c>
       <c r="G13" s="16" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>40</v>
@@ -4291,52 +4437,52 @@
         <v>45736</v>
       </c>
       <c r="Y13" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z13" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA13" s="16" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AB13" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AC13" s="16" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AD13" s="16"/>
     </row>
-    <row r="14" spans="1:30" ht="136">
+    <row r="14" spans="1:30" ht="153">
       <c r="A14" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>180</v>
-      </c>
       <c r="C14" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D14" s="9">
         <v>13</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>24</v>
@@ -4382,45 +4528,45 @@
         <v>46111</v>
       </c>
       <c r="Y14" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Z14" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA14" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AB14" s="15" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AC14" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AD14" s="16"/>
     </row>
     <row r="15" spans="1:30" ht="409.6">
       <c r="A15" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="17">
         <v>14</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J15" s="16"/>
       <c r="K15" s="16" t="s">
@@ -4436,12 +4582,9 @@
       <c r="O15" s="18"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
-      <c r="R15" s="11">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R15" s="11"/>
       <c r="S15" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T15" s="16"/>
       <c r="U15" s="13"/>
@@ -4455,35 +4598,35 @@
       <c r="AA15" s="16"/>
       <c r="AB15" s="16"/>
       <c r="AC15" s="16" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AD15" s="16" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="409.6">
       <c r="A16" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="9">
         <v>15</v>
       </c>
       <c r="E16" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>79</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8" t="s">
@@ -4499,12 +4642,9 @@
       <c r="O16" s="10"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
-      <c r="R16" s="12">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R16" s="12"/>
       <c r="S16" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T16" s="8"/>
       <c r="U16" s="13"/>
@@ -4518,48 +4658,48 @@
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
       <c r="AC16" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AD16" s="16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="409.6">
       <c r="A17" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D17" s="22">
         <v>16</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F17" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="J17" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="L17" s="22" t="s">
         <v>504</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>505</v>
-      </c>
-      <c r="H17" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="I17" s="22" t="s">
-        <v>300</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>506</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="L17" s="22" t="s">
-        <v>507</v>
       </c>
       <c r="M17" s="23">
         <v>12240</v>
@@ -4597,57 +4737,57 @@
         <v>46314</v>
       </c>
       <c r="Y17" s="22" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="Z17" s="22" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA17" s="22" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="AB17" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="AC17" s="22" t="s">
         <v>509</v>
       </c>
-      <c r="AC17" s="22" t="s">
-        <v>512</v>
-      </c>
       <c r="AD17" s="22" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="119">
       <c r="A18" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D18" s="9">
         <v>17</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>20</v>
@@ -4690,49 +4830,49 @@
         <v>46177</v>
       </c>
       <c r="Y18" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Z18" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA18" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AB18" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AC18" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AD18" s="16"/>
     </row>
     <row r="19" spans="1:30" ht="409.6">
       <c r="A19" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="17">
         <v>18</v>
       </c>
       <c r="E19" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" s="16" t="s">
         <v>86</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>87</v>
       </c>
       <c r="G19" s="16"/>
       <c r="H19" s="18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J19" s="16"/>
       <c r="K19" s="16" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="L19" s="16" t="s">
         <v>11</v>
@@ -4744,12 +4884,9 @@
       <c r="O19" s="18"/>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
-      <c r="R19" s="11">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R19" s="11"/>
       <c r="S19" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T19" s="16"/>
       <c r="U19" s="13"/>
@@ -4763,28 +4900,28 @@
       <c r="AA19" s="16"/>
       <c r="AB19" s="16"/>
       <c r="AC19" s="16" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AD19" s="16" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="409.6">
       <c r="A20" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="9">
         <v>19</v>
       </c>
       <c r="E20" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>90</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="10" t="s">
@@ -4807,12 +4944,9 @@
       <c r="O20" s="10"/>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
-      <c r="R20" s="12">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R20" s="12"/>
       <c r="S20" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T20" s="8"/>
       <c r="U20" s="13"/>
@@ -4826,56 +4960,53 @@
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
       <c r="AC20" s="8" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AD20" s="16" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="409.6">
       <c r="A21" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="17">
         <v>20</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J21" s="16"/>
       <c r="K21" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L21" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M21" s="18">
-        <v>13800</v>
+      <c r="M21" s="10">
+        <v>9500</v>
       </c>
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
       <c r="P21" s="11"/>
       <c r="Q21" s="11"/>
-      <c r="R21" s="11">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R21" s="11"/>
       <c r="S21" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T21" s="16"/>
       <c r="U21" s="13"/>
@@ -4889,42 +5020,42 @@
       <c r="AA21" s="16"/>
       <c r="AB21" s="16"/>
       <c r="AC21" s="16" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AD21" s="16" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="409.6">
       <c r="A22" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="9">
         <v>21</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="M22" s="10">
         <v>200</v>
@@ -4933,12 +5064,9 @@
       <c r="O22" s="10"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="11"/>
-      <c r="R22" s="12">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R22" s="12"/>
       <c r="S22" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T22" s="8"/>
       <c r="U22" s="13"/>
@@ -4952,28 +5080,28 @@
       <c r="AA22" s="8"/>
       <c r="AB22" s="8"/>
       <c r="AC22" s="8" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AD22" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="409.6">
       <c r="A23" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="17">
         <v>22</v>
       </c>
       <c r="E23" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="16" t="s">
         <v>96</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>97</v>
       </c>
       <c r="G23" s="16"/>
       <c r="H23" s="18" t="s">
@@ -4996,12 +5124,9 @@
       <c r="O23" s="18"/>
       <c r="P23" s="11"/>
       <c r="Q23" s="11"/>
-      <c r="R23" s="11">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R23" s="11"/>
       <c r="S23" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T23" s="16"/>
       <c r="U23" s="13"/>
@@ -5015,48 +5140,48 @@
       <c r="AA23" s="16"/>
       <c r="AB23" s="16"/>
       <c r="AC23" s="16" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AD23" s="16" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" ht="221">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="238">
       <c r="A24" s="16" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D24" s="17">
         <v>23</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F24" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>491</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="L24" s="16" t="s">
         <v>493</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>494</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="I24" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="J24" s="16" t="s">
-        <v>495</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>496</v>
       </c>
       <c r="M24" s="18">
         <v>6432</v>
@@ -5094,47 +5219,47 @@
         <v>46304</v>
       </c>
       <c r="Y24" s="16" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="Z24" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA24" s="16" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="AB24" s="26" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AC24" s="16" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AD24" s="16" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="409.6">
       <c r="A25" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="17">
         <v>24</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G25" s="16"/>
       <c r="H25" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J25" s="16"/>
       <c r="K25" s="16" t="s">
@@ -5150,12 +5275,9 @@
       <c r="O25" s="18"/>
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
-      <c r="R25" s="11">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R25" s="11"/>
       <c r="S25" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T25" s="16"/>
       <c r="U25" s="13"/>
@@ -5169,45 +5291,45 @@
       <c r="AA25" s="16"/>
       <c r="AB25" s="16"/>
       <c r="AC25" s="16" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AD25" s="16" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" ht="289">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" ht="306">
       <c r="A26" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D26" s="9">
         <v>25</v>
       </c>
       <c r="E26" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="F26" s="8" t="s">
-        <v>102</v>
-      </c>
       <c r="G26" s="8" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L26" s="8" t="s">
         <v>11</v>
@@ -5250,55 +5372,55 @@
         <v>46224</v>
       </c>
       <c r="Y26" s="8" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Z26" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA26" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AB26" s="15" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AC26" s="8" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AD26" s="16"/>
     </row>
     <row r="27" spans="1:30" ht="255">
       <c r="A27" s="16" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D27" s="17">
         <v>26</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H27" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J27" s="16" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L27" s="16" t="s">
         <v>20</v>
@@ -5341,28 +5463,28 @@
         <v>46234</v>
       </c>
       <c r="Y27" s="16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Z27" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA27" s="16" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AB27" s="27" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AC27" s="16" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AD27" s="16"/>
     </row>
     <row r="28" spans="1:30" ht="409.6">
       <c r="A28" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="9">
@@ -5372,18 +5494,18 @@
         <v>52</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J28" s="8"/>
       <c r="K28" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>20</v>
@@ -5395,12 +5517,9 @@
       <c r="O28" s="10"/>
       <c r="P28" s="11"/>
       <c r="Q28" s="11"/>
-      <c r="R28" s="12">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R28" s="12"/>
       <c r="S28" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T28" s="8"/>
       <c r="U28" s="13"/>
@@ -5414,43 +5533,43 @@
       <c r="AA28" s="8"/>
       <c r="AB28" s="8"/>
       <c r="AC28" s="8" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AD28" s="16" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="289">
       <c r="A29" s="16" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="17">
         <v>28</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H29" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J29" s="16" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L29" s="16" t="s">
         <v>20</v>
@@ -5493,52 +5612,52 @@
         <v>46232</v>
       </c>
       <c r="Y29" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z29" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA29" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="Z29" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA29" s="16" t="s">
-        <v>255</v>
-      </c>
       <c r="AB29" s="19" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AC29" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AD29" s="16"/>
     </row>
-    <row r="30" spans="1:30" ht="289">
+    <row r="30" spans="1:30" ht="306">
       <c r="A30" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D30" s="9">
         <v>29</v>
       </c>
       <c r="E30" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F30" s="8" t="s">
-        <v>109</v>
-      </c>
       <c r="G30" s="8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>24</v>
@@ -5585,49 +5704,49 @@
         <v>46233</v>
       </c>
       <c r="Y30" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="Z30" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA30" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="Z30" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA30" s="8" t="s">
-        <v>275</v>
-      </c>
       <c r="AB30" s="15" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AC30" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AD30" s="16"/>
     </row>
-    <row r="31" spans="1:30" ht="388">
+    <row r="31" spans="1:30" ht="409.6">
       <c r="A31" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="17">
         <v>30</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="F31" s="28" t="s">
-        <v>347</v>
+        <v>326</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>344</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J31" s="8"/>
       <c r="K31" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>11</v>
@@ -5639,12 +5758,9 @@
       <c r="O31" s="10"/>
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
-      <c r="R31" s="12">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R31" s="12"/>
       <c r="S31" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T31" s="8"/>
       <c r="U31" s="13"/>
@@ -5658,33 +5774,33 @@
       <c r="AA31" s="8"/>
       <c r="AB31" s="8"/>
       <c r="AC31" s="8" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AD31" s="16" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="119">
       <c r="A32" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D32" s="9">
         <v>31</v>
       </c>
       <c r="E32" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F32" s="8" t="s">
-        <v>74</v>
-      </c>
       <c r="G32" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>18</v>
@@ -5693,7 +5809,7 @@
         <v>50</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K32" s="8" t="s">
         <v>24</v>
@@ -5739,25 +5855,25 @@
         <v>45943</v>
       </c>
       <c r="Y32" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Z32" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AA32" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AB32" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AC32" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AD32" s="16"/>
     </row>
     <row r="33" spans="1:30" ht="34">
       <c r="A33" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -5765,17 +5881,17 @@
         <v>32</v>
       </c>
       <c r="E33" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="F33" s="16" t="s">
         <v>112</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>113</v>
       </c>
       <c r="G33" s="16"/>
       <c r="H33" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J33" s="16"/>
       <c r="K33" s="16" t="s">
@@ -5791,12 +5907,9 @@
       <c r="O33" s="18"/>
       <c r="P33" s="11"/>
       <c r="Q33" s="11"/>
-      <c r="R33" s="11">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R33" s="11"/>
       <c r="S33" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="T33" s="16"/>
       <c r="U33" s="13"/>
@@ -5810,51 +5923,51 @@
       <c r="AA33" s="16"/>
       <c r="AB33" s="16"/>
       <c r="AC33" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="AD33" s="16"/>
     </row>
     <row r="34" spans="1:30" ht="136">
       <c r="A34" s="16" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D34" s="17">
         <v>33</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F34" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="J34" s="16" t="s">
         <v>457</v>
       </c>
-      <c r="G34" s="16" t="s">
-        <v>458</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="I34" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="J34" s="16" t="s">
-        <v>460</v>
-      </c>
       <c r="K34" s="16" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="M34" s="29">
+        <v>312</v>
+      </c>
+      <c r="M34" s="28">
         <v>365.39866899999998</v>
       </c>
-      <c r="N34" s="29">
+      <c r="N34" s="28">
         <v>365.39866899999998</v>
       </c>
       <c r="O34" s="18">
@@ -5889,121 +6002,151 @@
         <v>46260</v>
       </c>
       <c r="Y34" s="16" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="Z34" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA34" s="16" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AB34" s="16" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AC34" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="AD34" s="16"/>
+    </row>
+    <row r="35" spans="1:30" ht="409.6">
+      <c r="A35" s="46" t="s">
+        <v>538</v>
+      </c>
+      <c r="B35" s="45" t="s">
+        <v>330</v>
+      </c>
+      <c r="C35" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="47">
+        <v>34</v>
+      </c>
+      <c r="E35" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="G35" s="60" t="s">
+        <v>537</v>
+      </c>
+      <c r="H35" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="J35" s="45" t="s">
+        <v>151</v>
+      </c>
+      <c r="K35" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="L35" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="M35" s="48">
+        <v>6394</v>
+      </c>
+      <c r="N35" s="48">
+        <v>6393.6319949999997</v>
+      </c>
+      <c r="O35" s="48">
+        <v>3310.574165</v>
+      </c>
+      <c r="P35" s="48">
+        <v>111.63955213</v>
+      </c>
+      <c r="Q35" s="48">
+        <v>659.89445980000005</v>
+      </c>
+      <c r="R35" s="48">
+        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
+        <v>771.53401193000002</v>
+      </c>
+      <c r="S35" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="T35" s="49">
+        <v>8200</v>
+      </c>
+      <c r="U35" s="50">
+        <v>47118</v>
+      </c>
+      <c r="V35" s="50">
+        <v>45887</v>
+      </c>
+      <c r="W35" s="50">
+        <v>46295</v>
+      </c>
+      <c r="X35" s="50">
+        <v>46322</v>
+      </c>
+      <c r="Y35" s="45" t="s">
+        <v>534</v>
+      </c>
+      <c r="Z35" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA35" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="AB35" s="51" t="s">
+        <v>535</v>
+      </c>
+      <c r="AC35" s="45" t="s">
+        <v>539</v>
+      </c>
+      <c r="AD35" s="52" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" ht="404">
+      <c r="A36" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="AD34" s="16"/>
-    </row>
-    <row r="35" spans="1:30" ht="409.6">
-      <c r="A35" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>333</v>
-      </c>
-      <c r="C35" s="16"/>
-      <c r="D35" s="17">
-        <v>34</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="G35" s="16"/>
-      <c r="H35" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="L35" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="M35" s="18">
-        <v>4000</v>
-      </c>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="11">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
-      <c r="S35" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="T35" s="16"/>
-      <c r="U35" s="13"/>
-      <c r="V35" s="13">
-        <v>45887</v>
-      </c>
-      <c r="W35" s="13"/>
-      <c r="X35" s="13"/>
-      <c r="Y35" s="16"/>
-      <c r="Z35" s="16"/>
-      <c r="AA35" s="16"/>
-      <c r="AB35" s="16"/>
-      <c r="AC35" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="AD35" s="16" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="36" spans="1:30" ht="372">
-      <c r="A36" s="8" t="s">
-        <v>468</v>
-      </c>
       <c r="B36" s="16" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D36" s="9">
         <v>35</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="J36" s="16" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K36" s="8" t="s">
         <v>31</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M36" s="10">
         <v>2693</v>
@@ -6043,55 +6186,55 @@
         <v>46272</v>
       </c>
       <c r="Y36" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="Z36" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA36" s="16" t="s">
+        <v>472</v>
+      </c>
+      <c r="AB36" s="29" t="s">
         <v>470</v>
       </c>
-      <c r="Z36" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA36" s="16" t="s">
-        <v>475</v>
-      </c>
-      <c r="AB36" s="30" t="s">
-        <v>473</v>
-      </c>
       <c r="AC36" s="8" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AD36" s="16"/>
     </row>
     <row r="37" spans="1:30" ht="204">
       <c r="A37" s="16" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D37" s="17">
         <v>36</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J37" s="16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L37" s="16" t="s">
         <v>11</v>
@@ -6134,55 +6277,55 @@
         <v>46198</v>
       </c>
       <c r="Y37" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Z37" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AA37" s="16" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="AB37" s="27" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AC37" s="16" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AD37" s="16"/>
     </row>
     <row r="38" spans="1:30" ht="102">
       <c r="A38" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D38" s="9">
         <v>37</v>
       </c>
       <c r="E38" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="16" t="s">
-        <v>71</v>
-      </c>
       <c r="G38" s="16" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H38" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J38" s="16" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L38" s="16" t="s">
         <v>20</v>
@@ -6225,49 +6368,49 @@
         <v>45896</v>
       </c>
       <c r="Y38" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Z38" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA38" s="16" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AB38" s="27" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AC38" s="16" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AD38" s="16"/>
     </row>
     <row r="39" spans="1:30" ht="409.6">
       <c r="A39" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="17">
         <v>38</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G39" s="8"/>
       <c r="H39" s="10" t="s">
         <v>18</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L39" s="8" t="s">
         <v>20</v>
@@ -6279,12 +6422,9 @@
       <c r="O39" s="10"/>
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
-      <c r="R39" s="12">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R39" s="12"/>
       <c r="S39" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T39" s="8"/>
       <c r="U39" s="13"/>
@@ -6298,39 +6438,39 @@
       <c r="AA39" s="8"/>
       <c r="AB39" s="8"/>
       <c r="AC39" s="8" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AD39" s="16" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="409.6">
       <c r="A40" s="16" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="9">
         <v>39</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G40" s="16"/>
       <c r="H40" s="18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J40" s="16"/>
       <c r="K40" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L40" s="16" t="s">
         <v>11</v>
@@ -6342,12 +6482,9 @@
       <c r="O40" s="18"/>
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
-      <c r="R40" s="11">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R40" s="11"/>
       <c r="S40" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T40" s="16"/>
       <c r="U40" s="13"/>
@@ -6361,39 +6498,39 @@
       <c r="AA40" s="16"/>
       <c r="AB40" s="16"/>
       <c r="AC40" s="16" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AD40" s="16" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="409.6">
       <c r="A41" s="16" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="17">
         <v>40</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G41" s="16"/>
       <c r="H41" s="18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J41" s="16"/>
       <c r="K41" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L41" s="16" t="s">
         <v>11</v>
@@ -6405,14 +6542,11 @@
       <c r="O41" s="18"/>
       <c r="P41" s="11"/>
       <c r="Q41" s="11"/>
-      <c r="R41" s="11">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R41" s="11"/>
       <c r="S41" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="T41" s="31"/>
+        <v>119</v>
+      </c>
+      <c r="T41" s="30"/>
       <c r="U41" s="13"/>
       <c r="V41" s="13">
         <v>46224</v>
@@ -6424,39 +6558,39 @@
       <c r="AA41" s="16"/>
       <c r="AB41" s="16"/>
       <c r="AC41" s="16" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AD41" s="19" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="409.6">
       <c r="A42" s="16" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="17">
         <v>41</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G42" s="16"/>
       <c r="H42" s="18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J42" s="16"/>
       <c r="K42" s="16" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="L42" s="16" t="s">
         <v>11</v>
@@ -6468,12 +6602,9 @@
       <c r="O42" s="18"/>
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
-      <c r="R42" s="11">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
+      <c r="R42" s="11"/>
       <c r="S42" s="16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="T42" s="18"/>
       <c r="U42" s="13"/>
@@ -6487,344 +6618,335 @@
       <c r="AA42" s="16"/>
       <c r="AB42" s="16"/>
       <c r="AC42" s="16" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AD42" s="16" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="43" spans="1:30" ht="409.6">
-      <c r="A43" s="46" t="s">
-        <v>484</v>
-      </c>
-      <c r="B43" s="46" t="s">
+      <c r="A43" s="31" t="s">
+        <v>481</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>511</v>
+      </c>
+      <c r="C43" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="D43" s="32">
+        <v>42</v>
+      </c>
+      <c r="E43" s="31" t="s">
+        <v>473</v>
+      </c>
+      <c r="F43" s="31" t="s">
+        <v>512</v>
+      </c>
+      <c r="G43" s="33" t="s">
+        <v>513</v>
+      </c>
+      <c r="H43" s="31" t="s">
+        <v>474</v>
+      </c>
+      <c r="I43" s="31" t="s">
         <v>514</v>
       </c>
-      <c r="C43" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="D43" s="47">
-        <v>42</v>
-      </c>
-      <c r="E43" s="46" t="s">
-        <v>476</v>
-      </c>
-      <c r="F43" s="46" t="s">
+      <c r="J43" s="31" t="s">
         <v>515</v>
       </c>
-      <c r="G43" s="48" t="s">
-        <v>516</v>
-      </c>
-      <c r="H43" s="46" t="s">
-        <v>477</v>
-      </c>
-      <c r="I43" s="46" t="s">
-        <v>517</v>
-      </c>
-      <c r="J43" s="46" t="s">
-        <v>518</v>
-      </c>
-      <c r="K43" s="46" t="s">
+      <c r="K43" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="L43" s="46" t="s">
-        <v>478</v>
-      </c>
-      <c r="M43" s="49">
+      <c r="L43" s="31" t="s">
+        <v>475</v>
+      </c>
+      <c r="M43" s="34">
         <v>1341</v>
       </c>
-      <c r="N43" s="49">
+      <c r="N43" s="34">
         <v>1252.9261080000001</v>
       </c>
-      <c r="O43" s="49">
+      <c r="O43" s="34">
         <v>1252.9261080000001</v>
       </c>
-      <c r="P43" s="49">
+      <c r="P43" s="34">
         <v>19.5</v>
       </c>
-      <c r="Q43" s="49">
+      <c r="Q43" s="34">
         <v>147.75303099999999</v>
       </c>
-      <c r="R43" s="49">
+      <c r="R43" s="34">
         <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
         <v>167.25303099999999</v>
       </c>
-      <c r="S43" s="46" t="s">
+      <c r="S43" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="T43" s="47">
+      <c r="T43" s="32">
         <v>6225</v>
       </c>
-      <c r="U43" s="50">
+      <c r="U43" s="35">
         <v>47026</v>
       </c>
-      <c r="V43" s="50">
+      <c r="V43" s="35">
         <v>46181</v>
       </c>
-      <c r="W43" s="50">
+      <c r="W43" s="35">
         <v>46294</v>
       </c>
-      <c r="X43" s="50">
+      <c r="X43" s="35">
         <v>46317</v>
       </c>
-      <c r="Y43" s="46" t="s">
+      <c r="Y43" s="31" t="s">
+        <v>516</v>
+      </c>
+      <c r="Z43" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA43" s="31" t="s">
+        <v>517</v>
+      </c>
+      <c r="AB43" s="36" t="s">
+        <v>529</v>
+      </c>
+      <c r="AC43" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="AD43" s="31" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" ht="409.6">
+      <c r="A44" s="37" t="s">
+        <v>482</v>
+      </c>
+      <c r="B44" s="37" t="s">
+        <v>476</v>
+      </c>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37">
+        <v>43</v>
+      </c>
+      <c r="E44" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="I44" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="J44" s="37"/>
+      <c r="K44" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="L44" s="37" t="s">
+        <v>478</v>
+      </c>
+      <c r="M44" s="37">
+        <v>1200</v>
+      </c>
+      <c r="N44" s="37"/>
+      <c r="O44" s="37"/>
+      <c r="P44" s="37"/>
+      <c r="Q44" s="37"/>
+      <c r="R44" s="37"/>
+      <c r="S44" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="T44" s="37"/>
+      <c r="U44" s="38"/>
+      <c r="V44" s="39">
+        <v>46296</v>
+      </c>
+      <c r="W44" s="38"/>
+      <c r="X44" s="38"/>
+      <c r="Y44" s="37"/>
+      <c r="Z44" s="37"/>
+      <c r="AA44" s="37"/>
+      <c r="AB44" s="37"/>
+      <c r="AC44" s="37" t="s">
+        <v>479</v>
+      </c>
+      <c r="AD44" s="37" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" ht="340">
+      <c r="A45" s="40" t="s">
+        <v>483</v>
+      </c>
+      <c r="B45" s="40" t="s">
+        <v>484</v>
+      </c>
+      <c r="C45" s="40"/>
+      <c r="D45" s="41">
+        <v>44</v>
+      </c>
+      <c r="E45" s="42" t="s">
+        <v>485</v>
+      </c>
+      <c r="F45" s="40" t="s">
+        <v>483</v>
+      </c>
+      <c r="G45" s="40"/>
+      <c r="H45" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="J45" s="40"/>
+      <c r="K45" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="40" t="s">
+        <v>486</v>
+      </c>
+      <c r="M45" s="42">
+        <v>2437</v>
+      </c>
+      <c r="N45" s="42"/>
+      <c r="O45" s="42"/>
+      <c r="P45" s="43"/>
+      <c r="Q45" s="43"/>
+      <c r="R45" s="43"/>
+      <c r="S45" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="T45" s="40"/>
+      <c r="U45" s="44"/>
+      <c r="V45" s="44"/>
+      <c r="W45" s="44"/>
+      <c r="X45" s="44"/>
+      <c r="Y45" s="40"/>
+      <c r="Z45" s="40"/>
+      <c r="AA45" s="40"/>
+      <c r="AB45" s="40"/>
+      <c r="AC45" s="40" t="s">
+        <v>488</v>
+      </c>
+      <c r="AD45" s="40" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" ht="409.6">
+      <c r="A46" s="46" t="s">
+        <v>518</v>
+      </c>
+      <c r="B46" s="45" t="s">
         <v>519</v>
       </c>
-      <c r="Z43" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA43" s="46" t="s">
+      <c r="C46" s="45"/>
+      <c r="D46" s="47">
+        <v>45</v>
+      </c>
+      <c r="E46" s="45" t="s">
         <v>520</v>
       </c>
-      <c r="AB43" s="51" t="s">
-        <v>532</v>
-      </c>
-      <c r="AC43" s="16" t="s">
-        <v>533</v>
-      </c>
-      <c r="AD43" s="46" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="44" spans="1:30" ht="409.6">
-      <c r="A44" s="32" t="s">
-        <v>485</v>
-      </c>
-      <c r="B44" s="32" t="s">
-        <v>479</v>
-      </c>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32">
-        <v>43</v>
-      </c>
-      <c r="E44" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="I44" s="32" t="s">
-        <v>300</v>
-      </c>
-      <c r="J44" s="32"/>
-      <c r="K44" s="32" t="s">
-        <v>480</v>
-      </c>
-      <c r="L44" s="32" t="s">
-        <v>481</v>
-      </c>
-      <c r="M44" s="32">
-        <v>1200</v>
-      </c>
-      <c r="N44" s="32"/>
-      <c r="O44" s="32"/>
-      <c r="P44" s="32"/>
-      <c r="Q44" s="32"/>
-      <c r="R44" s="32"/>
-      <c r="S44" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="T44" s="32"/>
-      <c r="U44" s="33"/>
-      <c r="V44" s="34">
-        <v>46296</v>
-      </c>
-      <c r="W44" s="33"/>
-      <c r="X44" s="33"/>
-      <c r="Y44" s="32"/>
-      <c r="Z44" s="32"/>
-      <c r="AA44" s="32"/>
-      <c r="AB44" s="32"/>
-      <c r="AC44" s="32" t="s">
-        <v>482</v>
-      </c>
-      <c r="AD44" s="32" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="45" spans="1:30" ht="272">
-      <c r="A45" s="35" t="s">
-        <v>486</v>
-      </c>
-      <c r="B45" s="35" t="s">
-        <v>487</v>
-      </c>
-      <c r="C45" s="35"/>
-      <c r="D45" s="36">
-        <v>44</v>
-      </c>
-      <c r="E45" s="37" t="s">
-        <v>488</v>
-      </c>
-      <c r="F45" s="35" t="s">
-        <v>486</v>
-      </c>
-      <c r="G45" s="35"/>
-      <c r="H45" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="I45" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="J45" s="35"/>
-      <c r="K45" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="L45" s="35" t="s">
-        <v>489</v>
-      </c>
-      <c r="M45" s="37">
-        <v>2437</v>
-      </c>
-      <c r="N45" s="37"/>
-      <c r="O45" s="37"/>
-      <c r="P45" s="38"/>
-      <c r="Q45" s="38"/>
-      <c r="R45" s="38">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
-      <c r="S45" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="T45" s="35"/>
-      <c r="U45" s="39"/>
-      <c r="V45" s="39"/>
-      <c r="W45" s="39"/>
-      <c r="X45" s="39"/>
-      <c r="Y45" s="35"/>
-      <c r="Z45" s="35"/>
-      <c r="AA45" s="35"/>
-      <c r="AB45" s="35"/>
-      <c r="AC45" s="35" t="s">
-        <v>491</v>
-      </c>
-      <c r="AD45" s="35" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="46" spans="1:30" ht="409.6">
-      <c r="A46" s="40" t="s">
+      <c r="F46" s="45" t="s">
         <v>521</v>
       </c>
-      <c r="B46" s="40" t="s">
+      <c r="G46" s="45"/>
+      <c r="H46" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="I46" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="J46" s="45"/>
+      <c r="K46" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="L46" s="45" t="s">
         <v>522</v>
       </c>
-      <c r="C46" s="40"/>
-      <c r="D46" s="41">
-        <v>45</v>
-      </c>
-      <c r="E46" s="42" t="s">
+      <c r="M46" s="48"/>
+      <c r="N46" s="48"/>
+      <c r="O46" s="48"/>
+      <c r="P46" s="48"/>
+      <c r="Q46" s="48"/>
+      <c r="R46" s="48"/>
+      <c r="S46" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="T46" s="49"/>
+      <c r="U46" s="50"/>
+      <c r="V46" s="50"/>
+      <c r="W46" s="50"/>
+      <c r="X46" s="50"/>
+      <c r="Y46" s="45"/>
+      <c r="Z46" s="45"/>
+      <c r="AA46" s="45"/>
+      <c r="AB46" s="45"/>
+      <c r="AC46" s="45" t="s">
         <v>523</v>
       </c>
-      <c r="F46" s="40" t="s">
+      <c r="AD46" s="52" t="s">
         <v>524</v>
       </c>
-      <c r="G46" s="43"/>
-      <c r="H46" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="I46" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="J46" s="40"/>
-      <c r="K46" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="L46" s="40" t="s">
+    </row>
+    <row r="47" spans="1:30" ht="409.6">
+      <c r="A47" s="53" t="s">
         <v>525</v>
       </c>
-      <c r="M46" s="42"/>
-      <c r="N46" s="42"/>
-      <c r="O46" s="42"/>
-      <c r="P46" s="44"/>
-      <c r="Q46" s="44"/>
-      <c r="R46" s="44">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
-      <c r="S46" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T46" s="41"/>
-      <c r="U46" s="45"/>
-      <c r="V46" s="45"/>
-      <c r="W46" s="45"/>
-      <c r="X46" s="45"/>
-      <c r="Y46" s="40"/>
-      <c r="Z46" s="40"/>
-      <c r="AA46" s="40"/>
-      <c r="AB46" s="40"/>
-      <c r="AC46" s="40" t="s">
+      <c r="B47" s="54" t="s">
         <v>526</v>
       </c>
-      <c r="AD46" s="40" t="s">
+      <c r="C47" s="54"/>
+      <c r="D47" s="55">
+        <v>46</v>
+      </c>
+      <c r="E47" s="54" t="s">
+        <v>520</v>
+      </c>
+      <c r="F47" s="54" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="47" spans="1:30" ht="409.6">
-      <c r="A47" s="40" t="s">
+      <c r="G47" s="54"/>
+      <c r="H47" s="54" t="s">
+        <v>138</v>
+      </c>
+      <c r="I47" s="54" t="s">
+        <v>147</v>
+      </c>
+      <c r="J47" s="54"/>
+      <c r="K47" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="L47" s="54" t="s">
         <v>528</v>
       </c>
-      <c r="B47" s="40" t="s">
-        <v>529</v>
-      </c>
-      <c r="C47" s="40"/>
-      <c r="D47" s="41">
-        <v>46</v>
-      </c>
-      <c r="E47" s="42" t="s">
+      <c r="M47" s="56"/>
+      <c r="N47" s="56"/>
+      <c r="O47" s="56"/>
+      <c r="P47" s="56"/>
+      <c r="Q47" s="56"/>
+      <c r="R47" s="56"/>
+      <c r="S47" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="T47" s="57"/>
+      <c r="U47" s="58"/>
+      <c r="V47" s="58"/>
+      <c r="W47" s="58"/>
+      <c r="X47" s="58"/>
+      <c r="Y47" s="54"/>
+      <c r="Z47" s="54"/>
+      <c r="AA47" s="54"/>
+      <c r="AB47" s="54"/>
+      <c r="AC47" s="54" t="s">
         <v>523</v>
       </c>
-      <c r="F47" s="40" t="s">
-        <v>530</v>
-      </c>
-      <c r="G47" s="43"/>
-      <c r="H47" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="I47" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="J47" s="40"/>
-      <c r="K47" s="40" t="s">
-        <v>171</v>
-      </c>
-      <c r="L47" s="40" t="s">
-        <v>531</v>
-      </c>
-      <c r="M47" s="42"/>
-      <c r="N47" s="42"/>
-      <c r="O47" s="42"/>
-      <c r="P47" s="44"/>
-      <c r="Q47" s="44"/>
-      <c r="R47" s="44">
-        <f>SUM(Tabla22[[#This Row],[inversion_activos_computables_comprometida_anio_1_mill_usd]:[inversion_activos_computables_comprometida_anio_2_mill_usd]])</f>
-        <v>0</v>
-      </c>
-      <c r="S47" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="T47" s="41"/>
-      <c r="U47" s="45"/>
-      <c r="V47" s="45"/>
-      <c r="W47" s="45"/>
-      <c r="X47" s="45"/>
-      <c r="Y47" s="40"/>
-      <c r="Z47" s="40"/>
-      <c r="AA47" s="40"/>
-      <c r="AB47" s="40"/>
-      <c r="AC47" s="40" t="s">
-        <v>526</v>
-      </c>
-      <c r="AD47" s="40" t="s">
-        <v>527</v>
+      <c r="AD47" s="59" t="s">
+        <v>524</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="AB2" r:id="rId1" xr:uid="{E7946696-3FA0-2340-9F0D-F82232A2D521}"/>
     <hyperlink ref="AB3" r:id="rId2" xr:uid="{864830E5-443A-F949-B08D-A9A2D962FC53}"/>
@@ -6851,12 +6973,13 @@
     <hyperlink ref="AB36" r:id="rId23" xr:uid="{58EFA9E3-F5DD-7244-B47A-5A35FCC395E1}"/>
     <hyperlink ref="AB24" r:id="rId24" xr:uid="{8FAD3DFA-392A-1846-AD7B-B2015845524B}"/>
     <hyperlink ref="AB43" r:id="rId25" xr:uid="{90467AD9-CA04-EB46-8DEF-7CFABD5FF4FC}"/>
+    <hyperlink ref="AB35" r:id="rId26" xr:uid="{137286A0-EDBB-1A49-8504-B971F04F806C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId26"/>
-  <legacyDrawing r:id="rId27"/>
+  <drawing r:id="rId27"/>
+  <legacyDrawing r:id="rId28"/>
   <tableParts count="1">
-    <tablePart r:id="rId28"/>
+    <tablePart r:id="rId29"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6876,22 +6999,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="32">
       <c r="A1" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>380</v>
-      </c>
       <c r="E1" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16">
@@ -6899,19 +7022,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16">
@@ -6919,19 +7042,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16">
@@ -6939,19 +7062,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16">
@@ -6962,16 +7085,16 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16">
@@ -6982,16 +7105,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16">
@@ -6999,19 +7122,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16">
@@ -7019,19 +7142,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16">
@@ -7042,16 +7165,16 @@
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16">
@@ -7062,16 +7185,16 @@
         <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16">
@@ -7079,19 +7202,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16">
@@ -7102,16 +7225,16 @@
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16">
@@ -7122,16 +7245,16 @@
         <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16">
@@ -7139,19 +7262,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16">
@@ -7159,19 +7282,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16">
@@ -7179,19 +7302,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16">
@@ -7199,19 +7322,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16">
@@ -7219,19 +7342,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32">
@@ -7239,19 +7362,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16">
@@ -7259,19 +7382,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16">
@@ -7279,19 +7402,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16">
@@ -7299,19 +7422,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16">
@@ -7322,16 +7445,16 @@
         <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16">
@@ -7339,19 +7462,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16">
@@ -7359,19 +7482,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="16">
@@ -7382,16 +7505,16 @@
         <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="32">
@@ -7399,19 +7522,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16">
@@ -7419,19 +7542,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="16">
@@ -7439,19 +7562,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="16">
@@ -7459,19 +7582,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16">
@@ -7479,19 +7602,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -7506,13 +7629,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="64">
       <c r="A1" s="4" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16">
@@ -7520,10 +7643,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="48">
@@ -7531,10 +7654,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="112">
@@ -7542,10 +7665,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16">
@@ -7575,10 +7698,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="16">
@@ -7586,10 +7709,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16">
@@ -7619,10 +7742,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16">
@@ -7652,10 +7775,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="64">
@@ -7663,10 +7786,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="64">
@@ -7674,10 +7797,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="96">
@@ -7685,10 +7808,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="96">
@@ -7696,10 +7819,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="96">
@@ -7707,10 +7830,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="48">
@@ -7718,10 +7841,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="64">
@@ -7729,10 +7852,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="80">
@@ -7740,10 +7863,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="32">
@@ -7762,10 +7885,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="32">
@@ -7773,10 +7896,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="32">
@@ -7795,10 +7918,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="64">
@@ -7806,10 +7929,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16">
@@ -7817,10 +7940,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16">
@@ -7828,10 +7951,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="32">
@@ -7839,10 +7962,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
